--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -666,16 +666,16 @@
         <v>0.0245</v>
       </c>
       <c r="F2" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H2" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I2" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="J2" t="n">
         <v>0.833</v>
@@ -690,7 +690,7 @@
         <v>0.733</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O2" t="n">
         <v>0.767</v>
@@ -738,7 +738,7 @@
         <v>0.867</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="AE2" t="n">
         <v>0.833</v>
@@ -802,16 +802,16 @@
         <v>0.0376</v>
       </c>
       <c r="F3" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H3" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I3" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="J3" t="n">
         <v>0.833</v>
@@ -826,7 +826,7 @@
         <v>0.733</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O3" t="n">
         <v>0.767</v>
@@ -874,7 +874,7 @@
         <v>0.867</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="AE3" t="n">
         <v>0.833</v>
@@ -938,16 +938,16 @@
         <v>0.062</v>
       </c>
       <c r="F4" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G4" t="n">
-        <v>0.806</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I4" t="n">
-        <v>0.119</v>
+        <v>0.115</v>
       </c>
       <c r="J4" t="n">
         <v>0.833</v>
@@ -962,7 +962,7 @@
         <v>0.733</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O4" t="n">
         <v>0.767</v>
@@ -1010,7 +1010,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="AE4" t="n">
         <v>0.733</v>
@@ -1074,16 +1074,16 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.806</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I5" t="n">
-        <v>0.119</v>
+        <v>0.115</v>
       </c>
       <c r="J5" t="n">
         <v>0.833</v>
@@ -1098,7 +1098,7 @@
         <v>0.733</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O5" t="n">
         <v>0.767</v>
@@ -1146,7 +1146,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="AE5" t="n">
         <v>0.733</v>
@@ -1210,16 +1210,16 @@
         <v>0.0699</v>
       </c>
       <c r="F6" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.12</v>
+        <v>0.117</v>
       </c>
       <c r="J6" t="n">
         <v>0.833</v>
@@ -1234,7 +1234,7 @@
         <v>0.733</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O6" t="n">
         <v>0.767</v>
@@ -1282,7 +1282,7 @@
         <v>0.967</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="AE6" t="n">
         <v>0.8</v>
@@ -1346,16 +1346,16 @@
         <v>0.0987</v>
       </c>
       <c r="F7" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I7" t="n">
-        <v>0.12</v>
+        <v>0.117</v>
       </c>
       <c r="J7" t="n">
         <v>0.833</v>
@@ -1370,7 +1370,7 @@
         <v>0.733</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O7" t="n">
         <v>0.767</v>
@@ -1418,7 +1418,7 @@
         <v>0.967</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="AE7" t="n">
         <v>0.8</v>
@@ -1482,16 +1482,16 @@
         <v>0.109</v>
       </c>
       <c r="F8" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>0.802</v>
       </c>
       <c r="H8" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I8" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="J8" t="n">
         <v>0.833</v>
@@ -1506,7 +1506,7 @@
         <v>0.733</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O8" t="n">
         <v>0.767</v>
@@ -1554,7 +1554,7 @@
         <v>0.967</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="AE8" t="n">
         <v>0.733</v>
@@ -1618,16 +1618,16 @@
         <v>0.196</v>
       </c>
       <c r="F9" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0.802</v>
       </c>
       <c r="H9" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I9" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="J9" t="n">
         <v>0.833</v>
@@ -1642,7 +1642,7 @@
         <v>0.733</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O9" t="n">
         <v>0.767</v>
@@ -1690,7 +1690,7 @@
         <v>0.967</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="AE9" t="n">
         <v>0.733</v>
@@ -1754,16 +1754,16 @@
         <v>0.0381</v>
       </c>
       <c r="F10" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G10" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="H10" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I10" t="n">
-        <v>0.15</v>
+        <v>0.147</v>
       </c>
       <c r="J10" t="n">
         <v>0.833</v>
@@ -1778,7 +1778,7 @@
         <v>0.733</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O10" t="n">
         <v>0.767</v>
@@ -1826,7 +1826,7 @@
         <v>0.833</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AE10" t="n">
         <v>0.833</v>
@@ -1890,16 +1890,16 @@
         <v>0.0532</v>
       </c>
       <c r="F11" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="G11" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="H11" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="I11" t="n">
-        <v>0.15</v>
+        <v>0.147</v>
       </c>
       <c r="J11" t="n">
         <v>0.833</v>
@@ -1914,7 +1914,7 @@
         <v>0.733</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O11" t="n">
         <v>0.767</v>
@@ -1962,7 +1962,7 @@
         <v>0.833</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AE11" t="n">
         <v>0.833</v>
@@ -2295,19 +2295,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.343</v>
+        <v>0.394</v>
       </c>
       <c r="F14" t="n">
         <v>0.804</v>
       </c>
       <c r="G14" t="n">
-        <v>0.79</v>
+        <v>0.792</v>
       </c>
       <c r="H14" t="n">
         <v>0.119</v>
       </c>
       <c r="I14" t="n">
-        <v>0.147</v>
+        <v>0.144</v>
       </c>
       <c r="J14" t="n">
         <v>0.767</v>
@@ -2370,7 +2370,7 @@
         <v>0.967</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AE14" t="n">
         <v>0.9</v>
@@ -2406,7 +2406,7 @@
         <v>0.467</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.381</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="15">
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.238</v>
+        <v>0.28</v>
       </c>
       <c r="F15" t="n">
         <v>0.804</v>
       </c>
       <c r="G15" t="n">
-        <v>0.79</v>
+        <v>0.792</v>
       </c>
       <c r="H15" t="n">
         <v>0.119</v>
       </c>
       <c r="I15" t="n">
-        <v>0.147</v>
+        <v>0.144</v>
       </c>
       <c r="J15" t="n">
         <v>0.767</v>
@@ -2506,7 +2506,7 @@
         <v>0.967</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AE15" t="n">
         <v>0.9</v>
@@ -2542,7 +2542,7 @@
         <v>0.467</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.264</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="16">
@@ -2567,19 +2567,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0322</v>
+        <v>0.0285</v>
       </c>
       <c r="F16" t="n">
         <v>0.804</v>
       </c>
       <c r="G16" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="H16" t="n">
         <v>0.119</v>
       </c>
       <c r="I16" t="n">
-        <v>0.151</v>
+        <v>0.148</v>
       </c>
       <c r="J16" t="n">
         <v>0.767</v>
@@ -2642,7 +2642,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AE16" t="n">
         <v>0.867</v>
@@ -2703,19 +2703,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0326</v>
+        <v>0.0325</v>
       </c>
       <c r="F17" t="n">
         <v>0.804</v>
       </c>
       <c r="G17" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="H17" t="n">
         <v>0.119</v>
       </c>
       <c r="I17" t="n">
-        <v>0.151</v>
+        <v>0.148</v>
       </c>
       <c r="J17" t="n">
         <v>0.767</v>
@@ -2778,7 +2778,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AE17" t="n">
         <v>0.867</v>
@@ -3111,19 +3111,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0203</v>
+        <v>0.0319</v>
       </c>
       <c r="F20" t="n">
         <v>0.804</v>
       </c>
       <c r="G20" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="H20" t="n">
         <v>0.119</v>
       </c>
       <c r="I20" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="J20" t="n">
         <v>0.767</v>
@@ -3186,7 +3186,7 @@
         <v>0.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="AE20" t="n">
         <v>0.833</v>
@@ -3247,19 +3247,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0201</v>
+        <v>0.0311</v>
       </c>
       <c r="F21" t="n">
         <v>0.804</v>
       </c>
       <c r="G21" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="H21" t="n">
         <v>0.119</v>
       </c>
       <c r="I21" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="J21" t="n">
         <v>0.767</v>
@@ -3322,7 +3322,7 @@
         <v>0.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="AE21" t="n">
         <v>0.833</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0308</v>
+        <v>0.0314</v>
       </c>
       <c r="F22" t="n">
         <v>0.731</v>
@@ -3392,7 +3392,7 @@
         <v>0.867</v>
       </c>
       <c r="H22" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I22" t="n">
         <v>0.141</v>
@@ -3410,7 +3410,7 @@
         <v>0.462</v>
       </c>
       <c r="N22" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O22" t="n">
         <v>0.792</v>
@@ -3458,7 +3458,7 @@
         <v>0.667</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="AE22" t="n">
         <v>0.833</v>
@@ -3494,7 +3494,7 @@
         <v>0.75</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.0616</v>
+        <v>0.06279999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3528,7 +3528,7 @@
         <v>0.867</v>
       </c>
       <c r="H23" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I23" t="n">
         <v>0.141</v>
@@ -3546,7 +3546,7 @@
         <v>0.462</v>
       </c>
       <c r="N23" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O23" t="n">
         <v>0.792</v>
@@ -3594,7 +3594,7 @@
         <v>0.667</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="AE23" t="n">
         <v>0.833</v>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0137</v>
+        <v>0.0139</v>
       </c>
       <c r="F24" t="n">
         <v>0.731</v>
@@ -3664,7 +3664,7 @@
         <v>0.888</v>
       </c>
       <c r="H24" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I24" t="n">
         <v>0.113</v>
@@ -3682,7 +3682,7 @@
         <v>0.462</v>
       </c>
       <c r="N24" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O24" t="n">
         <v>0.792</v>
@@ -3730,7 +3730,7 @@
         <v>0.857</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.875</v>
+        <v>0.882</v>
       </c>
       <c r="AE24" t="n">
         <v>0.76</v>
@@ -3766,7 +3766,7 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.0407</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="25">
@@ -3800,7 +3800,7 @@
         <v>0.888</v>
       </c>
       <c r="H25" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I25" t="n">
         <v>0.113</v>
@@ -3818,7 +3818,7 @@
         <v>0.462</v>
       </c>
       <c r="N25" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O25" t="n">
         <v>0.792</v>
@@ -3866,7 +3866,7 @@
         <v>0.857</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.875</v>
+        <v>0.882</v>
       </c>
       <c r="AE25" t="n">
         <v>0.76</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.00183</v>
+        <v>0.00188</v>
       </c>
       <c r="F26" t="n">
         <v>0.731</v>
@@ -3936,7 +3936,7 @@
         <v>0.894</v>
       </c>
       <c r="H26" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I26" t="n">
         <v>0.108</v>
@@ -3954,7 +3954,7 @@
         <v>0.462</v>
       </c>
       <c r="N26" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O26" t="n">
         <v>0.792</v>
@@ -4002,7 +4002,7 @@
         <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="AE26" t="n">
         <v>0.826</v>
@@ -4038,7 +4038,7 @@
         <v>0.714</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.0183</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="27">
@@ -4072,7 +4072,7 @@
         <v>0.894</v>
       </c>
       <c r="H27" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I27" t="n">
         <v>0.108</v>
@@ -4090,7 +4090,7 @@
         <v>0.462</v>
       </c>
       <c r="N27" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O27" t="n">
         <v>0.792</v>
@@ -4138,7 +4138,7 @@
         <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="AE27" t="n">
         <v>0.826</v>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.00417</v>
+        <v>0.00427</v>
       </c>
       <c r="F28" t="n">
         <v>0.731</v>
@@ -4208,7 +4208,7 @@
         <v>0.873</v>
       </c>
       <c r="H28" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I28" t="n">
         <v>0.155</v>
@@ -4226,7 +4226,7 @@
         <v>0.462</v>
       </c>
       <c r="N28" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O28" t="n">
         <v>0.792</v>
@@ -4274,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="AE28" t="n">
         <v>0.783</v>
@@ -4310,7 +4310,7 @@
         <v>0.765</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.0209</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="29">
@@ -4344,7 +4344,7 @@
         <v>0.873</v>
       </c>
       <c r="H29" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I29" t="n">
         <v>0.155</v>
@@ -4362,7 +4362,7 @@
         <v>0.462</v>
       </c>
       <c r="N29" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O29" t="n">
         <v>0.792</v>
@@ -4410,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="AE29" t="n">
         <v>0.783</v>
@@ -4471,16 +4471,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0163</v>
+        <v>0.0165</v>
       </c>
       <c r="F30" t="n">
         <v>0.731</v>
       </c>
       <c r="G30" t="n">
-        <v>0.822</v>
+        <v>0.823</v>
       </c>
       <c r="H30" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I30" t="n">
         <v>0.156</v>
@@ -4498,7 +4498,7 @@
         <v>0.462</v>
       </c>
       <c r="N30" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O30" t="n">
         <v>0.792</v>
@@ -4546,7 +4546,7 @@
         <v>0.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.857</v>
+        <v>0.867</v>
       </c>
       <c r="AE30" t="n">
         <v>0.864</v>
@@ -4582,7 +4582,7 @@
         <v>0.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.0407</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="31">
@@ -4613,10 +4613,10 @@
         <v>0.731</v>
       </c>
       <c r="G31" t="n">
-        <v>0.822</v>
+        <v>0.823</v>
       </c>
       <c r="H31" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="I31" t="n">
         <v>0.156</v>
@@ -4634,7 +4634,7 @@
         <v>0.462</v>
       </c>
       <c r="N31" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="O31" t="n">
         <v>0.792</v>
@@ -4682,7 +4682,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.857</v>
+        <v>0.867</v>
       </c>
       <c r="AE31" t="n">
         <v>0.864</v>
@@ -4854,7 +4854,7 @@
         <v>0.462</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.358</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="33">
@@ -4990,7 +4990,7 @@
         <v>0.462</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.345</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="34">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.322</v>
+        <v>0.333</v>
       </c>
       <c r="F34" t="n">
         <v>0.853</v>
       </c>
       <c r="G34" t="n">
-        <v>0.833</v>
+        <v>0.834</v>
       </c>
       <c r="H34" t="n">
         <v>0.13</v>
@@ -5090,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.762</v>
+        <v>0.773</v>
       </c>
       <c r="AE34" t="n">
         <v>0.909</v>
@@ -5126,7 +5126,7 @@
         <v>0.481</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.358</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="35">
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.328</v>
+        <v>0.374</v>
       </c>
       <c r="F35" t="n">
         <v>0.853</v>
       </c>
       <c r="G35" t="n">
-        <v>0.833</v>
+        <v>0.834</v>
       </c>
       <c r="H35" t="n">
         <v>0.13</v>
@@ -5226,7 +5226,7 @@
         <v>1</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.762</v>
+        <v>0.773</v>
       </c>
       <c r="AE35" t="n">
         <v>0.909</v>
@@ -5262,7 +5262,7 @@
         <v>0.481</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.345</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="36">
@@ -5287,13 +5287,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.298</v>
+        <v>0.31</v>
       </c>
       <c r="F36" t="n">
         <v>0.853</v>
       </c>
       <c r="G36" t="n">
-        <v>0.835</v>
+        <v>0.836</v>
       </c>
       <c r="H36" t="n">
         <v>0.13</v>
@@ -5362,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.778</v>
+        <v>0.789</v>
       </c>
       <c r="AE36" t="n">
         <v>0.905</v>
@@ -5398,7 +5398,7 @@
         <v>0.48</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.358</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="37">
@@ -5429,7 +5429,7 @@
         <v>0.853</v>
       </c>
       <c r="G37" t="n">
-        <v>0.835</v>
+        <v>0.836</v>
       </c>
       <c r="H37" t="n">
         <v>0.13</v>
@@ -5498,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.778</v>
+        <v>0.789</v>
       </c>
       <c r="AE37" t="n">
         <v>0.905</v>
@@ -6106,16 +6106,16 @@
         <v>0.499</v>
       </c>
       <c r="F42" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8</v>
+        <v>0.802</v>
       </c>
       <c r="H42" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I42" t="n">
-        <v>0.169</v>
+        <v>0.167</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -6130,7 +6130,7 @@
         <v>0.857</v>
       </c>
       <c r="N42" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O42" t="n">
         <v>0.905</v>
@@ -6178,7 +6178,7 @@
         <v>0.857</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="AE42" t="n">
         <v>0.952</v>
@@ -6214,7 +6214,7 @@
         <v>0.6</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.907</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="43">
@@ -6242,16 +6242,16 @@
         <v>0.575</v>
       </c>
       <c r="F43" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8</v>
+        <v>0.802</v>
       </c>
       <c r="H43" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I43" t="n">
-        <v>0.169</v>
+        <v>0.167</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -6266,7 +6266,7 @@
         <v>0.857</v>
       </c>
       <c r="N43" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O43" t="n">
         <v>0.905</v>
@@ -6314,7 +6314,7 @@
         <v>0.857</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="AE43" t="n">
         <v>0.952</v>
@@ -6350,7 +6350,7 @@
         <v>0.6</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.866</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="44">
@@ -6378,16 +6378,16 @@
         <v>0.799</v>
       </c>
       <c r="F44" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G44" t="n">
-        <v>0.771</v>
+        <v>0.774</v>
       </c>
       <c r="H44" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I44" t="n">
-        <v>0.181</v>
+        <v>0.179</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -6402,7 +6402,7 @@
         <v>0.857</v>
       </c>
       <c r="N44" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O44" t="n">
         <v>0.905</v>
@@ -6450,7 +6450,7 @@
         <v>0.857</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="AE44" t="n">
         <v>0.905</v>
@@ -6486,7 +6486,7 @@
         <v>0.6</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.907</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="45">
@@ -6514,16 +6514,16 @@
         <v>0.423</v>
       </c>
       <c r="F45" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G45" t="n">
-        <v>0.771</v>
+        <v>0.774</v>
       </c>
       <c r="H45" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I45" t="n">
-        <v>0.181</v>
+        <v>0.179</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -6538,7 +6538,7 @@
         <v>0.857</v>
       </c>
       <c r="N45" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O45" t="n">
         <v>0.905</v>
@@ -6586,7 +6586,7 @@
         <v>0.857</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="AE45" t="n">
         <v>0.905</v>
@@ -6622,7 +6622,7 @@
         <v>0.6</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.866</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="46">
@@ -6650,16 +6650,16 @@
         <v>0.827</v>
       </c>
       <c r="F46" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G46" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="H46" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I46" t="n">
-        <v>0.176</v>
+        <v>0.174</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -6674,7 +6674,7 @@
         <v>0.857</v>
       </c>
       <c r="N46" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O46" t="n">
         <v>0.905</v>
@@ -6722,7 +6722,7 @@
         <v>0.857</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="AE46" t="n">
         <v>0.905</v>
@@ -6758,7 +6758,7 @@
         <v>0.667</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.907</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="47">
@@ -6786,16 +6786,16 @@
         <v>0.657</v>
       </c>
       <c r="F47" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G47" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="H47" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I47" t="n">
-        <v>0.176</v>
+        <v>0.174</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -6810,7 +6810,7 @@
         <v>0.857</v>
       </c>
       <c r="N47" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O47" t="n">
         <v>0.905</v>
@@ -6858,7 +6858,7 @@
         <v>0.857</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="AE47" t="n">
         <v>0.905</v>
@@ -6894,7 +6894,7 @@
         <v>0.667</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.866</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="48">
@@ -6922,16 +6922,16 @@
         <v>0.907</v>
       </c>
       <c r="F48" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G48" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="H48" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I48" t="n">
-        <v>0.172</v>
+        <v>0.171</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6946,7 +6946,7 @@
         <v>0.857</v>
       </c>
       <c r="N48" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O48" t="n">
         <v>0.905</v>
@@ -6994,7 +6994,7 @@
         <v>0.857</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="AE48" t="n">
         <v>0.857</v>
@@ -7030,7 +7030,7 @@
         <v>0.867</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.907</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="49">
@@ -7058,16 +7058,16 @@
         <v>0.433</v>
       </c>
       <c r="F49" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G49" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="H49" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I49" t="n">
-        <v>0.172</v>
+        <v>0.171</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -7082,7 +7082,7 @@
         <v>0.857</v>
       </c>
       <c r="N49" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O49" t="n">
         <v>0.905</v>
@@ -7130,7 +7130,7 @@
         <v>0.857</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="AE49" t="n">
         <v>0.857</v>
@@ -7166,7 +7166,7 @@
         <v>0.867</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.866</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="50">
@@ -7194,16 +7194,16 @@
         <v>0.888</v>
       </c>
       <c r="F50" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G50" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="H50" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I50" t="n">
-        <v>0.183</v>
+        <v>0.179</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -7218,7 +7218,7 @@
         <v>0.857</v>
       </c>
       <c r="N50" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O50" t="n">
         <v>0.905</v>
@@ -7266,7 +7266,7 @@
         <v>0.857</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="AE50" t="n">
         <v>0.905</v>
@@ -7302,7 +7302,7 @@
         <v>0.8</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.907</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="51">
@@ -7330,16 +7330,16 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="G51" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="H51" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="I51" t="n">
-        <v>0.183</v>
+        <v>0.179</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -7354,7 +7354,7 @@
         <v>0.857</v>
       </c>
       <c r="N51" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="O51" t="n">
         <v>0.905</v>
@@ -7402,7 +7402,7 @@
         <v>0.857</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="AE51" t="n">
         <v>0.905</v>
@@ -7438,7 +7438,7 @@
         <v>0.8</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.866</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="52">
@@ -7574,7 +7574,7 @@
         <v>0.8</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.907</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="53">
@@ -7710,7 +7710,7 @@
         <v>0.8</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.866</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="54">
@@ -7735,19 +7735,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.832</v>
+        <v>0.959</v>
       </c>
       <c r="F54" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H54" t="n">
         <v>0.205</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>0.198</v>
       </c>
       <c r="J54" t="n">
         <v>0.958</v>
@@ -7810,7 +7810,7 @@
         <v>0.857</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="AE54" t="n">
         <v>0.952</v>
@@ -7846,7 +7846,7 @@
         <v>0.867</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.907</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="55">
@@ -7871,19 +7871,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.866</v>
+        <v>0.674</v>
       </c>
       <c r="F55" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H55" t="n">
         <v>0.205</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>0.198</v>
       </c>
       <c r="J55" t="n">
         <v>0.958</v>
@@ -7946,7 +7946,7 @@
         <v>0.857</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="AE55" t="n">
         <v>0.952</v>
@@ -7982,7 +7982,7 @@
         <v>0.867</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.866</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="56">
@@ -8007,19 +8007,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0646</v>
+        <v>0.0775</v>
       </c>
       <c r="F56" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0.764</v>
+        <v>0.767</v>
       </c>
       <c r="H56" t="n">
         <v>0.205</v>
       </c>
       <c r="I56" t="n">
-        <v>0.199</v>
+        <v>0.196</v>
       </c>
       <c r="J56" t="n">
         <v>0.958</v>
@@ -8082,7 +8082,7 @@
         <v>0.714</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="AE56" t="n">
         <v>0.905</v>
@@ -8118,7 +8118,7 @@
         <v>0.8</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.323</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="57">
@@ -8143,19 +8143,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0745</v>
+        <v>0.0926</v>
       </c>
       <c r="F57" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.764</v>
+        <v>0.767</v>
       </c>
       <c r="H57" t="n">
         <v>0.205</v>
       </c>
       <c r="I57" t="n">
-        <v>0.199</v>
+        <v>0.196</v>
       </c>
       <c r="J57" t="n">
         <v>0.958</v>
@@ -8218,7 +8218,7 @@
         <v>0.714</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="AE57" t="n">
         <v>0.905</v>
@@ -8254,7 +8254,7 @@
         <v>0.8</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.372</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="58">
@@ -8390,7 +8390,7 @@
         <v>0.867</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.907</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="59">
@@ -8526,7 +8526,7 @@
         <v>0.867</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.866</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="60">
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00396</v>
+        <v>0.00468</v>
       </c>
       <c r="F60" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>0.632</v>
+        <v>0.634</v>
       </c>
       <c r="H60" t="n">
         <v>0.205</v>
@@ -8626,7 +8626,7 @@
         <v>0.571</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AE60" t="n">
         <v>0.857</v>
@@ -8662,7 +8662,7 @@
         <v>0.733</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.0396</v>
+        <v>0.0468</v>
       </c>
     </row>
     <row r="61">
@@ -8687,13 +8687,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.00147</v>
       </c>
       <c r="F61" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>0.632</v>
+        <v>0.634</v>
       </c>
       <c r="H61" t="n">
         <v>0.205</v>
@@ -8762,7 +8762,7 @@
         <v>0.571</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AE61" t="n">
         <v>0.857</v>
@@ -8798,7 +8798,7 @@
         <v>0.733</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.00979</v>
+        <v>0.0147</v>
       </c>
     </row>
   </sheetData>
@@ -9227,16 +9227,16 @@
         <v>0.889</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="W2" t="n">
-        <v>0.187</v>
+        <v>0.18</v>
       </c>
       <c r="X2" t="n">
-        <v>0.749</v>
+        <v>0.719</v>
       </c>
       <c r="Y2" t="n">
         <v>0.767</v>
@@ -9441,16 +9441,16 @@
         <v>0.948</v>
       </c>
       <c r="U3" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="W3" t="n">
-        <v>0.335</v>
+        <v>0.338</v>
       </c>
       <c r="X3" t="n">
-        <v>0.894</v>
+        <v>0.9</v>
       </c>
       <c r="Y3" t="n">
         <v>0.792</v>
@@ -9655,13 +9655,13 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="V4" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="W4" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -9869,13 +9869,13 @@
         <v>0.319</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="W5" t="n">
-        <v>0.604</v>
+        <v>0.601</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -10083,13 +10083,13 @@
         <v>0.631</v>
       </c>
       <c r="U6" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="V6" t="n">
-        <v>0.875</v>
+        <v>0.882</v>
       </c>
       <c r="W6" t="n">
-        <v>0.656</v>
+        <v>0.658</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -10297,10 +10297,10 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="V7" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
@@ -10511,16 +10511,16 @@
         <v>0.137</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="V8" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="n">
-        <v>0.295</v>
+        <v>0.288</v>
       </c>
       <c r="X8" t="n">
-        <v>0.773</v>
+        <v>0.768</v>
       </c>
       <c r="Y8" t="n">
         <v>0.767</v>
@@ -10604,7 +10604,7 @@
         <v>0.254</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.773</v>
+        <v>0.768</v>
       </c>
       <c r="BA8" t="n">
         <v>0.9</v>
@@ -10725,13 +10725,13 @@
         <v>0.304</v>
       </c>
       <c r="U9" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="V9" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="W9" t="n">
-        <v>0.402</v>
+        <v>0.405</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -10939,13 +10939,13 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="V10" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="W10" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -11153,16 +11153,16 @@
         <v>0.206</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="W11" t="n">
-        <v>0.187</v>
+        <v>0.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0.749</v>
+        <v>0.719</v>
       </c>
       <c r="Y11" t="n">
         <v>0.767</v>
@@ -11367,13 +11367,13 @@
         <v>0.285</v>
       </c>
       <c r="U12" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="W12" t="n">
-        <v>0.335</v>
+        <v>0.338</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -11581,13 +11581,13 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="V13" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="W13" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
@@ -11795,10 +11795,10 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="V14" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
@@ -12009,13 +12009,13 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="V15" t="n">
-        <v>0.857</v>
+        <v>0.867</v>
       </c>
       <c r="W15" t="n">
-        <v>0.664</v>
+        <v>0.665</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -12223,10 +12223,10 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="V16" t="n">
         <v>0.542</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.5</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
@@ -13082,10 +13082,10 @@
         <v>0.667</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0.596</v>
+        <v>0.789</v>
       </c>
       <c r="X20" t="n">
         <v>1</v>
@@ -13296,10 +13296,10 @@
         <v>0.889</v>
       </c>
       <c r="V21" t="n">
-        <v>0.762</v>
+        <v>0.773</v>
       </c>
       <c r="W21" t="n">
-        <v>0.418</v>
+        <v>0.427</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -13510,7 +13510,7 @@
         <v>0.667</v>
       </c>
       <c r="V22" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="W22" t="n">
         <v>1</v>
@@ -13724,10 +13724,10 @@
         <v>0.667</v>
       </c>
       <c r="V23" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0.43</v>
+        <v>0.596</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -13938,10 +13938,10 @@
         <v>0.889</v>
       </c>
       <c r="V24" t="n">
-        <v>0.778</v>
+        <v>0.789</v>
       </c>
       <c r="W24" t="n">
-        <v>0.658</v>
+        <v>0.66</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
@@ -14152,10 +14152,10 @@
         <v>0.667</v>
       </c>
       <c r="V25" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="W25" t="n">
-        <v>0.766</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -15008,10 +15008,10 @@
         <v>0.667</v>
       </c>
       <c r="V29" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
@@ -15225,7 +15225,7 @@
         <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>0.489</v>
+        <v>0.487</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
@@ -15436,7 +15436,7 @@
         <v>0.667</v>
       </c>
       <c r="V31" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>

--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0245</v>
+        <v>0.0414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G2" t="n">
-        <v>0.819</v>
+        <v>0.831</v>
       </c>
       <c r="H2" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I2" t="n">
+        <v>0.09229999999999999</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.11</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0878</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0376</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G3" t="n">
-        <v>0.819</v>
+        <v>0.831</v>
       </c>
       <c r="H3" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I3" t="n">
-        <v>0.11</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.094</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.062</v>
+        <v>0.141</v>
       </c>
       <c r="F4" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="H4" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I4" t="n">
-        <v>0.115</v>
+        <v>0.104</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0999</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="F5" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="H5" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I5" t="n">
-        <v>0.115</v>
+        <v>0.104</v>
       </c>
       <c r="J5" t="n">
-        <v>0.14</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0699</v>
+        <v>0.222</v>
       </c>
       <c r="F6" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G6" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I6" t="n">
         <v>0.117</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0999</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0987</v>
+        <v>0.361</v>
       </c>
       <c r="F7" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G7" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I7" t="n">
         <v>0.117</v>
       </c>
       <c r="J7" t="n">
-        <v>0.141</v>
+        <v>0.401</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.109</v>
+        <v>0.208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G8" t="n">
-        <v>0.802</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I8" t="n">
-        <v>0.114</v>
+        <v>0.102</v>
       </c>
       <c r="J8" t="n">
-        <v>0.136</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.196</v>
+        <v>0.33</v>
       </c>
       <c r="F9" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G9" t="n">
-        <v>0.802</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I9" t="n">
-        <v>0.114</v>
+        <v>0.102</v>
       </c>
       <c r="J9" t="n">
-        <v>0.245</v>
+        <v>0.401</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0381</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G10" t="n">
-        <v>0.783</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I10" t="n">
-        <v>0.147</v>
+        <v>0.138</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0878</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0532</v>
+        <v>0.157</v>
       </c>
       <c r="F11" t="n">
-        <v>0.735</v>
+        <v>0.76</v>
       </c>
       <c r="G11" t="n">
-        <v>0.783</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="I11" t="n">
-        <v>0.147</v>
+        <v>0.138</v>
       </c>
       <c r="J11" t="n">
-        <v>0.106</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.51</v>
+        <v>0.449</v>
       </c>
       <c r="F12" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G12" t="n">
         <v>0.794</v>
       </c>
       <c r="H12" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I12" t="n">
         <v>0.143</v>
       </c>
       <c r="J12" t="n">
-        <v>0.51</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.477</v>
+        <v>0.455</v>
       </c>
       <c r="F13" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G13" t="n">
         <v>0.794</v>
       </c>
       <c r="H13" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I13" t="n">
         <v>0.143</v>
       </c>
       <c r="J13" t="n">
-        <v>0.477</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="14">
@@ -986,16 +986,16 @@
         <v>0.394</v>
       </c>
       <c r="F14" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G14" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="H14" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I14" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="J14" t="n">
         <v>0.438</v>
@@ -1026,19 +1026,19 @@
         <v>0.28</v>
       </c>
       <c r="F15" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G15" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="H15" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I15" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="J15" t="n">
-        <v>0.311</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16">
@@ -1066,19 +1066,19 @@
         <v>0.0285</v>
       </c>
       <c r="F16" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G16" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="H16" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I16" t="n">
-        <v>0.148</v>
+        <v>0.146</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0878</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="17">
@@ -1106,19 +1106,19 @@
         <v>0.0325</v>
       </c>
       <c r="F17" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G17" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="H17" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I17" t="n">
-        <v>0.148</v>
+        <v>0.146</v>
       </c>
       <c r="J17" t="n">
-        <v>0.094</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="18">
@@ -1146,19 +1146,19 @@
         <v>0.0439</v>
       </c>
       <c r="F18" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G18" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="H18" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I18" t="n">
-        <v>0.151</v>
+        <v>0.149</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0878</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="19">
@@ -1186,19 +1186,19 @@
         <v>0.0313</v>
       </c>
       <c r="F19" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G19" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="H19" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I19" t="n">
-        <v>0.151</v>
+        <v>0.149</v>
       </c>
       <c r="J19" t="n">
-        <v>0.094</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="20">
@@ -1226,19 +1226,19 @@
         <v>0.0319</v>
       </c>
       <c r="F20" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G20" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="H20" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I20" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0878</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="21">
@@ -1266,19 +1266,19 @@
         <v>0.0311</v>
       </c>
       <c r="F21" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G21" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="H21" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I21" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J21" t="n">
-        <v>0.094</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0314</v>
+        <v>0.0559</v>
       </c>
       <c r="F22" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G22" t="n">
-        <v>0.867</v>
+        <v>0.874</v>
       </c>
       <c r="H22" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I22" t="n">
-        <v>0.141</v>
+        <v>0.139</v>
       </c>
       <c r="J22" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="23">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0277</v>
+        <v>0.0426</v>
       </c>
       <c r="F23" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G23" t="n">
-        <v>0.867</v>
+        <v>0.874</v>
       </c>
       <c r="H23" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I23" t="n">
-        <v>0.141</v>
+        <v>0.139</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0554</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="24">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0139</v>
+        <v>0.0268</v>
       </c>
       <c r="F24" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G24" t="n">
-        <v>0.888</v>
+        <v>0.897</v>
       </c>
       <c r="H24" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I24" t="n">
-        <v>0.113</v>
+        <v>0.107</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0413</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0121</v>
+        <v>0.0186</v>
       </c>
       <c r="F25" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G25" t="n">
-        <v>0.888</v>
+        <v>0.897</v>
       </c>
       <c r="H25" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I25" t="n">
-        <v>0.113</v>
+        <v>0.107</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0375</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="26">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.00188</v>
+        <v>0.00754</v>
       </c>
       <c r="F26" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G26" t="n">
         <v>0.894</v>
       </c>
       <c r="H26" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I26" t="n">
         <v>0.108</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0188</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.00222</v>
+        <v>0.00604</v>
       </c>
       <c r="F27" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G27" t="n">
         <v>0.894</v>
       </c>
       <c r="H27" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I27" t="n">
         <v>0.108</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0222</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.00427</v>
+        <v>0.009939999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G28" t="n">
-        <v>0.873</v>
+        <v>0.883</v>
       </c>
       <c r="H28" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I28" t="n">
-        <v>0.155</v>
+        <v>0.149</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0214</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="29">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.00444</v>
+        <v>0.00765</v>
       </c>
       <c r="F29" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G29" t="n">
-        <v>0.873</v>
+        <v>0.883</v>
       </c>
       <c r="H29" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I29" t="n">
-        <v>0.155</v>
+        <v>0.149</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0222</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="30">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0165</v>
+        <v>0.0344</v>
       </c>
       <c r="F30" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G30" t="n">
-        <v>0.823</v>
+        <v>0.837</v>
       </c>
       <c r="H30" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I30" t="n">
-        <v>0.156</v>
+        <v>0.155</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0413</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.015</v>
+        <v>0.0262</v>
       </c>
       <c r="F31" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="G31" t="n">
-        <v>0.823</v>
+        <v>0.837</v>
       </c>
       <c r="H31" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="I31" t="n">
-        <v>0.156</v>
+        <v>0.155</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0375</v>
+        <v>0.0655</v>
       </c>
     </row>
     <row r="32">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.28</v>
+        <v>0.279</v>
       </c>
       <c r="F32" t="n">
         <v>0.853</v>
@@ -1715,10 +1715,10 @@
         <v>0.13</v>
       </c>
       <c r="I32" t="n">
-        <v>0.172</v>
+        <v>0.173</v>
       </c>
       <c r="J32" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="33">
@@ -1755,7 +1755,7 @@
         <v>0.13</v>
       </c>
       <c r="I33" t="n">
-        <v>0.172</v>
+        <v>0.173</v>
       </c>
       <c r="J33" t="n">
         <v>0.374</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="F34" t="n">
         <v>0.853</v>
@@ -1798,7 +1798,7 @@
         <v>0.159</v>
       </c>
       <c r="J34" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="35">
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.31</v>
+        <v>0.313</v>
       </c>
       <c r="F36" t="n">
         <v>0.853</v>
       </c>
       <c r="G36" t="n">
-        <v>0.836</v>
+        <v>0.837</v>
       </c>
       <c r="H36" t="n">
         <v>0.13</v>
@@ -1878,7 +1878,7 @@
         <v>0.147</v>
       </c>
       <c r="J36" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="37">
@@ -1909,7 +1909,7 @@
         <v>0.853</v>
       </c>
       <c r="G37" t="n">
-        <v>0.836</v>
+        <v>0.837</v>
       </c>
       <c r="H37" t="n">
         <v>0.13</v>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.15</v>
+        <v>0.152</v>
       </c>
       <c r="F38" t="n">
         <v>0.853</v>
       </c>
       <c r="G38" t="n">
-        <v>0.83</v>
+        <v>0.831</v>
       </c>
       <c r="H38" t="n">
         <v>0.13</v>
@@ -1958,7 +1958,7 @@
         <v>0.159</v>
       </c>
       <c r="J38" t="n">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="39">
@@ -1989,7 +1989,7 @@
         <v>0.853</v>
       </c>
       <c r="G39" t="n">
-        <v>0.83</v>
+        <v>0.831</v>
       </c>
       <c r="H39" t="n">
         <v>0.13</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.65</v>
+        <v>0.652</v>
       </c>
       <c r="F40" t="n">
         <v>0.853</v>
@@ -2038,7 +2038,7 @@
         <v>0.186</v>
       </c>
       <c r="J40" t="n">
-        <v>0.65</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="41">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.499</v>
+        <v>0.416</v>
       </c>
       <c r="F42" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G42" t="n">
-        <v>0.802</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I42" t="n">
-        <v>0.167</v>
+        <v>0.154</v>
       </c>
       <c r="J42" t="n">
         <v>0.959</v>
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.575</v>
+        <v>0.553</v>
       </c>
       <c r="F43" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G43" t="n">
-        <v>0.802</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I43" t="n">
-        <v>0.167</v>
+        <v>0.154</v>
       </c>
       <c r="J43" t="n">
-        <v>0.779</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="44">
@@ -2183,19 +2183,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.799</v>
+        <v>0.731</v>
       </c>
       <c r="F44" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G44" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="H44" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I44" t="n">
-        <v>0.179</v>
+        <v>0.176</v>
       </c>
       <c r="J44" t="n">
         <v>0.959</v>
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.423</v>
+        <v>0.346</v>
       </c>
       <c r="F45" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G45" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="H45" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I45" t="n">
-        <v>0.179</v>
+        <v>0.176</v>
       </c>
       <c r="J45" t="n">
-        <v>0.779</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="46">
@@ -2263,16 +2263,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.827</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G46" t="n">
         <v>0.772</v>
       </c>
       <c r="H46" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I46" t="n">
         <v>0.174</v>
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.657</v>
+        <v>0.556</v>
       </c>
       <c r="F47" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G47" t="n">
         <v>0.772</v>
       </c>
       <c r="H47" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I47" t="n">
         <v>0.174</v>
       </c>
       <c r="J47" t="n">
-        <v>0.779</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="48">
@@ -2343,19 +2343,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.907</v>
+        <v>0.782</v>
       </c>
       <c r="F48" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G48" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="H48" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I48" t="n">
-        <v>0.171</v>
+        <v>0.164</v>
       </c>
       <c r="J48" t="n">
         <v>0.959</v>
@@ -2386,19 +2386,19 @@
         <v>0.433</v>
       </c>
       <c r="F49" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G49" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="H49" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I49" t="n">
-        <v>0.171</v>
+        <v>0.164</v>
       </c>
       <c r="J49" t="n">
-        <v>0.779</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="50">
@@ -2426,16 +2426,16 @@
         <v>0.888</v>
       </c>
       <c r="F50" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G50" t="n">
-        <v>0.788</v>
+        <v>0.796</v>
       </c>
       <c r="H50" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I50" t="n">
-        <v>0.179</v>
+        <v>0.177</v>
       </c>
       <c r="J50" t="n">
         <v>0.959</v>
@@ -2466,19 +2466,19 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="G51" t="n">
-        <v>0.788</v>
+        <v>0.796</v>
       </c>
       <c r="H51" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="I51" t="n">
-        <v>0.179</v>
+        <v>0.177</v>
       </c>
       <c r="J51" t="n">
-        <v>0.779</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="52">
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.796</v>
+        <v>0.723</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I52" t="n">
         <v>0.199</v>
@@ -2543,22 +2543,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.754</v>
+        <v>0.638</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I53" t="n">
         <v>0.199</v>
       </c>
       <c r="J53" t="n">
-        <v>0.779</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="54">
@@ -2586,16 +2586,16 @@
         <v>0.959</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I54" t="n">
-        <v>0.198</v>
+        <v>0.197</v>
       </c>
       <c r="J54" t="n">
         <v>0.959</v>
@@ -2626,19 +2626,19 @@
         <v>0.674</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I55" t="n">
-        <v>0.198</v>
+        <v>0.197</v>
       </c>
       <c r="J55" t="n">
-        <v>0.779</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="56">
@@ -2666,16 +2666,16 @@
         <v>0.0775</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="H56" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I56" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="J56" t="n">
         <v>0.388</v>
@@ -2706,16 +2706,16 @@
         <v>0.0926</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="H57" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I57" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="J57" t="n">
         <v>0.463</v>
@@ -2746,16 +2746,16 @@
         <v>0.579</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I58" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="J58" t="n">
         <v>0.959</v>
@@ -2786,16 +2786,16 @@
         <v>0.779</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I59" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="J59" t="n">
         <v>0.779</v>
@@ -2826,16 +2826,16 @@
         <v>0.00468</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>0.634</v>
+        <v>0.637</v>
       </c>
       <c r="H60" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I60" t="n">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
       <c r="J60" t="n">
         <v>0.0468</v>
@@ -2866,16 +2866,16 @@
         <v>0.00147</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>0.634</v>
+        <v>0.637</v>
       </c>
       <c r="H61" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I61" t="n">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
       <c r="J61" t="n">
         <v>0.0147</v>
@@ -3078,16 +3078,16 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G5" t="n">
         <v>0.867</v>
       </c>
       <c r="H5" t="n">
-        <v>0.333</v>
+        <v>0.506</v>
       </c>
       <c r="I5" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3115,16 +3115,16 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.533</v>
+        <v>0.6</v>
       </c>
       <c r="G6" t="n">
         <v>0.733</v>
       </c>
       <c r="H6" t="n">
-        <v>0.18</v>
+        <v>0.412</v>
       </c>
       <c r="I6" t="n">
-        <v>0.719</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3152,13 +3152,13 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.767</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H7" t="n">
-        <v>0.748</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -3189,13 +3189,13 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="G8" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>0.771</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -3300,16 +3300,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G11" t="n">
         <v>0.667</v>
       </c>
       <c r="H11" t="n">
-        <v>0.295</v>
+        <v>0.43</v>
       </c>
       <c r="I11" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3337,13 +3337,13 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
-        <v>0.596</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -3642,7 +3642,7 @@
         <v>0.25</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="21">
@@ -3670,16 +3670,16 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="G21" t="n">
         <v>0.667</v>
       </c>
       <c r="H21" t="n">
-        <v>0.415</v>
+        <v>0.66</v>
       </c>
       <c r="I21" t="n">
-        <v>0.948</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -3707,16 +3707,16 @@
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.778</v>
+        <v>0.875</v>
       </c>
       <c r="G22" t="n">
         <v>0.944</v>
       </c>
       <c r="H22" t="n">
-        <v>0.338</v>
+        <v>0.591</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -3744,10 +3744,10 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.792</v>
+        <v>0.909</v>
       </c>
       <c r="G23" t="n">
-        <v>0.833</v>
+        <v>0.87</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -3781,13 +3781,13 @@
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.708</v>
+        <v>0.773</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8</v>
+        <v>0.842</v>
       </c>
       <c r="H24" t="n">
-        <v>0.728</v>
+        <v>0.703</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -3892,16 +3892,16 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G27" t="n">
         <v>0.875</v>
       </c>
       <c r="H27" t="n">
-        <v>0.248</v>
+        <v>0.257</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="28">
@@ -3929,13 +3929,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="G28" t="n">
-        <v>0.867</v>
+        <v>0.895</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.678</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -4336,7 +4336,7 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="G39" t="n">
         <v>0.952</v>
@@ -4521,13 +4521,13 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="G44" t="n">
-        <v>0.542</v>
+        <v>0.708</v>
       </c>
       <c r="H44" t="n">
-        <v>0.227</v>
+        <v>0.494</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -4854,16 +4854,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G53" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="I53" t="n">
-        <v>0.319</v>
+        <v>0.582</v>
       </c>
     </row>
     <row r="54">
@@ -4891,13 +4891,13 @@
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.533</v>
+        <v>0.6</v>
       </c>
       <c r="G54" t="n">
         <v>0.633</v>
       </c>
       <c r="H54" t="n">
-        <v>0.601</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -4928,16 +4928,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.767</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.733</v>
-      </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0.299</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4965,10 +4965,10 @@
         <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="G56" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
@@ -5076,16 +5076,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G59" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="H59" t="n">
-        <v>0.295</v>
+        <v>0.288</v>
       </c>
       <c r="I59" t="n">
-        <v>0.786</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -5113,10 +5113,10 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="G60" t="n">
-        <v>0.633</v>
+        <v>0.7</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
@@ -5159,7 +5159,7 @@
         <v>0.254</v>
       </c>
       <c r="I61" t="n">
-        <v>0.786</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -5233,7 +5233,7 @@
         <v>0.424</v>
       </c>
       <c r="I63" t="n">
-        <v>0.969</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="64">
@@ -5344,7 +5344,7 @@
         <v>0.21</v>
       </c>
       <c r="I66" t="n">
-        <v>0.673</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="67">
@@ -5446,16 +5446,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="G69" t="n">
         <v>0.857</v>
       </c>
       <c r="H69" t="n">
-        <v>0.158</v>
+        <v>0.173</v>
       </c>
       <c r="I69" t="n">
-        <v>0.631</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="70">
@@ -5483,13 +5483,13 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.778</v>
+        <v>0.875</v>
       </c>
       <c r="G70" t="n">
         <v>0.882</v>
       </c>
       <c r="H70" t="n">
-        <v>0.658</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -5520,16 +5520,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="G71" t="n">
         <v>0.792</v>
       </c>
-      <c r="G71" t="n">
-        <v>0.76</v>
-      </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0.418</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="72">
@@ -5557,13 +5557,13 @@
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.708</v>
+        <v>0.773</v>
       </c>
       <c r="G72" t="n">
-        <v>0.762</v>
+        <v>0.8</v>
       </c>
       <c r="H72" t="n">
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -5668,16 +5668,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G75" t="n">
-        <v>0.833</v>
+        <v>0.882</v>
       </c>
       <c r="H75" t="n">
-        <v>0.29</v>
+        <v>0.246</v>
       </c>
       <c r="I75" t="n">
-        <v>0.773</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="76">
@@ -5705,10 +5705,10 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="G76" t="n">
-        <v>0.842</v>
+        <v>0.857</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -6112,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="G87" t="n">
         <v>0.905</v>
@@ -6297,13 +6297,13 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G92" t="n">
         <v>0.75</v>
       </c>
-      <c r="G92" t="n">
-        <v>0.667</v>
-      </c>
       <c r="H92" t="n">
-        <v>0.752</v>
+        <v>0.724</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -6528,7 +6528,7 @@
         <v>0.36</v>
       </c>
       <c r="I98" t="n">
-        <v>0.773</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6630,16 +6630,16 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G101" t="n">
         <v>0.967</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0257</v>
+        <v>0.0523</v>
       </c>
       <c r="I101" t="n">
-        <v>0.137</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="102">
@@ -6667,16 +6667,16 @@
         <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>0.533</v>
+        <v>0.6</v>
       </c>
       <c r="G102" t="n">
         <v>0.7</v>
       </c>
       <c r="H102" t="n">
-        <v>0.288</v>
+        <v>0.589</v>
       </c>
       <c r="I102" t="n">
-        <v>0.768</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="103">
@@ -6704,16 +6704,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.767</v>
+        <v>0.9</v>
       </c>
       <c r="G103" t="n">
         <v>0.8</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0.472</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6741,13 +6741,13 @@
         <v>7</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="G104" t="n">
         <v>0.767</v>
       </c>
       <c r="H104" t="n">
-        <v>0.771</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -6852,16 +6852,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G107" t="n">
         <v>0.633</v>
       </c>
       <c r="H107" t="n">
-        <v>0.435</v>
+        <v>0.601</v>
       </c>
       <c r="I107" t="n">
-        <v>0.773</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="108">
@@ -6889,7 +6889,7 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="G108" t="n">
         <v>0.7</v>
@@ -6935,7 +6935,7 @@
         <v>0.254</v>
       </c>
       <c r="I109" t="n">
-        <v>0.768</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="110">
@@ -7009,7 +7009,7 @@
         <v>0.424</v>
       </c>
       <c r="I111" t="n">
-        <v>0.773</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -7222,13 +7222,13 @@
         <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0436</v>
+        <v>0.0537</v>
       </c>
       <c r="I117" t="n">
         <v>0.304</v>
@@ -7259,13 +7259,13 @@
         <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>0.778</v>
+        <v>0.875</v>
       </c>
       <c r="G118" t="n">
         <v>0.895</v>
       </c>
       <c r="H118" t="n">
-        <v>0.405</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -7296,13 +7296,13 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.792</v>
+        <v>0.909</v>
       </c>
       <c r="G119" t="n">
         <v>0.826</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0.665</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -7333,13 +7333,13 @@
         <v>7</v>
       </c>
       <c r="F120" t="n">
-        <v>0.708</v>
+        <v>0.773</v>
       </c>
       <c r="G120" t="n">
         <v>0.8</v>
       </c>
       <c r="H120" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -7444,13 +7444,13 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G123" t="n">
         <v>0.824</v>
       </c>
       <c r="H123" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -7481,13 +7481,13 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="G124" t="n">
         <v>0.895</v>
       </c>
       <c r="H124" t="n">
-        <v>0.668</v>
+        <v>0.678</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -7888,7 +7888,7 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="G135" t="n">
         <v>0.905</v>
@@ -8073,13 +8073,13 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="G140" t="n">
         <v>0.708</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>0.494</v>
       </c>
       <c r="I140" t="n">
         <v>1</v>
@@ -8406,16 +8406,16 @@
         <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G149" t="n">
         <v>0.967</v>
       </c>
       <c r="H149" t="n">
-        <v>0.0257</v>
+        <v>0.0523</v>
       </c>
       <c r="I149" t="n">
-        <v>0.206</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="150">
@@ -8443,16 +8443,16 @@
         <v>5</v>
       </c>
       <c r="F150" t="n">
-        <v>0.533</v>
+        <v>0.6</v>
       </c>
       <c r="G150" t="n">
         <v>0.733</v>
       </c>
       <c r="H150" t="n">
-        <v>0.18</v>
+        <v>0.412</v>
       </c>
       <c r="I150" t="n">
-        <v>0.719</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="151">
@@ -8480,16 +8480,16 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G151" t="n">
         <v>0.767</v>
       </c>
-      <c r="G151" t="n">
-        <v>0.733</v>
-      </c>
       <c r="H151" t="n">
-        <v>1</v>
+        <v>0.299</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="152">
@@ -8517,10 +8517,10 @@
         <v>7</v>
       </c>
       <c r="F152" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="G152" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -8628,13 +8628,13 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G155" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="H155" t="n">
-        <v>0.604</v>
+        <v>0.601</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
@@ -8665,10 +8665,10 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="G156" t="n">
-        <v>0.633</v>
+        <v>0.7</v>
       </c>
       <c r="H156" t="n">
         <v>1</v>
@@ -8711,7 +8711,7 @@
         <v>0.424</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="158">
@@ -8822,7 +8822,7 @@
         <v>0.047</v>
       </c>
       <c r="I160" t="n">
-        <v>0.251</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="161">
@@ -8998,16 +8998,16 @@
         <v>4</v>
       </c>
       <c r="F165" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0436</v>
+        <v>0.0537</v>
       </c>
       <c r="I165" t="n">
-        <v>0.285</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="166">
@@ -9035,13 +9035,13 @@
         <v>5</v>
       </c>
       <c r="F166" t="n">
-        <v>0.778</v>
+        <v>0.875</v>
       </c>
       <c r="G166" t="n">
         <v>0.944</v>
       </c>
       <c r="H166" t="n">
-        <v>0.338</v>
+        <v>0.591</v>
       </c>
       <c r="I166" t="n">
         <v>1</v>
@@ -9072,13 +9072,13 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.792</v>
+        <v>0.909</v>
       </c>
       <c r="G167" t="n">
-        <v>0.783</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>0.664</v>
       </c>
       <c r="I167" t="n">
         <v>1</v>
@@ -9109,10 +9109,10 @@
         <v>7</v>
       </c>
       <c r="F168" t="n">
-        <v>0.708</v>
+        <v>0.773</v>
       </c>
       <c r="G168" t="n">
-        <v>0.75</v>
+        <v>0.789</v>
       </c>
       <c r="H168" t="n">
         <v>1</v>
@@ -9220,13 +9220,13 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G171" t="n">
-        <v>0.778</v>
+        <v>0.824</v>
       </c>
       <c r="H171" t="n">
-        <v>0.497</v>
+        <v>0.462</v>
       </c>
       <c r="I171" t="n">
         <v>1</v>
@@ -9257,13 +9257,13 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="G172" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H172" t="n">
-        <v>0.629</v>
+        <v>0.382</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
@@ -9414,7 +9414,7 @@
         <v>0.0534</v>
       </c>
       <c r="I176" t="n">
-        <v>0.285</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="177">
@@ -9445,13 +9445,13 @@
         <v>0.308</v>
       </c>
       <c r="G177" t="n">
-        <v>0.765</v>
+        <v>0.8</v>
       </c>
       <c r="H177" t="n">
-        <v>0.0247</v>
+        <v>0.02</v>
       </c>
       <c r="I177" t="n">
-        <v>0.285</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="178">
@@ -9664,13 +9664,13 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="G183" t="n">
         <v>0.857</v>
       </c>
       <c r="H183" t="n">
-        <v>1</v>
+        <v>0.606</v>
       </c>
       <c r="I183" t="n">
         <v>1</v>
@@ -9849,13 +9849,13 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="G188" t="n">
-        <v>0.583</v>
+        <v>0.667</v>
       </c>
       <c r="H188" t="n">
-        <v>0.359</v>
+        <v>0.318</v>
       </c>
       <c r="I188" t="n">
         <v>1</v>
@@ -10037,13 +10037,13 @@
         <v>0.267</v>
       </c>
       <c r="G193" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="H193" t="n">
-        <v>0.00251</v>
+        <v>0.009220000000000001</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0401</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="194">
@@ -10182,13 +10182,13 @@
         <v>4</v>
       </c>
       <c r="F197" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="G197" t="n">
         <v>0.833</v>
       </c>
       <c r="H197" t="n">
-        <v>0.532</v>
+        <v>0.748</v>
       </c>
       <c r="I197" t="n">
         <v>1</v>
@@ -10219,7 +10219,7 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>0.533</v>
+        <v>0.6</v>
       </c>
       <c r="G198" t="n">
         <v>0.5669999999999999</v>
@@ -10256,13 +10256,13 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.767</v>
+        <v>0.9</v>
       </c>
       <c r="G199" t="n">
-        <v>0.833</v>
+        <v>0.9</v>
       </c>
       <c r="H199" t="n">
-        <v>0.748</v>
+        <v>1</v>
       </c>
       <c r="I199" t="n">
         <v>1</v>
@@ -10293,10 +10293,10 @@
         <v>7</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="G200" t="n">
-        <v>0.733</v>
+        <v>0.8</v>
       </c>
       <c r="H200" t="n">
         <v>1</v>
@@ -10404,13 +10404,13 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="G203" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H203" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="I203" t="n">
         <v>1</v>
@@ -10441,10 +10441,10 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="G204" t="n">
-        <v>0.633</v>
+        <v>0.7</v>
       </c>
       <c r="H204" t="n">
         <v>1</v>
@@ -10629,10 +10629,10 @@
         <v>0.333</v>
       </c>
       <c r="G209" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H209" t="n">
-        <v>0.295</v>
+        <v>0.192</v>
       </c>
       <c r="I209" t="n">
         <v>1</v>
@@ -10774,13 +10774,13 @@
         <v>4</v>
       </c>
       <c r="F213" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="G213" t="n">
         <v>0.6</v>
       </c>
       <c r="H213" t="n">
-        <v>0.68</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="I213" t="n">
         <v>1</v>
@@ -10811,13 +10811,13 @@
         <v>5</v>
       </c>
       <c r="F214" t="n">
-        <v>0.778</v>
+        <v>0.875</v>
       </c>
       <c r="G214" t="n">
         <v>0.867</v>
       </c>
       <c r="H214" t="n">
-        <v>0.665</v>
+        <v>1</v>
       </c>
       <c r="I214" t="n">
         <v>1</v>
@@ -10848,13 +10848,13 @@
         <v>6</v>
       </c>
       <c r="F215" t="n">
-        <v>0.792</v>
+        <v>0.909</v>
       </c>
       <c r="G215" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="H215" t="n">
-        <v>0.702</v>
+        <v>1</v>
       </c>
       <c r="I215" t="n">
         <v>1</v>
@@ -10885,13 +10885,13 @@
         <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>0.708</v>
+        <v>0.773</v>
       </c>
       <c r="G216" t="n">
-        <v>0.762</v>
+        <v>0.842</v>
       </c>
       <c r="H216" t="n">
-        <v>0.746</v>
+        <v>0.703</v>
       </c>
       <c r="I216" t="n">
         <v>1</v>
@@ -10996,13 +10996,13 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G219" t="n">
-        <v>0.867</v>
+        <v>0.929</v>
       </c>
       <c r="H219" t="n">
-        <v>0.252</v>
+        <v>0.198</v>
       </c>
       <c r="I219" t="n">
         <v>1</v>
@@ -11033,13 +11033,13 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="G220" t="n">
-        <v>0.882</v>
+        <v>0.895</v>
       </c>
       <c r="H220" t="n">
-        <v>0.679</v>
+        <v>0.678</v>
       </c>
       <c r="I220" t="n">
         <v>1</v>
@@ -11221,10 +11221,10 @@
         <v>0.308</v>
       </c>
       <c r="G225" t="n">
-        <v>0.5</v>
+        <v>0.522</v>
       </c>
       <c r="H225" t="n">
-        <v>0.315</v>
+        <v>0.301</v>
       </c>
       <c r="I225" t="n">
         <v>1</v>
@@ -11440,10 +11440,10 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="G231" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="H231" t="n">
         <v>1</v>
@@ -11625,13 +11625,13 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="G236" t="n">
-        <v>0.625</v>
+        <v>0.708</v>
       </c>
       <c r="H236" t="n">
-        <v>0.534</v>
+        <v>0.494</v>
       </c>
       <c r="I236" t="n">
         <v>1</v>
@@ -12146,10 +12146,10 @@
         <v>0.8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H250" t="n">
-        <v>0.761</v>
+        <v>0.552</v>
       </c>
       <c r="I250" t="n">
         <v>1</v>
@@ -12217,13 +12217,13 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G252" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="H252" t="n">
-        <v>0.779</v>
+        <v>0.771</v>
       </c>
       <c r="I252" t="n">
         <v>1</v>
@@ -12809,10 +12809,10 @@
         <v>11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="G268" t="n">
-        <v>0.9</v>
+        <v>0.905</v>
       </c>
       <c r="H268" t="n">
         <v>1</v>
@@ -13330,10 +13330,10 @@
         <v>0.8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H282" t="n">
-        <v>0.761</v>
+        <v>0.552</v>
       </c>
       <c r="I282" t="n">
         <v>1</v>
@@ -13401,13 +13401,13 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="G284" t="n">
-        <v>0.75</v>
+        <v>0.792</v>
       </c>
       <c r="H284" t="n">
-        <v>0.752</v>
+        <v>0.74</v>
       </c>
       <c r="I284" t="n">
         <v>1</v>
@@ -13993,10 +13993,10 @@
         <v>11</v>
       </c>
       <c r="F300" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G300" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -14585,10 +14585,10 @@
         <v>11</v>
       </c>
       <c r="F316" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="G316" t="n">
-        <v>0.895</v>
+        <v>0.9</v>
       </c>
       <c r="H316" t="n">
         <v>1</v>
@@ -15177,10 +15177,10 @@
         <v>11</v>
       </c>
       <c r="F332" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="G332" t="n">
-        <v>0.708</v>
+        <v>0.75</v>
       </c>
       <c r="H332" t="n">
         <v>1</v>
@@ -15769,10 +15769,10 @@
         <v>11</v>
       </c>
       <c r="F348" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G348" t="n">
         <v>0.667</v>
-      </c>
-      <c r="G348" t="n">
-        <v>0.633</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -16361,10 +16361,10 @@
         <v>11</v>
       </c>
       <c r="F364" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="G364" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16953,10 +16953,10 @@
         <v>11</v>
       </c>
       <c r="F380" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="G380" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="H380" t="n">
         <v>1</v>
@@ -17545,10 +17545,10 @@
         <v>11</v>
       </c>
       <c r="F396" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G396" t="n">
         <v>0.667</v>
-      </c>
-      <c r="G396" t="n">
-        <v>0.633</v>
       </c>
       <c r="H396" t="n">
         <v>1</v>
@@ -18137,10 +18137,10 @@
         <v>11</v>
       </c>
       <c r="F412" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="G412" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="H412" t="n">
         <v>1</v>
@@ -18729,10 +18729,10 @@
         <v>11</v>
       </c>
       <c r="F428" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="G428" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="H428" t="n">
         <v>1</v>
@@ -19321,13 +19321,13 @@
         <v>11</v>
       </c>
       <c r="F444" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G444" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="H444" t="n">
-        <v>0.789</v>
+        <v>0.785</v>
       </c>
       <c r="I444" t="n">
         <v>1</v>
@@ -19913,10 +19913,10 @@
         <v>11</v>
       </c>
       <c r="F460" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="G460" t="n">
-        <v>0.929</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H460" t="n">
         <v>1</v>
@@ -20505,13 +20505,13 @@
         <v>11</v>
       </c>
       <c r="F476" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="G476" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="H476" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="I476" t="n">
         <v>1</v>

--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0414</v>
+        <v>0.106</v>
       </c>
       <c r="F2" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.831</v>
+        <v>0.85</v>
       </c>
       <c r="H2" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0852</v>
       </c>
       <c r="J2" t="n">
-        <v>0.11</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.831</v>
+        <v>0.85</v>
       </c>
       <c r="H3" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0852</v>
       </c>
       <c r="J3" t="n">
-        <v>0.187</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.141</v>
+        <v>0.336</v>
       </c>
       <c r="F4" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.819</v>
+        <v>0.829</v>
       </c>
       <c r="H4" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="J4" t="n">
-        <v>0.235</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.142</v>
+        <v>0.44</v>
       </c>
       <c r="F5" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>0.819</v>
+        <v>0.829</v>
       </c>
       <c r="H5" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="J5" t="n">
-        <v>0.262</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.222</v>
+        <v>0.714</v>
       </c>
       <c r="F6" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I6" t="n">
-        <v>0.117</v>
+        <v>0.124</v>
       </c>
       <c r="J6" t="n">
-        <v>0.278</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.361</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.117</v>
+        <v>0.124</v>
       </c>
       <c r="J7" t="n">
-        <v>0.401</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.208</v>
+        <v>0.63</v>
       </c>
       <c r="F8" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.102</v>
+        <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.278</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>0.102</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="n">
-        <v>0.401</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>0.848</v>
       </c>
       <c r="H10" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.138</v>
+        <v>0.107</v>
       </c>
       <c r="J10" t="n">
-        <v>0.195</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.157</v>
+        <v>0.118</v>
       </c>
       <c r="F11" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0.848</v>
       </c>
       <c r="H11" t="n">
-        <v>0.174</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>0.138</v>
+        <v>0.107</v>
       </c>
       <c r="J11" t="n">
-        <v>0.262</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.449</v>
+        <v>0.572</v>
       </c>
       <c r="F12" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.794</v>
+        <v>0.804</v>
       </c>
       <c r="H12" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I12" t="n">
-        <v>0.143</v>
+        <v>0.137</v>
       </c>
       <c r="J12" t="n">
-        <v>0.449</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.455</v>
+        <v>0.499</v>
       </c>
       <c r="F13" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.794</v>
+        <v>0.804</v>
       </c>
       <c r="H13" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I13" t="n">
-        <v>0.143</v>
+        <v>0.137</v>
       </c>
       <c r="J13" t="n">
-        <v>0.455</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.394</v>
+        <v>0.401</v>
       </c>
       <c r="F14" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.794</v>
+        <v>0.802</v>
       </c>
       <c r="H14" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I14" t="n">
-        <v>0.143</v>
+        <v>0.137</v>
       </c>
       <c r="J14" t="n">
-        <v>0.438</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.28</v>
+        <v>0.327</v>
       </c>
       <c r="F15" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.794</v>
+        <v>0.802</v>
       </c>
       <c r="H15" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I15" t="n">
-        <v>0.143</v>
+        <v>0.137</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0285</v>
+        <v>0.008970000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.781</v>
+        <v>0.787</v>
       </c>
       <c r="H16" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I16" t="n">
-        <v>0.146</v>
+        <v>0.142</v>
       </c>
       <c r="J16" t="n">
-        <v>0.11</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0325</v>
+        <v>0.0119</v>
       </c>
       <c r="F17" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.781</v>
+        <v>0.787</v>
       </c>
       <c r="H17" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I17" t="n">
-        <v>0.146</v>
+        <v>0.142</v>
       </c>
       <c r="J17" t="n">
-        <v>0.108</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="18">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0439</v>
+        <v>0.0057</v>
       </c>
       <c r="F18" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.783</v>
+        <v>0.788</v>
       </c>
       <c r="H18" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I18" t="n">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="J18" t="n">
-        <v>0.11</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="19">
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0313</v>
+        <v>0.0106</v>
       </c>
       <c r="F19" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.783</v>
+        <v>0.788</v>
       </c>
       <c r="H19" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I19" t="n">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="J19" t="n">
-        <v>0.108</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="20">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0319</v>
+        <v>0.0506</v>
       </c>
       <c r="F20" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.765</v>
+        <v>0.771</v>
       </c>
       <c r="H20" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I20" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="J20" t="n">
-        <v>0.11</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="21">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0311</v>
+        <v>0.047</v>
       </c>
       <c r="F21" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.765</v>
+        <v>0.771</v>
       </c>
       <c r="H21" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I21" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="J21" t="n">
-        <v>0.108</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0559</v>
+        <v>0.152</v>
       </c>
       <c r="F22" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.874</v>
+        <v>0.9</v>
       </c>
       <c r="H22" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I22" t="n">
-        <v>0.139</v>
+        <v>0.123</v>
       </c>
       <c r="J22" t="n">
-        <v>0.112</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="23">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0426</v>
+        <v>0.184</v>
       </c>
       <c r="F23" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.874</v>
+        <v>0.9</v>
       </c>
       <c r="H23" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I23" t="n">
-        <v>0.139</v>
+        <v>0.123</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0852</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="24">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0268</v>
+        <v>0.0623</v>
       </c>
       <c r="F24" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.897</v>
+        <v>0.917</v>
       </c>
       <c r="H24" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I24" t="n">
-        <v>0.107</v>
+        <v>0.103</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="25">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0186</v>
+        <v>0.0409</v>
       </c>
       <c r="F25" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.897</v>
+        <v>0.917</v>
       </c>
       <c r="H25" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I25" t="n">
-        <v>0.107</v>
+        <v>0.103</v>
       </c>
       <c r="J25" t="n">
-        <v>0.062</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="26">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.00754</v>
+        <v>0.0253</v>
       </c>
       <c r="F26" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.894</v>
+        <v>0.903</v>
       </c>
       <c r="H26" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I26" t="n">
-        <v>0.108</v>
+        <v>0.0977</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0497</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.00604</v>
+        <v>0.0128</v>
       </c>
       <c r="F27" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.894</v>
+        <v>0.903</v>
       </c>
       <c r="H27" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I27" t="n">
-        <v>0.108</v>
+        <v>0.0977</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0382</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.009939999999999999</v>
+        <v>0.0217</v>
       </c>
       <c r="F28" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.883</v>
+        <v>0.889</v>
       </c>
       <c r="H28" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I28" t="n">
-        <v>0.149</v>
+        <v>0.147</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0497</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="29">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.00765</v>
+        <v>0.0218</v>
       </c>
       <c r="F29" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.883</v>
+        <v>0.889</v>
       </c>
       <c r="H29" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I29" t="n">
-        <v>0.149</v>
+        <v>0.147</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0382</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="30">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0344</v>
+        <v>0.0424</v>
       </c>
       <c r="F30" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.837</v>
+        <v>0.89</v>
       </c>
       <c r="H30" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I30" t="n">
-        <v>0.155</v>
+        <v>0.111</v>
       </c>
       <c r="J30" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="31">
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0262</v>
+        <v>0.0382</v>
       </c>
       <c r="F31" t="n">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.837</v>
+        <v>0.89</v>
       </c>
       <c r="H31" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="I31" t="n">
-        <v>0.155</v>
+        <v>0.111</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0655</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.279</v>
+        <v>0.322</v>
       </c>
       <c r="F32" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G32" t="n">
-        <v>0.832</v>
+        <v>0.838</v>
       </c>
       <c r="H32" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I32" t="n">
-        <v>0.173</v>
+        <v>0.163</v>
       </c>
       <c r="J32" t="n">
-        <v>0.369</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="33">
@@ -1746,19 +1746,19 @@
         <v>0.345</v>
       </c>
       <c r="F33" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G33" t="n">
-        <v>0.832</v>
+        <v>0.838</v>
       </c>
       <c r="H33" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I33" t="n">
-        <v>0.173</v>
+        <v>0.163</v>
       </c>
       <c r="J33" t="n">
-        <v>0.374</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="34">
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.332</v>
+        <v>0.368</v>
       </c>
       <c r="F34" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G34" t="n">
-        <v>0.834</v>
+        <v>0.84</v>
       </c>
       <c r="H34" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I34" t="n">
-        <v>0.159</v>
+        <v>0.149</v>
       </c>
       <c r="J34" t="n">
-        <v>0.369</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="35">
@@ -1823,22 +1823,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.374</v>
+        <v>0.328</v>
       </c>
       <c r="F35" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G35" t="n">
-        <v>0.834</v>
+        <v>0.84</v>
       </c>
       <c r="H35" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I35" t="n">
-        <v>0.159</v>
+        <v>0.149</v>
       </c>
       <c r="J35" t="n">
-        <v>0.374</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="36">
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.313</v>
+        <v>0.355</v>
       </c>
       <c r="F36" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G36" t="n">
-        <v>0.837</v>
+        <v>0.843</v>
       </c>
       <c r="H36" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I36" t="n">
-        <v>0.147</v>
+        <v>0.135</v>
       </c>
       <c r="J36" t="n">
-        <v>0.369</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="37">
@@ -1906,16 +1906,16 @@
         <v>0.239</v>
       </c>
       <c r="F37" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G37" t="n">
-        <v>0.837</v>
+        <v>0.843</v>
       </c>
       <c r="H37" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I37" t="n">
-        <v>0.147</v>
+        <v>0.135</v>
       </c>
       <c r="J37" t="n">
         <v>0.299</v>
@@ -1943,19 +1943,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.152</v>
+        <v>0.151</v>
       </c>
       <c r="F38" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G38" t="n">
-        <v>0.831</v>
+        <v>0.836</v>
       </c>
       <c r="H38" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I38" t="n">
-        <v>0.159</v>
+        <v>0.149</v>
       </c>
       <c r="J38" t="n">
         <v>0.253</v>
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.182</v>
+        <v>0.155</v>
       </c>
       <c r="F39" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G39" t="n">
-        <v>0.831</v>
+        <v>0.836</v>
       </c>
       <c r="H39" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I39" t="n">
-        <v>0.159</v>
+        <v>0.149</v>
       </c>
       <c r="J39" t="n">
-        <v>0.26</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="40">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.652</v>
+        <v>0.588</v>
       </c>
       <c r="F40" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G40" t="n">
-        <v>0.867</v>
+        <v>0.874</v>
       </c>
       <c r="H40" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I40" t="n">
-        <v>0.186</v>
+        <v>0.177</v>
       </c>
       <c r="J40" t="n">
-        <v>0.652</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="41">
@@ -2066,19 +2066,19 @@
         <v>0.0844</v>
       </c>
       <c r="F41" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G41" t="n">
-        <v>0.867</v>
+        <v>0.874</v>
       </c>
       <c r="H41" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I41" t="n">
-        <v>0.186</v>
+        <v>0.177</v>
       </c>
       <c r="J41" t="n">
-        <v>0.141</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="42">
@@ -2103,22 +2103,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.416</v>
+        <v>0.4</v>
       </c>
       <c r="F42" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.838</v>
       </c>
       <c r="H42" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I42" t="n">
-        <v>0.154</v>
+        <v>0.151</v>
       </c>
       <c r="J42" t="n">
-        <v>0.959</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="43">
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.553</v>
+        <v>0.515</v>
       </c>
       <c r="F43" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.838</v>
       </c>
       <c r="H43" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I43" t="n">
-        <v>0.154</v>
+        <v>0.151</v>
       </c>
       <c r="J43" t="n">
-        <v>0.749</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="44">
@@ -2183,22 +2183,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.731</v>
+        <v>0.497</v>
       </c>
       <c r="F44" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>0.779</v>
+        <v>0.792</v>
       </c>
       <c r="H44" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I44" t="n">
-        <v>0.176</v>
+        <v>0.184</v>
       </c>
       <c r="J44" t="n">
-        <v>0.959</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="45">
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="F45" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>0.779</v>
+        <v>0.792</v>
       </c>
       <c r="H45" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I45" t="n">
-        <v>0.176</v>
+        <v>0.184</v>
       </c>
       <c r="J45" t="n">
-        <v>0.749</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="46">
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.449</v>
       </c>
       <c r="F46" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>0.772</v>
+        <v>0.78</v>
       </c>
       <c r="H46" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I46" t="n">
-        <v>0.174</v>
+        <v>0.188</v>
       </c>
       <c r="J46" t="n">
-        <v>0.959</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="47">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.556</v>
+        <v>0.382</v>
       </c>
       <c r="F47" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0.772</v>
+        <v>0.78</v>
       </c>
       <c r="H47" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I47" t="n">
-        <v>0.174</v>
+        <v>0.188</v>
       </c>
       <c r="J47" t="n">
-        <v>0.749</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="48">
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.782</v>
+        <v>0.631</v>
       </c>
       <c r="F48" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>0.777</v>
+        <v>0.791</v>
       </c>
       <c r="H48" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I48" t="n">
-        <v>0.164</v>
+        <v>0.178</v>
       </c>
       <c r="J48" t="n">
-        <v>0.959</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="49">
@@ -2383,22 +2383,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.433</v>
+        <v>0.311</v>
       </c>
       <c r="F49" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>0.777</v>
+        <v>0.791</v>
       </c>
       <c r="H49" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I49" t="n">
-        <v>0.164</v>
+        <v>0.178</v>
       </c>
       <c r="J49" t="n">
-        <v>0.749</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="50">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.888</v>
+        <v>0.789</v>
       </c>
       <c r="F50" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>0.796</v>
+        <v>0.824</v>
       </c>
       <c r="H50" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I50" t="n">
-        <v>0.177</v>
+        <v>0.172</v>
       </c>
       <c r="J50" t="n">
-        <v>0.959</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="51">
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>0.796</v>
+        <v>0.824</v>
       </c>
       <c r="H51" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="I51" t="n">
-        <v>0.177</v>
+        <v>0.172</v>
       </c>
       <c r="J51" t="n">
-        <v>0.749</v>
+        <v>0.859</v>
       </c>
     </row>
     <row r="52">
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.723</v>
+        <v>0.861</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="H52" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I52" t="n">
-        <v>0.199</v>
+        <v>0.205</v>
       </c>
       <c r="J52" t="n">
-        <v>0.959</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="53">
@@ -2543,22 +2543,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.638</v>
+        <v>0.859</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="H53" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I53" t="n">
-        <v>0.199</v>
+        <v>0.205</v>
       </c>
       <c r="J53" t="n">
-        <v>0.749</v>
+        <v>0.859</v>
       </c>
     </row>
     <row r="54">
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.959</v>
+        <v>0.947</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="H54" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I54" t="n">
-        <v>0.197</v>
+        <v>0.204</v>
       </c>
       <c r="J54" t="n">
-        <v>0.959</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="55">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.674</v>
+        <v>0.838</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="H55" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I55" t="n">
-        <v>0.197</v>
+        <v>0.204</v>
       </c>
       <c r="J55" t="n">
-        <v>0.749</v>
+        <v>0.859</v>
       </c>
     </row>
     <row r="56">
@@ -2663,22 +2663,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0775</v>
+        <v>0.0555</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G56" t="n">
-        <v>0.769</v>
+        <v>0.782</v>
       </c>
       <c r="H56" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I56" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
-        <v>0.388</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="57">
@@ -2703,22 +2703,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0926</v>
+        <v>0.0506</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G57" t="n">
-        <v>0.769</v>
+        <v>0.782</v>
       </c>
       <c r="H57" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I57" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
-        <v>0.463</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="58">
@@ -2743,22 +2743,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.579</v>
+        <v>0.313</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="H58" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I58" t="n">
-        <v>0.203</v>
+        <v>0.21</v>
       </c>
       <c r="J58" t="n">
-        <v>0.959</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="59">
@@ -2783,22 +2783,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.779</v>
+        <v>0.441</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="H59" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I59" t="n">
-        <v>0.203</v>
+        <v>0.21</v>
       </c>
       <c r="J59" t="n">
-        <v>0.779</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="60">
@@ -2823,22 +2823,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00468</v>
+        <v>0.00442</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G60" t="n">
-        <v>0.637</v>
+        <v>0.651</v>
       </c>
       <c r="H60" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I60" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0468</v>
+        <v>0.0442</v>
       </c>
     </row>
     <row r="61">
@@ -2866,16 +2866,16 @@
         <v>0.00147</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G61" t="n">
-        <v>0.637</v>
+        <v>0.651</v>
       </c>
       <c r="H61" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I61" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="J61" t="n">
         <v>0.0147</v>
@@ -3013,7 +3013,7 @@
         <v>0.0105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0843</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="4">
@@ -3078,13 +3078,13 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.767</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.867</v>
+        <v>0.967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.506</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -3189,10 +3189,10 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -3300,13 +3300,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.533</v>
+        <v>0.7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.43</v>
+        <v>0.552</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -3340,10 +3340,10 @@
         <v>0.733</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -3485,16 +3485,16 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G16" t="n">
         <v>0.833</v>
       </c>
       <c r="H16" t="n">
-        <v>0.047</v>
+        <v>0.233</v>
       </c>
       <c r="I16" t="n">
-        <v>0.251</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -3522,16 +3522,16 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.333</v>
+        <v>0.433</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="H17" t="n">
-        <v>0.009209999999999999</v>
+        <v>0.0169</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0843</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="18">
@@ -3605,7 +3605,7 @@
         <v>0.0699</v>
       </c>
       <c r="I19" t="n">
-        <v>0.373</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3642,7 +3642,7 @@
         <v>0.25</v>
       </c>
       <c r="I20" t="n">
-        <v>0.823</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3670,13 +3670,13 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.667</v>
+        <v>0.875</v>
       </c>
       <c r="H21" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -3781,13 +3781,13 @@
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.773</v>
+        <v>0.783</v>
       </c>
       <c r="G24" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="H24" t="n">
-        <v>0.703</v>
+        <v>0.704</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -3892,16 +3892,16 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7</v>
+        <v>0.792</v>
       </c>
       <c r="G27" t="n">
-        <v>0.875</v>
+        <v>0.905</v>
       </c>
       <c r="H27" t="n">
-        <v>0.257</v>
+        <v>0.422</v>
       </c>
       <c r="I27" t="n">
-        <v>0.823</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3929,13 +3929,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.833</v>
+        <v>0.87</v>
       </c>
       <c r="G28" t="n">
         <v>0.895</v>
       </c>
       <c r="H28" t="n">
-        <v>0.678</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -4077,16 +4077,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.667</v>
+        <v>0.778</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0273</v>
+        <v>0.108</v>
       </c>
       <c r="I32" t="n">
-        <v>0.373</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="33">
@@ -4114,16 +4114,16 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.308</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.75</v>
+        <v>0.917</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0472</v>
+        <v>0.0557</v>
       </c>
       <c r="I33" t="n">
-        <v>0.373</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -4262,10 +4262,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -4373,10 +4373,10 @@
         <v>7</v>
       </c>
       <c r="F40" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="G40" t="n">
         <v>0.895</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.842</v>
       </c>
       <c r="H40" t="n">
         <v>1</v>
@@ -4484,10 +4484,10 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.636</v>
+        <v>0.826</v>
       </c>
       <c r="G43" t="n">
-        <v>0.636</v>
+        <v>0.826</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -4521,13 +4521,13 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G44" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="H44" t="n">
-        <v>0.494</v>
+        <v>0.52</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -4706,13 +4706,13 @@
         <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>0.267</v>
+        <v>0.294</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6</v>
+        <v>0.647</v>
       </c>
       <c r="H49" t="n">
-        <v>0.139</v>
+        <v>0.0844</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -4789,7 +4789,7 @@
         <v>0.0105</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0843</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="52">
@@ -4854,16 +4854,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>0.767</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9330000000000001</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.145</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.582</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -4894,10 +4894,10 @@
         <v>0.6</v>
       </c>
       <c r="G54" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0.789</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -4931,13 +4931,13 @@
         <v>0.9</v>
       </c>
       <c r="G55" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="H55" t="n">
-        <v>0.299</v>
+        <v>0.472</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6830000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -4965,10 +4965,10 @@
         <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
@@ -5076,16 +5076,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.533</v>
+        <v>0.7</v>
       </c>
       <c r="G59" t="n">
         <v>0.7</v>
       </c>
       <c r="H59" t="n">
-        <v>0.288</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6830000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5159,7 +5159,7 @@
         <v>0.254</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6830000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -5233,7 +5233,7 @@
         <v>0.424</v>
       </c>
       <c r="I63" t="n">
-        <v>0.848</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -5261,16 +5261,16 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G64" t="n">
         <v>0.833</v>
       </c>
       <c r="H64" t="n">
-        <v>0.047</v>
+        <v>0.233</v>
       </c>
       <c r="I64" t="n">
-        <v>0.251</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -5298,16 +5298,16 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.333</v>
+        <v>0.433</v>
       </c>
       <c r="G65" t="n">
         <v>0.733</v>
       </c>
       <c r="H65" t="n">
-        <v>0.00403</v>
+        <v>0.0352</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0644</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="66">
@@ -5344,7 +5344,7 @@
         <v>0.21</v>
       </c>
       <c r="I66" t="n">
-        <v>0.655</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="67">
@@ -5381,7 +5381,7 @@
         <v>0.0699</v>
       </c>
       <c r="I67" t="n">
-        <v>0.373</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5446,16 +5446,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.173</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.655</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -5486,7 +5486,7 @@
         <v>0.875</v>
       </c>
       <c r="G70" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
@@ -5523,13 +5523,13 @@
         <v>0.909</v>
       </c>
       <c r="G71" t="n">
-        <v>0.792</v>
+        <v>0.826</v>
       </c>
       <c r="H71" t="n">
-        <v>0.418</v>
+        <v>0.665</v>
       </c>
       <c r="I71" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -5557,10 +5557,10 @@
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.773</v>
+        <v>0.783</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H72" t="n">
         <v>1</v>
@@ -5668,16 +5668,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7</v>
+        <v>0.792</v>
       </c>
       <c r="G75" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="H75" t="n">
-        <v>0.246</v>
+        <v>0.679</v>
       </c>
       <c r="I75" t="n">
-        <v>0.655</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -5705,10 +5705,10 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.833</v>
+        <v>0.87</v>
       </c>
       <c r="G76" t="n">
-        <v>0.857</v>
+        <v>0.9</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -5853,16 +5853,16 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.667</v>
+        <v>0.778</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0273</v>
+        <v>0.108</v>
       </c>
       <c r="I80" t="n">
-        <v>0.218</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="81">
@@ -5890,16 +5890,16 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.308</v>
+        <v>0.5</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.909</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0188</v>
+        <v>0.0635</v>
       </c>
       <c r="I81" t="n">
-        <v>0.218</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -6038,10 +6038,10 @@
         <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>1</v>
@@ -6078,10 +6078,10 @@
         <v>0.583</v>
       </c>
       <c r="G86" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0.766</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
@@ -6149,10 +6149,10 @@
         <v>7</v>
       </c>
       <c r="F88" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="G88" t="n">
         <v>0.895</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0.842</v>
       </c>
       <c r="H88" t="n">
         <v>1</v>
@@ -6260,13 +6260,13 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.636</v>
+        <v>0.826</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>0.491</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -6297,13 +6297,13 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G92" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H92" t="n">
-        <v>0.724</v>
+        <v>0.742</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -6482,13 +6482,13 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.267</v>
+        <v>0.294</v>
       </c>
       <c r="G97" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
       <c r="H97" t="n">
-        <v>0.139</v>
+        <v>0.166</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -6528,7 +6528,7 @@
         <v>0.36</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -6565,7 +6565,7 @@
         <v>0.0523</v>
       </c>
       <c r="I99" t="n">
-        <v>0.209</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="100">
@@ -6630,16 +6630,16 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>0.767</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0523</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.209</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -6676,7 +6676,7 @@
         <v>0.589</v>
       </c>
       <c r="I102" t="n">
-        <v>0.962</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -6713,7 +6713,7 @@
         <v>0.472</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -6741,10 +6741,10 @@
         <v>7</v>
       </c>
       <c r="F104" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G104" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="H104" t="n">
         <v>1</v>
@@ -6852,16 +6852,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.533</v>
+        <v>0.7</v>
       </c>
       <c r="G107" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="H107" t="n">
-        <v>0.601</v>
+        <v>0.589</v>
       </c>
       <c r="I107" t="n">
-        <v>0.962</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -6892,10 +6892,10 @@
         <v>0.733</v>
       </c>
       <c r="G108" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -6935,7 +6935,7 @@
         <v>0.254</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8129999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -7009,7 +7009,7 @@
         <v>0.424</v>
       </c>
       <c r="I111" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -7037,16 +7037,16 @@
         <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G112" t="n">
         <v>0.9</v>
       </c>
       <c r="H112" t="n">
-        <v>0.00741</v>
+        <v>0.0575</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0736</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="113">
@@ -7074,16 +7074,16 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0.333</v>
+        <v>0.433</v>
       </c>
       <c r="G113" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="H113" t="n">
-        <v>0.009209999999999999</v>
+        <v>0.0352</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0736</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="114">
@@ -7157,7 +7157,7 @@
         <v>0.245</v>
       </c>
       <c r="I115" t="n">
-        <v>0.979</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -7222,16 +7222,16 @@
         <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0537</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.304</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -7333,10 +7333,10 @@
         <v>7</v>
       </c>
       <c r="F120" t="n">
-        <v>0.773</v>
+        <v>0.783</v>
       </c>
       <c r="G120" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H120" t="n">
         <v>1</v>
@@ -7444,13 +7444,13 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.7</v>
+        <v>0.792</v>
       </c>
       <c r="G123" t="n">
         <v>0.824</v>
       </c>
       <c r="H123" t="n">
-        <v>0.462</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -7481,13 +7481,13 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.833</v>
+        <v>0.87</v>
       </c>
       <c r="G124" t="n">
         <v>0.895</v>
       </c>
       <c r="H124" t="n">
-        <v>0.678</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -7629,16 +7629,16 @@
         <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>0.667</v>
+        <v>0.778</v>
       </c>
       <c r="G128" t="n">
         <v>0.947</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0461</v>
+        <v>0.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.304</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -7666,16 +7666,16 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.308</v>
+        <v>0.5</v>
       </c>
       <c r="G129" t="n">
-        <v>0.714</v>
+        <v>0.846</v>
       </c>
       <c r="H129" t="n">
-        <v>0.057</v>
+        <v>0.169</v>
       </c>
       <c r="I129" t="n">
-        <v>0.304</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -7814,10 +7814,10 @@
         <v>4</v>
       </c>
       <c r="F133" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
         <v>1</v>
@@ -7925,10 +7925,10 @@
         <v>7</v>
       </c>
       <c r="F136" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="G136" t="n">
         <v>0.895</v>
-      </c>
-      <c r="G136" t="n">
-        <v>0.842</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
@@ -8036,16 +8036,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.636</v>
+        <v>0.826</v>
       </c>
       <c r="G139" t="n">
-        <v>0.636</v>
+        <v>0.609</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0.189</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="140">
@@ -8073,13 +8073,13 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G140" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="H140" t="n">
-        <v>0.494</v>
+        <v>0.52</v>
       </c>
       <c r="I140" t="n">
         <v>1</v>
@@ -8119,7 +8119,7 @@
         <v>0.232</v>
       </c>
       <c r="I141" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="142">
@@ -8230,7 +8230,7 @@
         <v>0.235</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="145">
@@ -8258,16 +8258,16 @@
         <v>16</v>
       </c>
       <c r="F145" t="n">
-        <v>0.267</v>
+        <v>0.294</v>
       </c>
       <c r="G145" t="n">
-        <v>0.667</v>
+        <v>0.647</v>
       </c>
       <c r="H145" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0844</v>
       </c>
       <c r="I145" t="n">
-        <v>0.525</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="146">
@@ -8341,7 +8341,7 @@
         <v>0.299</v>
       </c>
       <c r="I147" t="n">
-        <v>0.957</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -8406,16 +8406,16 @@
         <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>0.767</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>0.0523</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.279</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -8452,7 +8452,7 @@
         <v>0.412</v>
       </c>
       <c r="I150" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -8489,7 +8489,7 @@
         <v>0.299</v>
       </c>
       <c r="I151" t="n">
-        <v>0.957</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -8517,10 +8517,10 @@
         <v>7</v>
       </c>
       <c r="F152" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G152" t="n">
-        <v>0.733</v>
+        <v>0.8</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -8628,13 +8628,13 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.533</v>
+        <v>0.7</v>
       </c>
       <c r="G155" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="H155" t="n">
-        <v>0.601</v>
+        <v>0.589</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
@@ -8668,10 +8668,10 @@
         <v>0.733</v>
       </c>
       <c r="G156" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I156" t="n">
         <v>1</v>
@@ -8711,7 +8711,7 @@
         <v>0.424</v>
       </c>
       <c r="I157" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -8813,16 +8813,16 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G160" t="n">
         <v>0.833</v>
       </c>
       <c r="H160" t="n">
-        <v>0.047</v>
+        <v>0.233</v>
       </c>
       <c r="I160" t="n">
-        <v>0.279</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -8850,16 +8850,16 @@
         <v>16</v>
       </c>
       <c r="F161" t="n">
-        <v>0.333</v>
+        <v>0.433</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="H161" t="n">
-        <v>0.000574</v>
+        <v>0.00278</v>
       </c>
       <c r="I161" t="n">
-        <v>0.009180000000000001</v>
+        <v>0.0445</v>
       </c>
     </row>
     <row r="162">
@@ -8998,16 +8998,16 @@
         <v>4</v>
       </c>
       <c r="F165" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0537</v>
+        <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -9109,10 +9109,10 @@
         <v>7</v>
       </c>
       <c r="F168" t="n">
-        <v>0.773</v>
+        <v>0.783</v>
       </c>
       <c r="G168" t="n">
-        <v>0.789</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H168" t="n">
         <v>1</v>
@@ -9220,13 +9220,13 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.7</v>
+        <v>0.792</v>
       </c>
       <c r="G171" t="n">
         <v>0.824</v>
       </c>
       <c r="H171" t="n">
-        <v>0.462</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
         <v>1</v>
@@ -9257,13 +9257,13 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.833</v>
+        <v>0.87</v>
       </c>
       <c r="G172" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="H172" t="n">
-        <v>0.382</v>
+        <v>0.624</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
@@ -9405,16 +9405,16 @@
         <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>0.667</v>
+        <v>0.778</v>
       </c>
       <c r="G176" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="H176" t="n">
-        <v>0.0534</v>
+        <v>0.338</v>
       </c>
       <c r="I176" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -9442,16 +9442,16 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.308</v>
+        <v>0.5</v>
       </c>
       <c r="G177" t="n">
-        <v>0.8</v>
+        <v>0.875</v>
       </c>
       <c r="H177" t="n">
-        <v>0.02</v>
+        <v>0.0687</v>
       </c>
       <c r="I177" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -9590,10 +9590,10 @@
         <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
         <v>1</v>
@@ -9701,13 +9701,13 @@
         <v>7</v>
       </c>
       <c r="F184" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="G184" t="n">
         <v>0.895</v>
       </c>
-      <c r="G184" t="n">
-        <v>0.789</v>
-      </c>
       <c r="H184" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
         <v>1</v>
@@ -9812,13 +9812,13 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.636</v>
+        <v>0.826</v>
       </c>
       <c r="G187" t="n">
-        <v>0.636</v>
+        <v>0.609</v>
       </c>
       <c r="H187" t="n">
-        <v>1</v>
+        <v>0.189</v>
       </c>
       <c r="I187" t="n">
         <v>1</v>
@@ -9849,13 +9849,13 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.667</v>
+        <v>0.64</v>
       </c>
       <c r="H188" t="n">
-        <v>0.318</v>
+        <v>0.345</v>
       </c>
       <c r="I188" t="n">
         <v>1</v>
@@ -10034,16 +10034,16 @@
         <v>16</v>
       </c>
       <c r="F193" t="n">
-        <v>0.267</v>
+        <v>0.294</v>
       </c>
       <c r="G193" t="n">
-        <v>0.8</v>
+        <v>0.824</v>
       </c>
       <c r="H193" t="n">
-        <v>0.009220000000000001</v>
+        <v>0.0049</v>
       </c>
       <c r="I193" t="n">
-        <v>0.148</v>
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -10117,7 +10117,7 @@
         <v>0.0523</v>
       </c>
       <c r="I195" t="n">
-        <v>0.837</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="196">
@@ -10182,13 +10182,13 @@
         <v>4</v>
       </c>
       <c r="F197" t="n">
-        <v>0.767</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="H197" t="n">
-        <v>0.748</v>
+        <v>1</v>
       </c>
       <c r="I197" t="n">
         <v>1</v>
@@ -10222,7 +10222,7 @@
         <v>0.6</v>
       </c>
       <c r="G198" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -10293,13 +10293,13 @@
         <v>7</v>
       </c>
       <c r="F200" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="G200" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="H200" t="n">
-        <v>1</v>
+        <v>0.731</v>
       </c>
       <c r="I200" t="n">
         <v>1</v>
@@ -10376,7 +10376,7 @@
         <v>0.145</v>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="203">
@@ -10404,13 +10404,13 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.533</v>
+        <v>0.7</v>
       </c>
       <c r="G203" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="H203" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="I203" t="n">
         <v>1</v>
@@ -10589,13 +10589,13 @@
         <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="G208" t="n">
-        <v>0.633</v>
+        <v>0.8</v>
       </c>
       <c r="H208" t="n">
-        <v>0.792</v>
+        <v>0.382</v>
       </c>
       <c r="I208" t="n">
         <v>1</v>
@@ -10626,16 +10626,16 @@
         <v>16</v>
       </c>
       <c r="F209" t="n">
-        <v>0.333</v>
+        <v>0.433</v>
       </c>
       <c r="G209" t="n">
-        <v>0.533</v>
+        <v>0.7</v>
       </c>
       <c r="H209" t="n">
-        <v>0.192</v>
+        <v>0.0673</v>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="210">
@@ -10774,13 +10774,13 @@
         <v>4</v>
       </c>
       <c r="F213" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G213" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H213" t="n">
-        <v>0.6909999999999999</v>
+        <v>1</v>
       </c>
       <c r="I213" t="n">
         <v>1</v>
@@ -10814,7 +10814,7 @@
         <v>0.875</v>
       </c>
       <c r="G214" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="H214" t="n">
         <v>1</v>
@@ -10885,13 +10885,13 @@
         <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>0.773</v>
+        <v>0.783</v>
       </c>
       <c r="G216" t="n">
-        <v>0.842</v>
+        <v>0.895</v>
       </c>
       <c r="H216" t="n">
-        <v>0.703</v>
+        <v>0.428</v>
       </c>
       <c r="I216" t="n">
         <v>1</v>
@@ -10996,10 +10996,10 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.7</v>
+        <v>0.792</v>
       </c>
       <c r="G219" t="n">
-        <v>0.929</v>
+        <v>0.95</v>
       </c>
       <c r="H219" t="n">
         <v>0.198</v>
@@ -11033,13 +11033,13 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.833</v>
+        <v>0.87</v>
       </c>
       <c r="G220" t="n">
-        <v>0.895</v>
+        <v>0.9</v>
       </c>
       <c r="H220" t="n">
-        <v>0.678</v>
+        <v>1</v>
       </c>
       <c r="I220" t="n">
         <v>1</v>
@@ -11181,13 +11181,13 @@
         <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>0.667</v>
+        <v>0.778</v>
       </c>
       <c r="G224" t="n">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
       <c r="H224" t="n">
-        <v>1</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I224" t="n">
         <v>1</v>
@@ -11218,13 +11218,13 @@
         <v>16</v>
       </c>
       <c r="F225" t="n">
-        <v>0.308</v>
+        <v>0.5</v>
       </c>
       <c r="G225" t="n">
-        <v>0.522</v>
+        <v>0.722</v>
       </c>
       <c r="H225" t="n">
-        <v>0.301</v>
+        <v>0.412</v>
       </c>
       <c r="I225" t="n">
         <v>1</v>
@@ -11366,10 +11366,10 @@
         <v>4</v>
       </c>
       <c r="F229" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G229" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H229" t="n">
         <v>1</v>
@@ -11406,7 +11406,7 @@
         <v>0.583</v>
       </c>
       <c r="G230" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="H230" t="n">
         <v>1</v>
@@ -11477,10 +11477,10 @@
         <v>7</v>
       </c>
       <c r="F232" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="G232" t="n">
         <v>0.895</v>
-      </c>
-      <c r="G232" t="n">
-        <v>0.842</v>
       </c>
       <c r="H232" t="n">
         <v>1</v>
@@ -11588,10 +11588,10 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.636</v>
+        <v>0.826</v>
       </c>
       <c r="G235" t="n">
-        <v>0.591</v>
+        <v>0.826</v>
       </c>
       <c r="H235" t="n">
         <v>1</v>
@@ -11625,13 +11625,13 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="G236" t="n">
-        <v>0.708</v>
+        <v>0.72</v>
       </c>
       <c r="H236" t="n">
-        <v>0.494</v>
+        <v>0.742</v>
       </c>
       <c r="I236" t="n">
         <v>1</v>
@@ -11810,16 +11810,16 @@
         <v>16</v>
       </c>
       <c r="F241" t="n">
-        <v>0.267</v>
+        <v>0.294</v>
       </c>
       <c r="G241" t="n">
-        <v>0.8</v>
+        <v>0.765</v>
       </c>
       <c r="H241" t="n">
-        <v>0.009220000000000001</v>
+        <v>0.0149</v>
       </c>
       <c r="I241" t="n">
-        <v>0.148</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="242">
@@ -11958,10 +11958,10 @@
         <v>4</v>
       </c>
       <c r="F245" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
         <v>1</v>
@@ -12069,10 +12069,10 @@
         <v>7</v>
       </c>
       <c r="F248" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G248" t="n">
-        <v>0.767</v>
+        <v>0.867</v>
       </c>
       <c r="H248" t="n">
         <v>1</v>
@@ -12217,13 +12217,13 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="G252" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="H252" t="n">
-        <v>0.771</v>
+        <v>0.779</v>
       </c>
       <c r="I252" t="n">
         <v>1</v>
@@ -12405,10 +12405,10 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G257" t="n">
-        <v>0.433</v>
+        <v>0.5</v>
       </c>
       <c r="H257" t="n">
-        <v>0.439</v>
+        <v>0.796</v>
       </c>
       <c r="I257" t="n">
         <v>1</v>
@@ -12661,10 +12661,10 @@
         <v>7</v>
       </c>
       <c r="F264" t="n">
-        <v>0.842</v>
+        <v>0.864</v>
       </c>
       <c r="G264" t="n">
-        <v>0.875</v>
+        <v>0.895</v>
       </c>
       <c r="H264" t="n">
         <v>1</v>
@@ -12775,7 +12775,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.947</v>
+        <v>0.95</v>
       </c>
       <c r="H267" t="n">
         <v>1</v>
@@ -12994,13 +12994,13 @@
         <v>16</v>
       </c>
       <c r="F273" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="G273" t="n">
-        <v>0.462</v>
+        <v>0.538</v>
       </c>
       <c r="H273" t="n">
-        <v>0.778</v>
+        <v>0.783</v>
       </c>
       <c r="I273" t="n">
         <v>1</v>
@@ -13142,10 +13142,10 @@
         <v>4</v>
       </c>
       <c r="F277" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H277" t="n">
         <v>1</v>
@@ -13253,13 +13253,13 @@
         <v>7</v>
       </c>
       <c r="F280" t="n">
-        <v>0.842</v>
+        <v>1</v>
       </c>
       <c r="G280" t="n">
-        <v>0.737</v>
+        <v>0.895</v>
       </c>
       <c r="H280" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.486</v>
       </c>
       <c r="I280" t="n">
         <v>1</v>
@@ -13364,13 +13364,13 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.727</v>
+        <v>0.739</v>
       </c>
       <c r="G283" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="H283" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="I283" t="n">
         <v>1</v>
@@ -13401,13 +13401,13 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="G284" t="n">
-        <v>0.792</v>
+        <v>0.76</v>
       </c>
       <c r="H284" t="n">
-        <v>0.74</v>
+        <v>0.754</v>
       </c>
       <c r="I284" t="n">
         <v>1</v>
@@ -13586,10 +13586,10 @@
         <v>16</v>
       </c>
       <c r="F289" t="n">
-        <v>0.867</v>
+        <v>0.824</v>
       </c>
       <c r="G289" t="n">
-        <v>0.8</v>
+        <v>0.824</v>
       </c>
       <c r="H289" t="n">
         <v>1</v>
@@ -13734,10 +13734,10 @@
         <v>4</v>
       </c>
       <c r="F293" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="H293" t="n">
         <v>1</v>
@@ -13845,10 +13845,10 @@
         <v>7</v>
       </c>
       <c r="F296" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G296" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13959,10 +13959,10 @@
         <v>0.8</v>
       </c>
       <c r="G299" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="H299" t="n">
-        <v>0.552</v>
+        <v>0.761</v>
       </c>
       <c r="I299" t="n">
         <v>1</v>
@@ -13993,10 +13993,10 @@
         <v>11</v>
       </c>
       <c r="F300" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G300" t="n">
         <v>0.7</v>
-      </c>
-      <c r="G300" t="n">
-        <v>0.733</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -14181,10 +14181,10 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G305" t="n">
-        <v>0.467</v>
+        <v>0.533</v>
       </c>
       <c r="H305" t="n">
-        <v>0.606</v>
+        <v>1</v>
       </c>
       <c r="I305" t="n">
         <v>1</v>
@@ -14437,10 +14437,10 @@
         <v>7</v>
       </c>
       <c r="F312" t="n">
-        <v>0.842</v>
+        <v>0.864</v>
       </c>
       <c r="G312" t="n">
-        <v>0.85</v>
+        <v>0.857</v>
       </c>
       <c r="H312" t="n">
         <v>1</v>
@@ -14551,10 +14551,10 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0.842</v>
+        <v>0.857</v>
       </c>
       <c r="H315" t="n">
-        <v>0.234</v>
+        <v>0.238</v>
       </c>
       <c r="I315" t="n">
         <v>1</v>
@@ -14770,13 +14770,13 @@
         <v>16</v>
       </c>
       <c r="F321" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="G321" t="n">
-        <v>0.481</v>
+        <v>0.556</v>
       </c>
       <c r="H321" t="n">
-        <v>0.781</v>
+        <v>1</v>
       </c>
       <c r="I321" t="n">
         <v>1</v>
@@ -14918,10 +14918,10 @@
         <v>4</v>
       </c>
       <c r="F325" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G325" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H325" t="n">
         <v>1</v>
@@ -15029,10 +15029,10 @@
         <v>7</v>
       </c>
       <c r="F328" t="n">
-        <v>0.842</v>
+        <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.895</v>
+        <v>0.947</v>
       </c>
       <c r="H328" t="n">
         <v>1</v>
@@ -15140,10 +15140,10 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
-        <v>0.727</v>
+        <v>0.739</v>
       </c>
       <c r="G331" t="n">
-        <v>0.727</v>
+        <v>0.783</v>
       </c>
       <c r="H331" t="n">
         <v>1</v>
@@ -15177,10 +15177,10 @@
         <v>11</v>
       </c>
       <c r="F332" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="G332" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H332" t="n">
         <v>1</v>
@@ -15362,10 +15362,10 @@
         <v>16</v>
       </c>
       <c r="F337" t="n">
-        <v>0.867</v>
+        <v>0.824</v>
       </c>
       <c r="G337" t="n">
-        <v>0.867</v>
+        <v>0.882</v>
       </c>
       <c r="H337" t="n">
         <v>1</v>
@@ -15510,10 +15510,10 @@
         <v>4</v>
       </c>
       <c r="F341" t="n">
+        <v>1</v>
+      </c>
+      <c r="G341" t="n">
         <v>0.967</v>
-      </c>
-      <c r="G341" t="n">
-        <v>0.9330000000000001</v>
       </c>
       <c r="H341" t="n">
         <v>1</v>
@@ -15621,10 +15621,10 @@
         <v>7</v>
       </c>
       <c r="F344" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G344" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H344" t="n">
         <v>1</v>
@@ -15769,10 +15769,10 @@
         <v>11</v>
       </c>
       <c r="F348" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="G348" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -15957,10 +15957,10 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G353" t="n">
-        <v>0.467</v>
+        <v>0.533</v>
       </c>
       <c r="H353" t="n">
-        <v>0.606</v>
+        <v>1</v>
       </c>
       <c r="I353" t="n">
         <v>1</v>
@@ -16213,10 +16213,10 @@
         <v>7</v>
       </c>
       <c r="F360" t="n">
-        <v>0.842</v>
+        <v>0.864</v>
       </c>
       <c r="G360" t="n">
-        <v>0.85</v>
+        <v>0.857</v>
       </c>
       <c r="H360" t="n">
         <v>1</v>
@@ -16327,7 +16327,7 @@
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0.857</v>
+        <v>0.864</v>
       </c>
       <c r="H363" t="n">
         <v>0.243</v>
@@ -16546,13 +16546,13 @@
         <v>16</v>
       </c>
       <c r="F369" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="G369" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H369" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="I369" t="n">
         <v>1</v>
@@ -16694,10 +16694,10 @@
         <v>4</v>
       </c>
       <c r="F373" t="n">
+        <v>1</v>
+      </c>
+      <c r="G373" t="n">
         <v>0.857</v>
-      </c>
-      <c r="G373" t="n">
-        <v>0.714</v>
       </c>
       <c r="H373" t="n">
         <v>1</v>
@@ -16805,10 +16805,10 @@
         <v>7</v>
       </c>
       <c r="F376" t="n">
-        <v>0.842</v>
+        <v>1</v>
       </c>
       <c r="G376" t="n">
-        <v>0.895</v>
+        <v>0.947</v>
       </c>
       <c r="H376" t="n">
         <v>1</v>
@@ -16916,13 +16916,13 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.727</v>
+        <v>0.739</v>
       </c>
       <c r="G379" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="H379" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="I379" t="n">
         <v>1</v>
@@ -16953,10 +16953,10 @@
         <v>11</v>
       </c>
       <c r="F380" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="G380" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="H380" t="n">
         <v>1</v>
@@ -17138,10 +17138,10 @@
         <v>16</v>
       </c>
       <c r="F385" t="n">
-        <v>0.867</v>
+        <v>0.824</v>
       </c>
       <c r="G385" t="n">
-        <v>0.8</v>
+        <v>0.824</v>
       </c>
       <c r="H385" t="n">
         <v>1</v>
@@ -17286,10 +17286,10 @@
         <v>4</v>
       </c>
       <c r="F389" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="H389" t="n">
         <v>1</v>
@@ -17397,13 +17397,13 @@
         <v>7</v>
       </c>
       <c r="F392" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G392" t="n">
         <v>0.833</v>
       </c>
       <c r="H392" t="n">
-        <v>1</v>
+        <v>0.706</v>
       </c>
       <c r="I392" t="n">
         <v>1</v>
@@ -17545,10 +17545,10 @@
         <v>11</v>
       </c>
       <c r="F396" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="G396" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="H396" t="n">
         <v>1</v>
@@ -17733,10 +17733,10 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G401" t="n">
-        <v>0.433</v>
+        <v>0.5</v>
       </c>
       <c r="H401" t="n">
-        <v>0.439</v>
+        <v>0.796</v>
       </c>
       <c r="I401" t="n">
         <v>1</v>
@@ -17989,7 +17989,7 @@
         <v>7</v>
       </c>
       <c r="F408" t="n">
-        <v>0.842</v>
+        <v>0.864</v>
       </c>
       <c r="G408" t="n">
         <v>0.85</v>
@@ -18103,7 +18103,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.944</v>
+        <v>0.947</v>
       </c>
       <c r="H411" t="n">
         <v>1</v>
@@ -18322,13 +18322,13 @@
         <v>16</v>
       </c>
       <c r="F417" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="G417" t="n">
-        <v>0.464</v>
+        <v>0.536</v>
       </c>
       <c r="H417" t="n">
-        <v>0.781</v>
+        <v>0.785</v>
       </c>
       <c r="I417" t="n">
         <v>1</v>
@@ -18470,10 +18470,10 @@
         <v>4</v>
       </c>
       <c r="F421" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G421" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H421" t="n">
         <v>1</v>
@@ -18581,13 +18581,13 @@
         <v>7</v>
       </c>
       <c r="F424" t="n">
-        <v>0.842</v>
+        <v>1</v>
       </c>
       <c r="G424" t="n">
         <v>0.895</v>
       </c>
       <c r="H424" t="n">
-        <v>1</v>
+        <v>0.486</v>
       </c>
       <c r="I424" t="n">
         <v>1</v>
@@ -18692,10 +18692,10 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.727</v>
+        <v>0.739</v>
       </c>
       <c r="G427" t="n">
-        <v>0.773</v>
+        <v>0.783</v>
       </c>
       <c r="H427" t="n">
         <v>1</v>
@@ -18729,10 +18729,10 @@
         <v>11</v>
       </c>
       <c r="F428" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="G428" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="H428" t="n">
         <v>1</v>
@@ -18914,10 +18914,10 @@
         <v>16</v>
       </c>
       <c r="F433" t="n">
-        <v>0.867</v>
+        <v>0.824</v>
       </c>
       <c r="G433" t="n">
-        <v>0.867</v>
+        <v>0.882</v>
       </c>
       <c r="H433" t="n">
         <v>1</v>
@@ -19062,13 +19062,13 @@
         <v>4</v>
       </c>
       <c r="F437" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H437" t="n">
-        <v>0.612</v>
+        <v>0.492</v>
       </c>
       <c r="I437" t="n">
         <v>1</v>
@@ -19173,13 +19173,13 @@
         <v>7</v>
       </c>
       <c r="F440" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G440" t="n">
         <v>0.8</v>
       </c>
-      <c r="G440" t="n">
-        <v>0.767</v>
-      </c>
       <c r="H440" t="n">
-        <v>1</v>
+        <v>0.472</v>
       </c>
       <c r="I440" t="n">
         <v>1</v>
@@ -19321,13 +19321,13 @@
         <v>11</v>
       </c>
       <c r="F444" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="G444" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="H444" t="n">
-        <v>0.785</v>
+        <v>0.789</v>
       </c>
       <c r="I444" t="n">
         <v>1</v>
@@ -19509,10 +19509,10 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G449" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="H449" t="n">
-        <v>1</v>
+        <v>0.596</v>
       </c>
       <c r="I449" t="n">
         <v>1</v>
@@ -19765,10 +19765,10 @@
         <v>7</v>
       </c>
       <c r="F456" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="G456" t="n">
         <v>0.842</v>
-      </c>
-      <c r="G456" t="n">
-        <v>0.833</v>
       </c>
       <c r="H456" t="n">
         <v>1</v>
@@ -20098,13 +20098,13 @@
         <v>16</v>
       </c>
       <c r="F465" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="G465" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="H465" t="n">
         <v>0.542</v>
-      </c>
-      <c r="G465" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="H465" t="n">
-        <v>1</v>
       </c>
       <c r="I465" t="n">
         <v>1</v>
@@ -20144,7 +20144,7 @@
         <v>0.348</v>
       </c>
       <c r="I466" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="467">
@@ -20181,7 +20181,7 @@
         <v>0.4</v>
       </c>
       <c r="I467" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="468">
@@ -20246,16 +20246,16 @@
         <v>4</v>
       </c>
       <c r="F469" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>0.571</v>
+        <v>0.714</v>
       </c>
       <c r="H469" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.462</v>
       </c>
       <c r="I469" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="470">
@@ -20357,16 +20357,16 @@
         <v>7</v>
       </c>
       <c r="F472" t="n">
+        <v>1</v>
+      </c>
+      <c r="G472" t="n">
         <v>0.842</v>
       </c>
-      <c r="G472" t="n">
-        <v>0.789</v>
-      </c>
       <c r="H472" t="n">
-        <v>1</v>
+        <v>0.23</v>
       </c>
       <c r="I472" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="473">
@@ -20440,7 +20440,7 @@
         <v>0.158</v>
       </c>
       <c r="I474" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="475">
@@ -20468,16 +20468,16 @@
         <v>10</v>
       </c>
       <c r="F475" t="n">
-        <v>0.727</v>
+        <v>0.739</v>
       </c>
       <c r="G475" t="n">
-        <v>0.591</v>
+        <v>0.609</v>
       </c>
       <c r="H475" t="n">
-        <v>0.526</v>
+        <v>0.53</v>
       </c>
       <c r="I475" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="476">
@@ -20505,16 +20505,16 @@
         <v>11</v>
       </c>
       <c r="F476" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="G476" t="n">
-        <v>0.583</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H476" t="n">
-        <v>0.547</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I476" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="477">
@@ -20625,7 +20625,7 @@
         <v>0.407</v>
       </c>
       <c r="I479" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="480">
@@ -20690,13 +20690,13 @@
         <v>16</v>
       </c>
       <c r="F481" t="n">
-        <v>0.867</v>
+        <v>0.824</v>
       </c>
       <c r="G481" t="n">
-        <v>0.733</v>
+        <v>0.765</v>
       </c>
       <c r="H481" t="n">
-        <v>0.651</v>
+        <v>1</v>
       </c>
       <c r="I481" t="n">
         <v>1</v>

--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.106</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.85</v>
+        <v>0.852</v>
       </c>
       <c r="H2" t="n">
         <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0852</v>
+        <v>0.0843</v>
       </c>
       <c r="J2" t="n">
-        <v>0.212</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.85</v>
+        <v>0.852</v>
       </c>
       <c r="H3" t="n">
         <v>0.15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0852</v>
+        <v>0.0843</v>
       </c>
       <c r="J3" t="n">
         <v>0.454</v>
@@ -638,7 +638,7 @@
         <v>0.105</v>
       </c>
       <c r="J5" t="n">
-        <v>0.624</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="6">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.63</v>
+        <v>0.584</v>
       </c>
       <c r="F8" t="n">
         <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H8" t="n">
         <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.106</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="9">
@@ -789,13 +789,13 @@
         <v>0.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H9" t="n">
         <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.106</v>
       </c>
       <c r="J9" t="n">
         <v>0.903</v>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="F10" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.848</v>
+        <v>0.85</v>
       </c>
       <c r="H10" t="n">
         <v>0.15</v>
@@ -838,7 +838,7 @@
         <v>0.107</v>
       </c>
       <c r="J10" t="n">
-        <v>0.189</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="11">
@@ -869,7 +869,7 @@
         <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.848</v>
+        <v>0.85</v>
       </c>
       <c r="H11" t="n">
         <v>0.15</v>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.572</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.804</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>0.125</v>
       </c>
       <c r="I12" t="n">
-        <v>0.137</v>
+        <v>0.139</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.499</v>
+        <v>0.62</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.804</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>0.125</v>
       </c>
       <c r="I13" t="n">
-        <v>0.137</v>
+        <v>0.139</v>
       </c>
       <c r="J13" t="n">
-        <v>0.624</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="14">
@@ -986,16 +986,16 @@
         <v>0.401</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.802</v>
+        <v>0.804</v>
       </c>
       <c r="H14" t="n">
         <v>0.125</v>
       </c>
       <c r="I14" t="n">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="J14" t="n">
         <v>0.573</v>
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.327</v>
+        <v>0.377</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.802</v>
+        <v>0.804</v>
       </c>
       <c r="H15" t="n">
         <v>0.125</v>
       </c>
       <c r="I15" t="n">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="J15" t="n">
-        <v>0.545</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="16">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.008970000000000001</v>
+        <v>0.00725</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>0.787</v>
@@ -1078,7 +1078,7 @@
         <v>0.142</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0449</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="17">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0119</v>
+        <v>0.011</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0.787</v>
@@ -1118,7 +1118,7 @@
         <v>0.142</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0595</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="18">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0057</v>
+        <v>0.0028</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>0.788</v>
@@ -1158,7 +1158,7 @@
         <v>0.144</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0449</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="19">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0106</v>
+        <v>0.00661</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.788</v>
@@ -1198,7 +1198,7 @@
         <v>0.144</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0595</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="20">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0506</v>
+        <v>0.0461</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0.771</v>
@@ -1238,7 +1238,7 @@
         <v>0.111</v>
       </c>
       <c r="J20" t="n">
-        <v>0.169</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="21">
@@ -1266,7 +1266,7 @@
         <v>0.047</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0.771</v>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.152</v>
+        <v>0.151</v>
       </c>
       <c r="F22" t="n">
         <v>0.8129999999999999</v>
@@ -1318,7 +1318,7 @@
         <v>0.123</v>
       </c>
       <c r="J22" t="n">
-        <v>0.253</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="23">
@@ -1543,19 +1543,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0217</v>
+        <v>0.0206</v>
       </c>
       <c r="F28" t="n">
         <v>0.8129999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.889</v>
+        <v>0.89</v>
       </c>
       <c r="H28" t="n">
         <v>0.199</v>
       </c>
       <c r="I28" t="n">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="J28" t="n">
         <v>0.127</v>
@@ -1589,13 +1589,13 @@
         <v>0.8129999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.889</v>
+        <v>0.89</v>
       </c>
       <c r="H29" t="n">
         <v>0.199</v>
       </c>
       <c r="I29" t="n">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="J29" t="n">
         <v>0.102</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0424</v>
+        <v>0.0421</v>
       </c>
       <c r="F30" t="n">
         <v>0.8129999999999999</v>
@@ -1638,7 +1638,7 @@
         <v>0.111</v>
       </c>
       <c r="J30" t="n">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="31">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.322</v>
+        <v>0.328</v>
       </c>
       <c r="F32" t="n">
         <v>0.857</v>
@@ -1718,7 +1718,7 @@
         <v>0.163</v>
       </c>
       <c r="J32" t="n">
-        <v>0.409</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="33">
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.368</v>
+        <v>0.375</v>
       </c>
       <c r="F34" t="n">
         <v>0.857</v>
       </c>
       <c r="G34" t="n">
-        <v>0.84</v>
+        <v>0.841</v>
       </c>
       <c r="H34" t="n">
         <v>0.123</v>
@@ -1798,7 +1798,7 @@
         <v>0.149</v>
       </c>
       <c r="J34" t="n">
-        <v>0.409</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="35">
@@ -1829,7 +1829,7 @@
         <v>0.857</v>
       </c>
       <c r="G35" t="n">
-        <v>0.84</v>
+        <v>0.841</v>
       </c>
       <c r="H35" t="n">
         <v>0.123</v>
@@ -1878,7 +1878,7 @@
         <v>0.135</v>
       </c>
       <c r="J36" t="n">
-        <v>0.409</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>0.149</v>
       </c>
       <c r="J38" t="n">
-        <v>0.253</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="39">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="F42" t="n">
         <v>0.8139999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>0.838</v>
+        <v>0.841</v>
       </c>
       <c r="H42" t="n">
         <v>0.205</v>
       </c>
       <c r="I42" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="J42" t="n">
         <v>0.828</v>
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.515</v>
+        <v>0.445</v>
       </c>
       <c r="F43" t="n">
         <v>0.8139999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>0.838</v>
+        <v>0.841</v>
       </c>
       <c r="H43" t="n">
         <v>0.205</v>
       </c>
       <c r="I43" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="J43" t="n">
-        <v>0.736</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="44">
@@ -2238,7 +2238,7 @@
         <v>0.184</v>
       </c>
       <c r="J45" t="n">
-        <v>0.735</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="46">
@@ -2318,7 +2318,7 @@
         <v>0.188</v>
       </c>
       <c r="J47" t="n">
-        <v>0.735</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="48">
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.631</v>
+        <v>0.667</v>
       </c>
       <c r="F48" t="n">
         <v>0.8139999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="H48" t="n">
         <v>0.205</v>
       </c>
       <c r="I48" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="J48" t="n">
-        <v>0.901</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="49">
@@ -2389,16 +2389,16 @@
         <v>0.8139999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="H49" t="n">
         <v>0.205</v>
       </c>
       <c r="I49" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="J49" t="n">
-        <v>0.735</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="50">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.789</v>
+        <v>0.736</v>
       </c>
       <c r="F50" t="n">
         <v>0.8139999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>0.824</v>
+        <v>0.827</v>
       </c>
       <c r="H50" t="n">
         <v>0.205</v>
@@ -2438,7 +2438,7 @@
         <v>0.172</v>
       </c>
       <c r="J50" t="n">
-        <v>0.947</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="51">
@@ -2463,13 +2463,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="F51" t="n">
         <v>0.8139999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>0.824</v>
+        <v>0.827</v>
       </c>
       <c r="H51" t="n">
         <v>0.205</v>
@@ -2478,7 +2478,7 @@
         <v>0.172</v>
       </c>
       <c r="J51" t="n">
-        <v>0.859</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="52">
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.861</v>
+        <v>0.973</v>
       </c>
       <c r="F52" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G52" t="n">
-        <v>0.826</v>
+        <v>0.832</v>
       </c>
       <c r="H52" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I52" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="J52" t="n">
-        <v>0.947</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="53">
@@ -2543,22 +2543,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.859</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G53" t="n">
-        <v>0.826</v>
+        <v>0.832</v>
       </c>
       <c r="H53" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I53" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="J53" t="n">
-        <v>0.859</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2586,19 +2586,19 @@
         <v>0.947</v>
       </c>
       <c r="F54" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G54" t="n">
-        <v>0.829</v>
+        <v>0.831</v>
       </c>
       <c r="H54" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I54" t="n">
-        <v>0.204</v>
+        <v>0.203</v>
       </c>
       <c r="J54" t="n">
-        <v>0.947</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="55">
@@ -2626,19 +2626,19 @@
         <v>0.838</v>
       </c>
       <c r="F55" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G55" t="n">
-        <v>0.829</v>
+        <v>0.831</v>
       </c>
       <c r="H55" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I55" t="n">
-        <v>0.204</v>
+        <v>0.203</v>
       </c>
       <c r="J55" t="n">
-        <v>0.859</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="56">
@@ -2663,22 +2663,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0555</v>
+        <v>0.0374</v>
       </c>
       <c r="F56" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G56" t="n">
         <v>0.782</v>
       </c>
       <c r="H56" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I56" t="n">
         <v>0.2</v>
       </c>
       <c r="J56" t="n">
-        <v>0.278</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="57">
@@ -2703,22 +2703,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0506</v>
+        <v>0.0152</v>
       </c>
       <c r="F57" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G57" t="n">
         <v>0.782</v>
       </c>
       <c r="H57" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I57" t="n">
         <v>0.2</v>
       </c>
       <c r="J57" t="n">
-        <v>0.253</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="58">
@@ -2743,22 +2743,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.313</v>
+        <v>0.189</v>
       </c>
       <c r="F58" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G58" t="n">
         <v>0.819</v>
       </c>
       <c r="H58" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I58" t="n">
         <v>0.21</v>
       </c>
       <c r="J58" t="n">
-        <v>0.828</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="59">
@@ -2783,22 +2783,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.441</v>
+        <v>0.327</v>
       </c>
       <c r="F59" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G59" t="n">
         <v>0.819</v>
       </c>
       <c r="H59" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I59" t="n">
         <v>0.21</v>
       </c>
       <c r="J59" t="n">
-        <v>0.735</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="60">
@@ -2823,22 +2823,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00442</v>
+        <v>0.00393</v>
       </c>
       <c r="F60" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G60" t="n">
         <v>0.651</v>
       </c>
       <c r="H60" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I60" t="n">
         <v>0.226</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0442</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="61">
@@ -2866,13 +2866,13 @@
         <v>0.00147</v>
       </c>
       <c r="F61" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G61" t="n">
         <v>0.651</v>
       </c>
       <c r="H61" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I61" t="n">
         <v>0.226</v>
@@ -3303,10 +3303,10 @@
         <v>0.7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="H11" t="n">
-        <v>0.552</v>
+        <v>0.36</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -3895,10 +3895,10 @@
         <v>0.792</v>
       </c>
       <c r="G27" t="n">
-        <v>0.905</v>
+        <v>0.909</v>
       </c>
       <c r="H27" t="n">
-        <v>0.422</v>
+        <v>0.418</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -4487,7 +4487,7 @@
         <v>0.826</v>
       </c>
       <c r="G43" t="n">
-        <v>0.826</v>
+        <v>0.87</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -8631,10 +8631,10 @@
         <v>0.7</v>
       </c>
       <c r="G155" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="H155" t="n">
-        <v>0.589</v>
+        <v>0.785</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
@@ -9223,7 +9223,7 @@
         <v>0.792</v>
       </c>
       <c r="G171" t="n">
-        <v>0.824</v>
+        <v>0.833</v>
       </c>
       <c r="H171" t="n">
         <v>1</v>
@@ -9815,10 +9815,10 @@
         <v>0.826</v>
       </c>
       <c r="G187" t="n">
-        <v>0.609</v>
+        <v>0.652</v>
       </c>
       <c r="H187" t="n">
-        <v>0.189</v>
+        <v>0.314</v>
       </c>
       <c r="I187" t="n">
         <v>1</v>
@@ -10407,13 +10407,13 @@
         <v>0.7</v>
       </c>
       <c r="G203" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H203" t="n">
-        <v>0.36</v>
+        <v>0.209</v>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="204">
@@ -10999,10 +10999,10 @@
         <v>0.792</v>
       </c>
       <c r="G219" t="n">
-        <v>0.95</v>
+        <v>0.952</v>
       </c>
       <c r="H219" t="n">
-        <v>0.198</v>
+        <v>0.193</v>
       </c>
       <c r="I219" t="n">
         <v>1</v>
@@ -11591,7 +11591,7 @@
         <v>0.826</v>
       </c>
       <c r="G235" t="n">
-        <v>0.826</v>
+        <v>0.87</v>
       </c>
       <c r="H235" t="n">
         <v>1</v>
@@ -12180,13 +12180,13 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G251" t="n">
-        <v>0.833</v>
+        <v>0.9</v>
       </c>
       <c r="H251" t="n">
-        <v>1</v>
+        <v>0.706</v>
       </c>
       <c r="I251" t="n">
         <v>1</v>
@@ -12775,7 +12775,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.95</v>
+        <v>0.955</v>
       </c>
       <c r="H267" t="n">
         <v>1</v>
@@ -13364,13 +13364,13 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.739</v>
+        <v>0.783</v>
       </c>
       <c r="G283" t="n">
-        <v>0.826</v>
+        <v>0.913</v>
       </c>
       <c r="H283" t="n">
-        <v>0.722</v>
+        <v>0.414</v>
       </c>
       <c r="I283" t="n">
         <v>1</v>
@@ -13956,13 +13956,13 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G299" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="H299" t="n">
-        <v>0.761</v>
+        <v>0.748</v>
       </c>
       <c r="I299" t="n">
         <v>1</v>
@@ -14551,7 +14551,7 @@
         <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0.857</v>
+        <v>0.864</v>
       </c>
       <c r="H315" t="n">
         <v>0.238</v>
@@ -15140,10 +15140,10 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
-        <v>0.739</v>
+        <v>0.783</v>
       </c>
       <c r="G331" t="n">
-        <v>0.783</v>
+        <v>0.826</v>
       </c>
       <c r="H331" t="n">
         <v>1</v>
@@ -15732,13 +15732,13 @@
         <v>10</v>
       </c>
       <c r="F347" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G347" t="n">
         <v>0.767</v>
       </c>
       <c r="H347" t="n">
-        <v>1</v>
+        <v>0.748</v>
       </c>
       <c r="I347" t="n">
         <v>1</v>
@@ -16330,7 +16330,7 @@
         <v>0.864</v>
       </c>
       <c r="H363" t="n">
-        <v>0.243</v>
+        <v>0.238</v>
       </c>
       <c r="I363" t="n">
         <v>1</v>
@@ -16916,13 +16916,13 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.739</v>
+        <v>0.783</v>
       </c>
       <c r="G379" t="n">
         <v>0.826</v>
       </c>
       <c r="H379" t="n">
-        <v>0.722</v>
+        <v>1</v>
       </c>
       <c r="I379" t="n">
         <v>1</v>
@@ -17508,7 +17508,7 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G395" t="n">
         <v>0.8</v>
@@ -18692,7 +18692,7 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.739</v>
+        <v>0.783</v>
       </c>
       <c r="G427" t="n">
         <v>0.783</v>
@@ -19284,13 +19284,13 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G443" t="n">
         <v>0.7</v>
       </c>
       <c r="H443" t="n">
-        <v>0.552</v>
+        <v>0.36</v>
       </c>
       <c r="I443" t="n">
         <v>1</v>
@@ -20144,7 +20144,7 @@
         <v>0.348</v>
       </c>
       <c r="I466" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="467">
@@ -20181,7 +20181,7 @@
         <v>0.4</v>
       </c>
       <c r="I467" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="468">
@@ -20255,7 +20255,7 @@
         <v>0.462</v>
       </c>
       <c r="I469" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="470">
@@ -20366,7 +20366,7 @@
         <v>0.23</v>
       </c>
       <c r="I472" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="473">
@@ -20440,7 +20440,7 @@
         <v>0.158</v>
       </c>
       <c r="I474" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="475">
@@ -20468,16 +20468,16 @@
         <v>10</v>
       </c>
       <c r="F475" t="n">
-        <v>0.739</v>
+        <v>0.783</v>
       </c>
       <c r="G475" t="n">
         <v>0.609</v>
       </c>
       <c r="H475" t="n">
-        <v>0.53</v>
+        <v>0.337</v>
       </c>
       <c r="I475" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="476">
@@ -20625,7 +20625,7 @@
         <v>0.407</v>
       </c>
       <c r="I479" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="480">

--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0617</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="G2" t="n">
-        <v>0.852</v>
+        <v>0.827</v>
       </c>
       <c r="H2" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0843</v>
+        <v>0.104</v>
       </c>
       <c r="J2" t="n">
-        <v>0.192</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.227</v>
+        <v>0.121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="G3" t="n">
-        <v>0.852</v>
+        <v>0.827</v>
       </c>
       <c r="H3" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0843</v>
+        <v>0.104</v>
       </c>
       <c r="J3" t="n">
-        <v>0.454</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.336</v>
+        <v>0.198</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="G4" t="n">
-        <v>0.829</v>
+        <v>0.802</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I4" t="n">
-        <v>0.105</v>
+        <v>0.135</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.44</v>
+        <v>0.247</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.829</v>
+        <v>0.802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I5" t="n">
-        <v>0.105</v>
+        <v>0.135</v>
       </c>
       <c r="J5" t="n">
-        <v>0.629</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.714</v>
+        <v>0.35</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.798</v>
       </c>
       <c r="H6" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.124</v>
+        <v>0.133</v>
       </c>
       <c r="J6" t="n">
-        <v>0.714</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.637</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.798</v>
       </c>
       <c r="H7" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I7" t="n">
-        <v>0.124</v>
+        <v>0.133</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.584</v>
+        <v>0.272</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="G8" t="n">
-        <v>0.819</v>
+        <v>0.802</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.106</v>
+        <v>0.116</v>
       </c>
       <c r="J8" t="n">
-        <v>0.714</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="G9" t="n">
-        <v>0.819</v>
+        <v>0.802</v>
       </c>
       <c r="H9" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I9" t="n">
-        <v>0.106</v>
+        <v>0.116</v>
       </c>
       <c r="J9" t="n">
-        <v>0.903</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0701</v>
+        <v>0.114</v>
       </c>
       <c r="F10" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.8</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.85</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I10" t="n">
-        <v>0.107</v>
+        <v>0.145</v>
       </c>
       <c r="J10" t="n">
-        <v>0.175</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.118</v>
+        <v>0.129</v>
       </c>
       <c r="F11" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.8</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.85</v>
-      </c>
       <c r="H11" t="n">
-        <v>0.15</v>
+        <v>0.192</v>
       </c>
       <c r="I11" t="n">
-        <v>0.107</v>
+        <v>0.145</v>
       </c>
       <c r="J11" t="n">
-        <v>0.295</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.785</v>
       </c>
       <c r="H12" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.139</v>
+        <v>0.176</v>
       </c>
       <c r="J12" t="n">
-        <v>0.714</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.62</v>
+        <v>0.633</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.785</v>
       </c>
       <c r="H13" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.139</v>
+        <v>0.176</v>
       </c>
       <c r="J13" t="n">
-        <v>0.775</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.401</v>
+        <v>0.347</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G14" t="n">
-        <v>0.804</v>
+        <v>0.783</v>
       </c>
       <c r="H14" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.136</v>
+        <v>0.166</v>
       </c>
       <c r="J14" t="n">
-        <v>0.573</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.377</v>
+        <v>0.192</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G15" t="n">
-        <v>0.804</v>
+        <v>0.783</v>
       </c>
       <c r="H15" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.136</v>
+        <v>0.166</v>
       </c>
       <c r="J15" t="n">
-        <v>0.628</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.00725</v>
+        <v>0.013</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G16" t="n">
-        <v>0.787</v>
+        <v>0.771</v>
       </c>
       <c r="H16" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I16" t="n">
-        <v>0.142</v>
+        <v>0.169</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0363</v>
+        <v>0.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G17" t="n">
-        <v>0.787</v>
+        <v>0.771</v>
       </c>
       <c r="H17" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.142</v>
+        <v>0.169</v>
       </c>
       <c r="J17" t="n">
-        <v>0.055</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0028</v>
+        <v>0.0179</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G18" t="n">
-        <v>0.788</v>
+        <v>0.769</v>
       </c>
       <c r="H18" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I18" t="n">
-        <v>0.144</v>
+        <v>0.178</v>
       </c>
       <c r="J18" t="n">
-        <v>0.028</v>
+        <v>0.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.00661</v>
+        <v>0.0176</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G19" t="n">
-        <v>0.788</v>
+        <v>0.769</v>
       </c>
       <c r="H19" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.144</v>
+        <v>0.178</v>
       </c>
       <c r="J19" t="n">
-        <v>0.055</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0461</v>
+        <v>0.188</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G20" t="n">
-        <v>0.771</v>
+        <v>0.762</v>
       </c>
       <c r="H20" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I20" t="n">
-        <v>0.111</v>
+        <v>0.124</v>
       </c>
       <c r="J20" t="n">
-        <v>0.154</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="21">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.047</v>
+        <v>0.0859</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G21" t="n">
-        <v>0.771</v>
+        <v>0.762</v>
       </c>
       <c r="H21" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I21" t="n">
-        <v>0.111</v>
+        <v>0.124</v>
       </c>
       <c r="J21" t="n">
-        <v>0.157</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.151</v>
+        <v>0.119</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9</v>
+        <v>0.895</v>
       </c>
       <c r="H22" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I22" t="n">
         <v>0.123</v>
       </c>
       <c r="J22" t="n">
-        <v>0.252</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="23">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.184</v>
+        <v>0.142</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9</v>
+        <v>0.895</v>
       </c>
       <c r="H23" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I23" t="n">
         <v>0.123</v>
       </c>
       <c r="J23" t="n">
-        <v>0.263</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="24">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0623</v>
+        <v>0.0477</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G24" t="n">
-        <v>0.917</v>
+        <v>0.91</v>
       </c>
       <c r="H24" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I24" t="n">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="J24" t="n">
-        <v>0.156</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="25">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0409</v>
+        <v>0.0329</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G25" t="n">
-        <v>0.917</v>
+        <v>0.91</v>
       </c>
       <c r="H25" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I25" t="n">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="J25" t="n">
-        <v>0.102</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="26">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0253</v>
+        <v>0.0213</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G26" t="n">
-        <v>0.903</v>
+        <v>0.9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0977</v>
+        <v>0.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.127</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0128</v>
+        <v>0.00993</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G27" t="n">
-        <v>0.903</v>
+        <v>0.9</v>
       </c>
       <c r="H27" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0977</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.102</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0206</v>
+        <v>0.0244</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G28" t="n">
-        <v>0.89</v>
+        <v>0.886</v>
       </c>
       <c r="H28" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I28" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="J28" t="n">
-        <v>0.127</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="29">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0218</v>
+        <v>0.0166</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G29" t="n">
-        <v>0.89</v>
+        <v>0.886</v>
       </c>
       <c r="H29" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I29" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="J29" t="n">
-        <v>0.102</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="30">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0421</v>
+        <v>0.0323</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G30" t="n">
-        <v>0.89</v>
+        <v>0.878</v>
       </c>
       <c r="H30" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I30" t="n">
-        <v>0.111</v>
+        <v>0.126</v>
       </c>
       <c r="J30" t="n">
-        <v>0.14</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="31">
@@ -1666,19 +1666,19 @@
         <v>0.0382</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="G31" t="n">
-        <v>0.89</v>
+        <v>0.878</v>
       </c>
       <c r="H31" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
       <c r="I31" t="n">
-        <v>0.111</v>
+        <v>0.126</v>
       </c>
       <c r="J31" t="n">
-        <v>0.102</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.328</v>
+        <v>0.278</v>
       </c>
       <c r="F32" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G32" t="n">
-        <v>0.838</v>
+        <v>0.829</v>
       </c>
       <c r="H32" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I32" t="n">
-        <v>0.163</v>
+        <v>0.182</v>
       </c>
       <c r="J32" t="n">
-        <v>0.417</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="33">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.345</v>
+        <v>0.422</v>
       </c>
       <c r="F33" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G33" t="n">
-        <v>0.838</v>
+        <v>0.829</v>
       </c>
       <c r="H33" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I33" t="n">
-        <v>0.163</v>
+        <v>0.182</v>
       </c>
       <c r="J33" t="n">
-        <v>0.345</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="34">
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.375</v>
+        <v>0.356</v>
       </c>
       <c r="F34" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G34" t="n">
-        <v>0.841</v>
+        <v>0.833</v>
       </c>
       <c r="H34" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I34" t="n">
-        <v>0.149</v>
+        <v>0.163</v>
       </c>
       <c r="J34" t="n">
-        <v>0.417</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="35">
@@ -1826,19 +1826,19 @@
         <v>0.328</v>
       </c>
       <c r="F35" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G35" t="n">
-        <v>0.841</v>
+        <v>0.833</v>
       </c>
       <c r="H35" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I35" t="n">
-        <v>0.149</v>
+        <v>0.163</v>
       </c>
       <c r="J35" t="n">
-        <v>0.345</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="36">
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.355</v>
+        <v>0.323</v>
       </c>
       <c r="F36" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G36" t="n">
-        <v>0.843</v>
+        <v>0.835</v>
       </c>
       <c r="H36" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I36" t="n">
-        <v>0.135</v>
+        <v>0.152</v>
       </c>
       <c r="J36" t="n">
-        <v>0.417</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="37">
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.239</v>
+        <v>0.213</v>
       </c>
       <c r="F37" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G37" t="n">
-        <v>0.843</v>
+        <v>0.835</v>
       </c>
       <c r="H37" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I37" t="n">
-        <v>0.135</v>
+        <v>0.152</v>
       </c>
       <c r="J37" t="n">
-        <v>0.299</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="38">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.151</v>
+        <v>0.13</v>
       </c>
       <c r="F38" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G38" t="n">
-        <v>0.836</v>
+        <v>0.827</v>
       </c>
       <c r="H38" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I38" t="n">
-        <v>0.149</v>
+        <v>0.167</v>
       </c>
       <c r="J38" t="n">
-        <v>0.252</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="39">
@@ -1986,19 +1986,19 @@
         <v>0.155</v>
       </c>
       <c r="F39" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G39" t="n">
-        <v>0.836</v>
+        <v>0.827</v>
       </c>
       <c r="H39" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I39" t="n">
-        <v>0.149</v>
+        <v>0.167</v>
       </c>
       <c r="J39" t="n">
-        <v>0.258</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="40">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.588</v>
+        <v>0.502</v>
       </c>
       <c r="F40" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G40" t="n">
-        <v>0.874</v>
+        <v>0.873</v>
       </c>
       <c r="H40" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I40" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="J40" t="n">
-        <v>0.588</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="41">
@@ -2063,22 +2063,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.0844</v>
+        <v>0.0712</v>
       </c>
       <c r="F41" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G41" t="n">
-        <v>0.874</v>
+        <v>0.873</v>
       </c>
       <c r="H41" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I41" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="J41" t="n">
-        <v>0.169</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="42">
@@ -2103,22 +2103,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.35</v>
+        <v>0.169</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G42" t="n">
-        <v>0.841</v>
+        <v>0.799</v>
       </c>
       <c r="H42" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I42" t="n">
-        <v>0.152</v>
+        <v>0.175</v>
       </c>
       <c r="J42" t="n">
-        <v>0.828</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="43">
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.445</v>
+        <v>0.203</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G43" t="n">
-        <v>0.841</v>
+        <v>0.799</v>
       </c>
       <c r="H43" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I43" t="n">
-        <v>0.152</v>
+        <v>0.175</v>
       </c>
       <c r="J43" t="n">
-        <v>0.636</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="44">
@@ -2183,22 +2183,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.497</v>
+        <v>0.901</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G44" t="n">
-        <v>0.792</v>
+        <v>0.751</v>
       </c>
       <c r="H44" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I44" t="n">
-        <v>0.184</v>
+        <v>0.233</v>
       </c>
       <c r="J44" t="n">
-        <v>0.828</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.347</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G45" t="n">
-        <v>0.792</v>
+        <v>0.751</v>
       </c>
       <c r="H45" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I45" t="n">
-        <v>0.184</v>
+        <v>0.233</v>
       </c>
       <c r="J45" t="n">
-        <v>0.636</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="46">
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.449</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G46" t="n">
-        <v>0.78</v>
+        <v>0.758</v>
       </c>
       <c r="H46" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I46" t="n">
-        <v>0.188</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
-        <v>0.828</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.382</v>
+        <v>0.861</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G47" t="n">
-        <v>0.78</v>
+        <v>0.758</v>
       </c>
       <c r="H47" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I47" t="n">
-        <v>0.188</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
-        <v>0.636</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="48">
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.667</v>
+        <v>0.785</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G48" t="n">
-        <v>0.794</v>
+        <v>0.768</v>
       </c>
       <c r="H48" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I48" t="n">
-        <v>0.176</v>
+        <v>0.187</v>
       </c>
       <c r="J48" t="n">
-        <v>0.92</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2383,22 +2383,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.311</v>
+        <v>0.875</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G49" t="n">
-        <v>0.794</v>
+        <v>0.768</v>
       </c>
       <c r="H49" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I49" t="n">
-        <v>0.176</v>
+        <v>0.187</v>
       </c>
       <c r="J49" t="n">
-        <v>0.636</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="50">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.736</v>
+        <v>0.91</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G50" t="n">
-        <v>0.827</v>
+        <v>0.751</v>
       </c>
       <c r="H50" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I50" t="n">
-        <v>0.172</v>
+        <v>0.197</v>
       </c>
       <c r="J50" t="n">
-        <v>0.92</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.76</v>
+        <v>0.594</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G51" t="n">
-        <v>0.827</v>
+        <v>0.751</v>
       </c>
       <c r="H51" t="n">
-        <v>0.205</v>
+        <v>0.254</v>
       </c>
       <c r="I51" t="n">
-        <v>0.172</v>
+        <v>0.197</v>
       </c>
       <c r="J51" t="n">
-        <v>0.931</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="52">
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.973</v>
+        <v>0.764</v>
       </c>
       <c r="F52" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G52" t="n">
-        <v>0.832</v>
+        <v>0.798</v>
       </c>
       <c r="H52" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I52" t="n">
-        <v>0.206</v>
+        <v>0.227</v>
       </c>
       <c r="J52" t="n">
-        <v>0.973</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2543,22 +2543,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0.695</v>
       </c>
       <c r="F53" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G53" t="n">
-        <v>0.832</v>
+        <v>0.798</v>
       </c>
       <c r="H53" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I53" t="n">
-        <v>0.206</v>
+        <v>0.227</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="54">
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.947</v>
+        <v>0.832</v>
       </c>
       <c r="F54" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G54" t="n">
-        <v>0.831</v>
+        <v>0.801</v>
       </c>
       <c r="H54" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I54" t="n">
-        <v>0.203</v>
+        <v>0.214</v>
       </c>
       <c r="J54" t="n">
-        <v>0.973</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.838</v>
+        <v>0.878</v>
       </c>
       <c r="F55" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G55" t="n">
-        <v>0.831</v>
+        <v>0.801</v>
       </c>
       <c r="H55" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I55" t="n">
-        <v>0.203</v>
+        <v>0.214</v>
       </c>
       <c r="J55" t="n">
-        <v>0.931</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="56">
@@ -2663,22 +2663,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0374</v>
+        <v>0.0532</v>
       </c>
       <c r="F56" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G56" t="n">
-        <v>0.782</v>
+        <v>0.756</v>
       </c>
       <c r="H56" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>0.209</v>
       </c>
       <c r="J56" t="n">
-        <v>0.187</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="57">
@@ -2703,22 +2703,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0152</v>
+        <v>0.0506</v>
       </c>
       <c r="F57" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G57" t="n">
-        <v>0.782</v>
+        <v>0.756</v>
       </c>
       <c r="H57" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>0.209</v>
       </c>
       <c r="J57" t="n">
-        <v>0.076</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="58">
@@ -2743,22 +2743,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.189</v>
+        <v>0.21</v>
       </c>
       <c r="F58" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G58" t="n">
-        <v>0.819</v>
+        <v>0.789</v>
       </c>
       <c r="H58" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I58" t="n">
-        <v>0.21</v>
+        <v>0.223</v>
       </c>
       <c r="J58" t="n">
-        <v>0.63</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="59">
@@ -2783,22 +2783,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.327</v>
+        <v>0.173</v>
       </c>
       <c r="F59" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G59" t="n">
-        <v>0.819</v>
+        <v>0.789</v>
       </c>
       <c r="H59" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I59" t="n">
-        <v>0.21</v>
+        <v>0.223</v>
       </c>
       <c r="J59" t="n">
-        <v>0.636</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="60">
@@ -2823,22 +2823,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00393</v>
+        <v>0.0113</v>
       </c>
       <c r="F60" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G60" t="n">
-        <v>0.651</v>
+        <v>0.641</v>
       </c>
       <c r="H60" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I60" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0393</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="61">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.00147</v>
+        <v>0.00465</v>
       </c>
       <c r="F61" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G61" t="n">
-        <v>0.651</v>
+        <v>0.641</v>
       </c>
       <c r="H61" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I61" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0147</v>
+        <v>0.0465</v>
       </c>
     </row>
     <row r="62">
@@ -2903,22 +2903,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.171</v>
+        <v>0.11</v>
       </c>
       <c r="F62" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G62" t="n">
-        <v>0.853</v>
+        <v>0.825</v>
       </c>
       <c r="H62" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0896</v>
+        <v>0.104</v>
       </c>
       <c r="J62" t="n">
-        <v>0.38</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="63">
@@ -2943,22 +2943,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.293</v>
+        <v>0.233</v>
       </c>
       <c r="F63" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G63" t="n">
-        <v>0.853</v>
+        <v>0.825</v>
       </c>
       <c r="H63" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0896</v>
+        <v>0.104</v>
       </c>
       <c r="J63" t="n">
-        <v>0.586</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="64">
@@ -2983,22 +2983,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.361</v>
+        <v>0.235</v>
       </c>
       <c r="F64" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G64" t="n">
-        <v>0.831</v>
+        <v>0.796</v>
       </c>
       <c r="H64" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I64" t="n">
-        <v>0.121</v>
+        <v>0.166</v>
       </c>
       <c r="J64" t="n">
-        <v>0.595</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="65">
@@ -3023,22 +3023,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.917</v>
+        <v>0.47</v>
       </c>
       <c r="F65" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G65" t="n">
-        <v>0.831</v>
+        <v>0.796</v>
       </c>
       <c r="H65" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I65" t="n">
-        <v>0.121</v>
+        <v>0.166</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="66">
@@ -3063,22 +3063,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.51</v>
+        <v>0.226</v>
       </c>
       <c r="F66" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G66" t="n">
-        <v>0.819</v>
+        <v>0.803</v>
       </c>
       <c r="H66" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I66" t="n">
-        <v>0.118</v>
+        <v>0.127</v>
       </c>
       <c r="J66" t="n">
-        <v>0.595</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="67">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0.642</v>
       </c>
       <c r="F67" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G67" t="n">
-        <v>0.819</v>
+        <v>0.803</v>
       </c>
       <c r="H67" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I67" t="n">
-        <v>0.118</v>
+        <v>0.127</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="68">
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.538</v>
+        <v>0.239</v>
       </c>
       <c r="F68" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="H68" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I68" t="n">
-        <v>0.119</v>
+        <v>0.123</v>
       </c>
       <c r="J68" t="n">
-        <v>0.595</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="69">
@@ -3183,22 +3183,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.778</v>
+        <v>0.46</v>
       </c>
       <c r="F69" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="H69" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I69" t="n">
-        <v>0.119</v>
+        <v>0.123</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="70">
@@ -3223,22 +3223,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="F70" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="G70" t="n">
         <v>0.791</v>
       </c>
-      <c r="G70" t="n">
-        <v>0.84</v>
-      </c>
       <c r="H70" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I70" t="n">
-        <v>0.121</v>
+        <v>0.137</v>
       </c>
       <c r="J70" t="n">
-        <v>0.38</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="71">
@@ -3263,22 +3263,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.272</v>
+        <v>0.388</v>
       </c>
       <c r="F71" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="G71" t="n">
         <v>0.791</v>
       </c>
-      <c r="G71" t="n">
-        <v>0.84</v>
-      </c>
       <c r="H71" t="n">
-        <v>0.18</v>
+        <v>0.221</v>
       </c>
       <c r="I71" t="n">
-        <v>0.121</v>
+        <v>0.137</v>
       </c>
       <c r="J71" t="n">
-        <v>0.586</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="72">
@@ -3303,22 +3303,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.528</v>
+        <v>0.434</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G72" t="n">
-        <v>0.805</v>
+        <v>0.784</v>
       </c>
       <c r="H72" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I72" t="n">
-        <v>0.173</v>
+        <v>0.191</v>
       </c>
       <c r="J72" t="n">
-        <v>0.595</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="73">
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.778</v>
+        <v>0.51</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G73" t="n">
-        <v>0.805</v>
+        <v>0.784</v>
       </c>
       <c r="H73" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I73" t="n">
-        <v>0.173</v>
+        <v>0.191</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="74">
@@ -3383,22 +3383,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.595</v>
+        <v>0.555</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="H74" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I74" t="n">
-        <v>0.169</v>
+        <v>0.181</v>
       </c>
       <c r="J74" t="n">
-        <v>0.595</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="75">
@@ -3423,19 +3423,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.859</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="H75" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I75" t="n">
-        <v>0.169</v>
+        <v>0.181</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
@@ -3463,22 +3463,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.0432</v>
+        <v>0.0565</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G76" t="n">
-        <v>0.786</v>
+        <v>0.77</v>
       </c>
       <c r="H76" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I76" t="n">
-        <v>0.163</v>
+        <v>0.177</v>
       </c>
       <c r="J76" t="n">
-        <v>0.144</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="77">
@@ -3503,22 +3503,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.0277</v>
+        <v>0.0414</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G77" t="n">
-        <v>0.786</v>
+        <v>0.77</v>
       </c>
       <c r="H77" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I77" t="n">
-        <v>0.163</v>
+        <v>0.177</v>
       </c>
       <c r="J77" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="78">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.00889</v>
+        <v>0.0235</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G78" t="n">
-        <v>0.795</v>
+        <v>0.777</v>
       </c>
       <c r="H78" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I78" t="n">
-        <v>0.159</v>
+        <v>0.177</v>
       </c>
       <c r="J78" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="79">
@@ -3583,22 +3583,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.00222</v>
+        <v>0.0186</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G79" t="n">
-        <v>0.795</v>
+        <v>0.777</v>
       </c>
       <c r="H79" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I79" t="n">
-        <v>0.159</v>
+        <v>0.177</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0222</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="80">
@@ -3623,22 +3623,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0341</v>
+        <v>0.0634</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G80" t="n">
-        <v>0.716</v>
+        <v>0.708</v>
       </c>
       <c r="H80" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I80" t="n">
         <v>0.191</v>
       </c>
       <c r="J80" t="n">
-        <v>0.144</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="81">
@@ -3663,22 +3663,22 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0171</v>
+        <v>0.0409</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G81" t="n">
-        <v>0.716</v>
+        <v>0.708</v>
       </c>
       <c r="H81" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I81" t="n">
         <v>0.191</v>
       </c>
       <c r="J81" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.138</v>
       </c>
     </row>
   </sheetData>
@@ -3813,7 +3813,7 @@
         <v>0.0105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.135</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="4">
@@ -3878,10 +3878,10 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="G5" t="n">
-        <v>0.967</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -4063,13 +4063,13 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.767</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.8</v>
-      </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.771</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -4100,13 +4100,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7</v>
+        <v>0.533</v>
       </c>
       <c r="G11" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="H11" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -4137,13 +4137,13 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="n">
         <v>0.667</v>
       </c>
       <c r="H12" t="n">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -4285,16 +4285,16 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.667</v>
+        <v>0.467</v>
       </c>
       <c r="G16" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="H16" t="n">
-        <v>0.233</v>
+        <v>0.0326</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="17">
@@ -4322,16 +4322,16 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.433</v>
+        <v>0.333</v>
       </c>
       <c r="G17" t="n">
-        <v>0.767</v>
+        <v>0.667</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0169</v>
+        <v>0.0194</v>
       </c>
       <c r="I17" t="n">
-        <v>0.135</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="18">
@@ -4405,7 +4405,7 @@
         <v>0.0699</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="20">
@@ -4473,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -4692,13 +4692,13 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.792</v>
+        <v>0.737</v>
       </c>
       <c r="G27" t="n">
-        <v>0.909</v>
+        <v>0.882</v>
       </c>
       <c r="H27" t="n">
-        <v>0.418</v>
+        <v>0.408</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -4729,7 +4729,7 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.87</v>
+        <v>0.864</v>
       </c>
       <c r="G28" t="n">
         <v>0.895</v>
@@ -4877,16 +4877,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.108</v>
+        <v>0.0391</v>
       </c>
       <c r="I32" t="n">
-        <v>0.577</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="33">
@@ -4914,16 +4914,16 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="G33" t="n">
-        <v>0.917</v>
+        <v>0.889</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0557</v>
+        <v>0.035</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="34">
@@ -5062,10 +5062,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -5247,13 +5247,13 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G42" t="n">
         <v>0.767</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.8</v>
-      </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0.771</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -5284,10 +5284,10 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.826</v>
+        <v>0.609</v>
       </c>
       <c r="G43" t="n">
-        <v>0.87</v>
+        <v>0.652</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -5321,13 +5321,13 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="G44" t="n">
         <v>0.68</v>
       </c>
       <c r="H44" t="n">
-        <v>0.52</v>
+        <v>0.754</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -5469,13 +5469,13 @@
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G48" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0.205</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
@@ -5506,16 +5506,16 @@
         <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>0.294</v>
+        <v>0.118</v>
       </c>
       <c r="G49" t="n">
-        <v>0.647</v>
+        <v>0.471</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0844</v>
+        <v>0.057</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="50">
@@ -5589,7 +5589,7 @@
         <v>0.0436</v>
       </c>
       <c r="I51" t="n">
-        <v>0.349</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="52">
@@ -5654,10 +5654,10 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
@@ -5839,13 +5839,13 @@
         <v>9</v>
       </c>
       <c r="F58" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.868</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.889</v>
-      </c>
       <c r="H58" t="n">
-        <v>0.776</v>
+        <v>0.594</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -5876,13 +5876,13 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="G59" t="n">
-        <v>0.889</v>
+        <v>0.75</v>
       </c>
       <c r="H59" t="n">
-        <v>0.386</v>
+        <v>0.471</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -5913,13 +5913,13 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.833</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G60" t="n">
         <v>0.773</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6</v>
+        <v>0.798</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -6061,16 +6061,16 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.737</v>
+        <v>0.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0.857</v>
+        <v>0.788</v>
       </c>
       <c r="H64" t="n">
-        <v>0.254</v>
+        <v>0.0203</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="65">
@@ -6098,16 +6098,16 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.37</v>
+        <v>0.167</v>
       </c>
       <c r="G65" t="n">
-        <v>0.759</v>
+        <v>0.615</v>
       </c>
       <c r="H65" t="n">
-        <v>0.00637</v>
+        <v>0.00159</v>
       </c>
       <c r="I65" t="n">
-        <v>0.102</v>
+        <v>0.0255</v>
       </c>
     </row>
     <row r="66">
@@ -6246,7 +6246,7 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -6431,10 +6431,10 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="G74" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="H74" t="n">
         <v>1</v>
@@ -6468,13 +6468,13 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7</v>
+        <v>0.533</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -6505,10 +6505,10 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G76" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -6653,16 +6653,16 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.667</v>
+        <v>0.467</v>
       </c>
       <c r="G80" t="n">
-        <v>0.833</v>
+        <v>0.733</v>
       </c>
       <c r="H80" t="n">
-        <v>0.233</v>
+        <v>0.0641</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="81">
@@ -6690,16 +6690,16 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.433</v>
+        <v>0.333</v>
       </c>
       <c r="G81" t="n">
-        <v>0.733</v>
+        <v>0.533</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0352</v>
+        <v>0.192</v>
       </c>
       <c r="I81" t="n">
-        <v>0.282</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -6736,7 +6736,7 @@
         <v>0.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.842</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="83">
@@ -6773,7 +6773,7 @@
         <v>0.0699</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="84">
@@ -7060,13 +7060,13 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.792</v>
+        <v>0.737</v>
       </c>
       <c r="G91" t="n">
-        <v>0.889</v>
+        <v>0.882</v>
       </c>
       <c r="H91" t="n">
-        <v>0.679</v>
+        <v>0.408</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -7097,10 +7097,10 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.87</v>
+        <v>0.864</v>
       </c>
       <c r="G92" t="n">
-        <v>0.9</v>
+        <v>0.895</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
@@ -7245,16 +7245,16 @@
         <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>0.108</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>0.577</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="97">
@@ -7282,16 +7282,16 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="G97" t="n">
-        <v>0.909</v>
+        <v>0.8</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0635</v>
+        <v>0.242</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="98">
@@ -7430,7 +7430,7 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -7615,10 +7615,10 @@
         <v>9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="G106" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -7652,13 +7652,13 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.826</v>
+        <v>0.609</v>
       </c>
       <c r="G107" t="n">
-        <v>0.696</v>
+        <v>0.652</v>
       </c>
       <c r="H107" t="n">
-        <v>0.491</v>
+        <v>1</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -7689,13 +7689,13 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="G108" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H108" t="n">
-        <v>0.742</v>
+        <v>0.754</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -7837,13 +7837,13 @@
         <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G112" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>0.343</v>
       </c>
       <c r="I112" t="n">
         <v>1</v>
@@ -7874,13 +7874,13 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0.294</v>
+        <v>0.118</v>
       </c>
       <c r="G113" t="n">
-        <v>0.588</v>
+        <v>0.235</v>
       </c>
       <c r="H113" t="n">
-        <v>0.166</v>
+        <v>0.656</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -7957,7 +7957,7 @@
         <v>0.0436</v>
       </c>
       <c r="I115" t="n">
-        <v>0.349</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -8022,16 +8022,16 @@
         <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0.481</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="118">
@@ -8105,7 +8105,7 @@
         <v>0.484</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="120">
@@ -8207,10 +8207,10 @@
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.868</v>
+        <v>0.824</v>
       </c>
       <c r="G122" t="n">
-        <v>0.868</v>
+        <v>0.824</v>
       </c>
       <c r="H122" t="n">
         <v>1</v>
@@ -8244,16 +8244,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="G123" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="H123" t="n">
-        <v>0.795</v>
+        <v>0.471</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="124">
@@ -8281,13 +8281,13 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.833</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G124" t="n">
-        <v>0.8</v>
+        <v>0.773</v>
       </c>
       <c r="H124" t="n">
-        <v>0.79</v>
+        <v>0.798</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -8401,7 +8401,7 @@
         <v>0.249</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="128">
@@ -8429,16 +8429,16 @@
         <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>0.737</v>
+        <v>0.5</v>
       </c>
       <c r="G128" t="n">
-        <v>0.857</v>
+        <v>0.75</v>
       </c>
       <c r="H128" t="n">
-        <v>0.254</v>
+        <v>0.0697</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -8466,16 +8466,16 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.37</v>
+        <v>0.167</v>
       </c>
       <c r="G129" t="n">
-        <v>0.714</v>
+        <v>0.364</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0151</v>
+        <v>0.183</v>
       </c>
       <c r="I129" t="n">
-        <v>0.242</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="130">
@@ -8549,7 +8549,7 @@
         <v>0.0523</v>
       </c>
       <c r="I131" t="n">
-        <v>0.306</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="132">
@@ -8614,7 +8614,7 @@
         <v>4</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -8799,13 +8799,13 @@
         <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="G138" t="n">
-        <v>0.7</v>
+        <v>0.633</v>
       </c>
       <c r="H138" t="n">
-        <v>0.771</v>
+        <v>0.785</v>
       </c>
       <c r="I138" t="n">
         <v>1</v>
@@ -8836,13 +8836,13 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.7</v>
+        <v>0.533</v>
       </c>
       <c r="G139" t="n">
         <v>0.6</v>
       </c>
       <c r="H139" t="n">
-        <v>0.589</v>
+        <v>0.795</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -8873,13 +8873,13 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G140" t="n">
         <v>0.667</v>
       </c>
       <c r="H140" t="n">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I140" t="n">
         <v>1</v>
@@ -9021,16 +9021,16 @@
         <v>15</v>
       </c>
       <c r="F144" t="n">
-        <v>0.667</v>
+        <v>0.467</v>
       </c>
       <c r="G144" t="n">
-        <v>0.9</v>
+        <v>0.833</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0575</v>
+        <v>0.00611</v>
       </c>
       <c r="I144" t="n">
-        <v>0.306</v>
+        <v>0.0977</v>
       </c>
     </row>
     <row r="145">
@@ -9058,16 +9058,16 @@
         <v>16</v>
       </c>
       <c r="F145" t="n">
-        <v>0.433</v>
+        <v>0.333</v>
       </c>
       <c r="G145" t="n">
-        <v>0.733</v>
+        <v>0.633</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0352</v>
+        <v>0.0379</v>
       </c>
       <c r="I145" t="n">
-        <v>0.306</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="146">
@@ -9428,13 +9428,13 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.792</v>
+        <v>0.737</v>
       </c>
       <c r="G155" t="n">
         <v>0.824</v>
       </c>
       <c r="H155" t="n">
-        <v>1</v>
+        <v>0.695</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
@@ -9465,7 +9465,7 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
-        <v>0.87</v>
+        <v>0.864</v>
       </c>
       <c r="G156" t="n">
         <v>0.895</v>
@@ -9613,13 +9613,13 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="G160" t="n">
-        <v>0.947</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H160" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="I160" t="n">
         <v>1</v>
@@ -9650,16 +9650,16 @@
         <v>16</v>
       </c>
       <c r="F161" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="G161" t="n">
-        <v>0.846</v>
+        <v>0.8</v>
       </c>
       <c r="H161" t="n">
-        <v>0.169</v>
+        <v>0.0584</v>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="162">
@@ -9798,7 +9798,7 @@
         <v>4</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
@@ -9983,13 +9983,13 @@
         <v>9</v>
       </c>
       <c r="F170" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="G170" t="n">
-        <v>0.7</v>
+        <v>0.633</v>
       </c>
       <c r="H170" t="n">
-        <v>0.771</v>
+        <v>0.785</v>
       </c>
       <c r="I170" t="n">
         <v>1</v>
@@ -10020,16 +10020,16 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.826</v>
+        <v>0.609</v>
       </c>
       <c r="G171" t="n">
         <v>0.609</v>
       </c>
       <c r="H171" t="n">
-        <v>0.189</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>0.752</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -10057,13 +10057,13 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="G172" t="n">
         <v>0.68</v>
       </c>
       <c r="H172" t="n">
-        <v>0.52</v>
+        <v>0.754</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
@@ -10103,7 +10103,7 @@
         <v>0.232</v>
       </c>
       <c r="I173" t="n">
-        <v>0.752</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="174">
@@ -10205,16 +10205,16 @@
         <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G176" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H176" t="n">
-        <v>0.235</v>
+        <v>0.0225</v>
       </c>
       <c r="I176" t="n">
-        <v>0.752</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="177">
@@ -10242,16 +10242,16 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.294</v>
+        <v>0.118</v>
       </c>
       <c r="G177" t="n">
-        <v>0.647</v>
+        <v>0.471</v>
       </c>
       <c r="H177" t="n">
-        <v>0.0844</v>
+        <v>0.057</v>
       </c>
       <c r="I177" t="n">
-        <v>0.675</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="178">
@@ -10390,16 +10390,16 @@
         <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
       </c>
       <c r="H181" t="n">
-        <v>1</v>
+        <v>0.481</v>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="182">
@@ -10575,16 +10575,16 @@
         <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>0.868</v>
+        <v>0.824</v>
       </c>
       <c r="G186" t="n">
-        <v>0.824</v>
+        <v>0.776</v>
       </c>
       <c r="H186" t="n">
-        <v>0.594</v>
+        <v>0.622</v>
       </c>
       <c r="I186" t="n">
-        <v>0.8</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="187">
@@ -10612,16 +10612,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="G187" t="n">
         <v>0.7</v>
       </c>
       <c r="H187" t="n">
-        <v>0.316</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>0.722</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -10649,16 +10649,16 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.833</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G188" t="n">
         <v>0.773</v>
       </c>
       <c r="H188" t="n">
-        <v>0.6</v>
+        <v>0.798</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -10797,16 +10797,16 @@
         <v>15</v>
       </c>
       <c r="F192" t="n">
-        <v>0.737</v>
+        <v>0.5</v>
       </c>
       <c r="G192" t="n">
-        <v>0.923</v>
+        <v>0.865</v>
       </c>
       <c r="H192" t="n">
-        <v>0.0362</v>
+        <v>0.00148</v>
       </c>
       <c r="I192" t="n">
-        <v>0.29</v>
+        <v>0.0237</v>
       </c>
     </row>
     <row r="193">
@@ -10834,16 +10834,16 @@
         <v>16</v>
       </c>
       <c r="F193" t="n">
-        <v>0.37</v>
+        <v>0.167</v>
       </c>
       <c r="G193" t="n">
-        <v>0.733</v>
+        <v>0.593</v>
       </c>
       <c r="H193" t="n">
-        <v>0.007979999999999999</v>
+        <v>0.00357</v>
       </c>
       <c r="I193" t="n">
-        <v>0.128</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="194">
@@ -10982,7 +10982,7 @@
         <v>4</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="G197" t="n">
         <v>1</v>
@@ -11167,13 +11167,13 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="G202" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H202" t="n">
-        <v>0.771</v>
+        <v>1</v>
       </c>
       <c r="I202" t="n">
         <v>1</v>
@@ -11204,13 +11204,13 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.7</v>
+        <v>0.533</v>
       </c>
       <c r="G203" t="n">
         <v>0.633</v>
       </c>
       <c r="H203" t="n">
-        <v>0.785</v>
+        <v>0.601</v>
       </c>
       <c r="I203" t="n">
         <v>1</v>
@@ -11241,13 +11241,13 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G204" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="H204" t="n">
-        <v>0.779</v>
+        <v>0.785</v>
       </c>
       <c r="I204" t="n">
         <v>1</v>
@@ -11389,16 +11389,16 @@
         <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>0.667</v>
+        <v>0.467</v>
       </c>
       <c r="G208" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="H208" t="n">
-        <v>0.233</v>
+        <v>0.0326</v>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="209">
@@ -11426,16 +11426,16 @@
         <v>16</v>
       </c>
       <c r="F209" t="n">
-        <v>0.433</v>
+        <v>0.333</v>
       </c>
       <c r="G209" t="n">
-        <v>0.833</v>
+        <v>0.7</v>
       </c>
       <c r="H209" t="n">
-        <v>0.00278</v>
+        <v>0.009209999999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0445</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="210">
@@ -11796,13 +11796,13 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.792</v>
+        <v>0.737</v>
       </c>
       <c r="G219" t="n">
         <v>0.833</v>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I219" t="n">
         <v>1</v>
@@ -11833,10 +11833,10 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.87</v>
+        <v>0.864</v>
       </c>
       <c r="G220" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H220" t="n">
         <v>0.624</v>
@@ -11981,13 +11981,13 @@
         <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="G224" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H224" t="n">
-        <v>0.338</v>
+        <v>0.139</v>
       </c>
       <c r="I224" t="n">
         <v>1</v>
@@ -12018,16 +12018,16 @@
         <v>16</v>
       </c>
       <c r="F225" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="G225" t="n">
-        <v>0.875</v>
+        <v>0.833</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0687</v>
+        <v>0.0449</v>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>0.719</v>
       </c>
     </row>
     <row r="226">
@@ -12166,7 +12166,7 @@
         <v>4</v>
       </c>
       <c r="F229" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G229" t="n">
         <v>1</v>
@@ -12351,13 +12351,13 @@
         <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="G234" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H234" t="n">
-        <v>0.771</v>
+        <v>1</v>
       </c>
       <c r="I234" t="n">
         <v>1</v>
@@ -12388,13 +12388,13 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.826</v>
+        <v>0.609</v>
       </c>
       <c r="G235" t="n">
         <v>0.652</v>
       </c>
       <c r="H235" t="n">
-        <v>0.314</v>
+        <v>1</v>
       </c>
       <c r="I235" t="n">
         <v>1</v>
@@ -12425,13 +12425,13 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="G236" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H236" t="n">
-        <v>0.345</v>
+        <v>0.364</v>
       </c>
       <c r="I236" t="n">
         <v>1</v>
@@ -12573,16 +12573,16 @@
         <v>15</v>
       </c>
       <c r="F240" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G240" t="n">
         <v>0.7</v>
       </c>
-      <c r="G240" t="n">
-        <v>0.8</v>
-      </c>
       <c r="H240" t="n">
-        <v>0.716</v>
+        <v>0.111</v>
       </c>
       <c r="I240" t="n">
-        <v>1</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="241">
@@ -12610,16 +12610,16 @@
         <v>16</v>
       </c>
       <c r="F241" t="n">
-        <v>0.294</v>
+        <v>0.118</v>
       </c>
       <c r="G241" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0049</v>
+        <v>0.0104</v>
       </c>
       <c r="I241" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="242">
@@ -12758,16 +12758,16 @@
         <v>4</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="G245" t="n">
         <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>1</v>
+        <v>0.481</v>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="246">
@@ -12943,16 +12943,16 @@
         <v>9</v>
       </c>
       <c r="F250" t="n">
-        <v>0.868</v>
+        <v>0.824</v>
       </c>
       <c r="G250" t="n">
-        <v>0.824</v>
+        <v>0.8</v>
       </c>
       <c r="H250" t="n">
-        <v>0.594</v>
+        <v>0.804</v>
       </c>
       <c r="I250" t="n">
-        <v>0.792</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="251">
@@ -12980,16 +12980,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="G251" t="n">
         <v>0.732</v>
       </c>
       <c r="H251" t="n">
-        <v>0.45</v>
+        <v>0.634</v>
       </c>
       <c r="I251" t="n">
-        <v>0.7</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="252">
@@ -13017,13 +13017,13 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
-        <v>0.833</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G252" t="n">
-        <v>0.762</v>
+        <v>0.732</v>
       </c>
       <c r="H252" t="n">
-        <v>0.438</v>
+        <v>0.45</v>
       </c>
       <c r="I252" t="n">
         <v>0.7</v>
@@ -13165,16 +13165,16 @@
         <v>15</v>
       </c>
       <c r="F256" t="n">
-        <v>0.737</v>
+        <v>0.5</v>
       </c>
       <c r="G256" t="n">
-        <v>0.865</v>
+        <v>0.8</v>
       </c>
       <c r="H256" t="n">
-        <v>0.249</v>
+        <v>0.0117</v>
       </c>
       <c r="I256" t="n">
-        <v>0.7</v>
+        <v>0.0936</v>
       </c>
     </row>
     <row r="257">
@@ -13202,16 +13202,16 @@
         <v>16</v>
       </c>
       <c r="F257" t="n">
-        <v>0.37</v>
+        <v>0.167</v>
       </c>
       <c r="G257" t="n">
-        <v>0.848</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H257" t="n">
-        <v>0.000171</v>
+        <v>0.000237</v>
       </c>
       <c r="I257" t="n">
-        <v>0.00273</v>
+        <v>0.00379</v>
       </c>
     </row>
     <row r="258">
@@ -13285,7 +13285,7 @@
         <v>0.0523</v>
       </c>
       <c r="I259" t="n">
-        <v>0.538</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="260">
@@ -13350,10 +13350,10 @@
         <v>4</v>
       </c>
       <c r="F261" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="G261" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="H261" t="n">
         <v>1</v>
@@ -13535,16 +13535,16 @@
         <v>9</v>
       </c>
       <c r="F266" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="G266" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H266" t="n">
-        <v>0.145</v>
+        <v>0.552</v>
       </c>
       <c r="I266" t="n">
-        <v>0.776</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -13572,16 +13572,16 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.7</v>
+        <v>0.533</v>
       </c>
       <c r="G267" t="n">
-        <v>0.867</v>
+        <v>0.667</v>
       </c>
       <c r="H267" t="n">
-        <v>0.209</v>
+        <v>0.43</v>
       </c>
       <c r="I267" t="n">
-        <v>0.837</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -13609,13 +13609,13 @@
         <v>11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G268" t="n">
-        <v>0.7</v>
+        <v>0.633</v>
       </c>
       <c r="H268" t="n">
-        <v>1</v>
+        <v>0.785</v>
       </c>
       <c r="I268" t="n">
         <v>1</v>
@@ -13757,13 +13757,13 @@
         <v>15</v>
       </c>
       <c r="F272" t="n">
-        <v>0.667</v>
+        <v>0.467</v>
       </c>
       <c r="G272" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H272" t="n">
-        <v>0.382</v>
+        <v>0.438</v>
       </c>
       <c r="I272" t="n">
         <v>1</v>
@@ -13794,16 +13794,16 @@
         <v>16</v>
       </c>
       <c r="F273" t="n">
-        <v>0.433</v>
+        <v>0.333</v>
       </c>
       <c r="G273" t="n">
-        <v>0.7</v>
+        <v>0.533</v>
       </c>
       <c r="H273" t="n">
-        <v>0.0673</v>
+        <v>0.192</v>
       </c>
       <c r="I273" t="n">
-        <v>0.538</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -14164,13 +14164,13 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.792</v>
+        <v>0.737</v>
       </c>
       <c r="G283" t="n">
-        <v>0.952</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H283" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="I283" t="n">
         <v>1</v>
@@ -14201,10 +14201,10 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.87</v>
+        <v>0.864</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9</v>
+        <v>0.889</v>
       </c>
       <c r="H284" t="n">
         <v>1</v>
@@ -14349,13 +14349,13 @@
         <v>15</v>
       </c>
       <c r="F288" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="G288" t="n">
-        <v>0.85</v>
+        <v>0.786</v>
       </c>
       <c r="H288" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.665</v>
       </c>
       <c r="I288" t="n">
         <v>1</v>
@@ -14386,13 +14386,13 @@
         <v>16</v>
       </c>
       <c r="F289" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="G289" t="n">
-        <v>0.722</v>
+        <v>0.615</v>
       </c>
       <c r="H289" t="n">
-        <v>0.412</v>
+        <v>0.35</v>
       </c>
       <c r="I289" t="n">
         <v>1</v>
@@ -14432,7 +14432,7 @@
         <v>0.109</v>
       </c>
       <c r="I290" t="n">
-        <v>0.776</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="291">
@@ -14534,10 +14534,10 @@
         <v>4</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G293" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="H293" t="n">
         <v>1</v>
@@ -14719,16 +14719,16 @@
         <v>9</v>
       </c>
       <c r="F298" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="G298" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H298" t="n">
-        <v>0.145</v>
+        <v>0.552</v>
       </c>
       <c r="I298" t="n">
-        <v>0.776</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -14756,10 +14756,10 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.826</v>
+        <v>0.609</v>
       </c>
       <c r="G299" t="n">
-        <v>0.87</v>
+        <v>0.609</v>
       </c>
       <c r="H299" t="n">
         <v>1</v>
@@ -14793,13 +14793,13 @@
         <v>11</v>
       </c>
       <c r="F300" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="G300" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H300" t="n">
-        <v>0.742</v>
+        <v>0.538</v>
       </c>
       <c r="I300" t="n">
         <v>1</v>
@@ -14941,13 +14941,13 @@
         <v>15</v>
       </c>
       <c r="F304" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G304" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="H304" t="n">
-        <v>0.451</v>
+        <v>0.527</v>
       </c>
       <c r="I304" t="n">
         <v>1</v>
@@ -14978,16 +14978,16 @@
         <v>16</v>
       </c>
       <c r="F305" t="n">
-        <v>0.294</v>
+        <v>0.118</v>
       </c>
       <c r="G305" t="n">
-        <v>0.765</v>
+        <v>0.471</v>
       </c>
       <c r="H305" t="n">
-        <v>0.0149</v>
+        <v>0.057</v>
       </c>
       <c r="I305" t="n">
-        <v>0.239</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="306">
@@ -15061,7 +15061,7 @@
         <v>0.158</v>
       </c>
       <c r="I307" t="n">
-        <v>0.841</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -15126,10 +15126,10 @@
         <v>4</v>
       </c>
       <c r="F309" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="G309" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="H309" t="n">
         <v>1</v>
@@ -15311,16 +15311,16 @@
         <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>0.868</v>
+        <v>0.824</v>
       </c>
       <c r="G314" t="n">
-        <v>0.966</v>
+        <v>0.889</v>
       </c>
       <c r="H314" t="n">
-        <v>0.0837</v>
+        <v>0.409</v>
       </c>
       <c r="I314" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -15348,16 +15348,16 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="G315" t="n">
-        <v>0.909</v>
+        <v>0.737</v>
       </c>
       <c r="H315" t="n">
-        <v>0.234</v>
+        <v>0.626</v>
       </c>
       <c r="I315" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -15385,13 +15385,13 @@
         <v>11</v>
       </c>
       <c r="F316" t="n">
-        <v>0.833</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G316" t="n">
-        <v>0.8</v>
+        <v>0.744</v>
       </c>
       <c r="H316" t="n">
-        <v>0.79</v>
+        <v>0.613</v>
       </c>
       <c r="I316" t="n">
         <v>1</v>
@@ -15533,16 +15533,16 @@
         <v>15</v>
       </c>
       <c r="F320" t="n">
-        <v>0.737</v>
+        <v>0.5</v>
       </c>
       <c r="G320" t="n">
-        <v>0.85</v>
+        <v>0.647</v>
       </c>
       <c r="H320" t="n">
-        <v>0.268</v>
+        <v>0.319</v>
       </c>
       <c r="I320" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -15570,16 +15570,16 @@
         <v>16</v>
       </c>
       <c r="F321" t="n">
-        <v>0.37</v>
+        <v>0.167</v>
       </c>
       <c r="G321" t="n">
-        <v>0.743</v>
+        <v>0.533</v>
       </c>
       <c r="H321" t="n">
-        <v>0.00447</v>
+        <v>0.00991</v>
       </c>
       <c r="I321" t="n">
-        <v>0.0716</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="322">
@@ -15903,13 +15903,13 @@
         <v>9</v>
       </c>
       <c r="F330" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G330" t="n">
-        <v>0.7</v>
+        <v>0.633</v>
       </c>
       <c r="H330" t="n">
-        <v>0.552</v>
+        <v>0.399</v>
       </c>
       <c r="I330" t="n">
         <v>1</v>
@@ -15940,13 +15940,13 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="G331" t="n">
         <v>0.833</v>
       </c>
-      <c r="G331" t="n">
-        <v>0.9</v>
-      </c>
       <c r="H331" t="n">
-        <v>0.706</v>
+        <v>0.748</v>
       </c>
       <c r="I331" t="n">
         <v>1</v>
@@ -15977,13 +15977,13 @@
         <v>11</v>
       </c>
       <c r="F332" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G332" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H332" t="n">
-        <v>0.779</v>
+        <v>0.785</v>
       </c>
       <c r="I332" t="n">
         <v>1</v>
@@ -16125,7 +16125,7 @@
         <v>15</v>
       </c>
       <c r="F336" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G336" t="n">
         <v>0.667</v>
@@ -16162,13 +16162,13 @@
         <v>16</v>
       </c>
       <c r="F337" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="G337" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H337" t="n">
-        <v>0.796</v>
+        <v>0.422</v>
       </c>
       <c r="I337" t="n">
         <v>1</v>
@@ -16535,7 +16535,7 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0.955</v>
+        <v>0.95</v>
       </c>
       <c r="H347" t="n">
         <v>1</v>
@@ -16569,10 +16569,10 @@
         <v>11</v>
       </c>
       <c r="F348" t="n">
-        <v>0.895</v>
+        <v>0.889</v>
       </c>
       <c r="G348" t="n">
-        <v>0.905</v>
+        <v>0.9</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -16717,7 +16717,7 @@
         <v>15</v>
       </c>
       <c r="F352" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G352" t="n">
         <v>0.679</v>
@@ -16754,13 +16754,13 @@
         <v>16</v>
       </c>
       <c r="F353" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="G353" t="n">
-        <v>0.538</v>
+        <v>0.4</v>
       </c>
       <c r="H353" t="n">
-        <v>0.783</v>
+        <v>0.751</v>
       </c>
       <c r="I353" t="n">
         <v>1</v>
@@ -17087,13 +17087,13 @@
         <v>9</v>
       </c>
       <c r="F362" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G362" t="n">
-        <v>0.7</v>
+        <v>0.633</v>
       </c>
       <c r="H362" t="n">
-        <v>0.552</v>
+        <v>0.399</v>
       </c>
       <c r="I362" t="n">
         <v>1</v>
@@ -17124,13 +17124,13 @@
         <v>10</v>
       </c>
       <c r="F363" t="n">
-        <v>0.783</v>
+        <v>0.696</v>
       </c>
       <c r="G363" t="n">
-        <v>0.913</v>
+        <v>0.826</v>
       </c>
       <c r="H363" t="n">
-        <v>0.414</v>
+        <v>0.491</v>
       </c>
       <c r="I363" t="n">
         <v>1</v>
@@ -17161,13 +17161,13 @@
         <v>11</v>
       </c>
       <c r="F364" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G364" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H364" t="n">
-        <v>0.754</v>
+        <v>0.762</v>
       </c>
       <c r="I364" t="n">
         <v>1</v>
@@ -17309,13 +17309,13 @@
         <v>15</v>
       </c>
       <c r="F368" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G368" t="n">
         <v>0.95</v>
       </c>
       <c r="H368" t="n">
-        <v>1</v>
+        <v>0.605</v>
       </c>
       <c r="I368" t="n">
         <v>1</v>
@@ -17346,13 +17346,13 @@
         <v>16</v>
       </c>
       <c r="F369" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="G369" t="n">
-        <v>0.824</v>
+        <v>0.471</v>
       </c>
       <c r="H369" t="n">
-        <v>1</v>
+        <v>0.732</v>
       </c>
       <c r="I369" t="n">
         <v>1</v>
@@ -17679,13 +17679,13 @@
         <v>9</v>
       </c>
       <c r="F378" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="G378" t="n">
-        <v>0.824</v>
+        <v>0.776</v>
       </c>
       <c r="H378" t="n">
-        <v>0.409</v>
+        <v>0.3</v>
       </c>
       <c r="I378" t="n">
         <v>1</v>
@@ -17716,13 +17716,13 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.878</v>
+        <v>0.821</v>
       </c>
       <c r="G379" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.884</v>
       </c>
       <c r="H379" t="n">
-        <v>0.47</v>
+        <v>0.536</v>
       </c>
       <c r="I379" t="n">
         <v>1</v>
@@ -17753,13 +17753,13 @@
         <v>11</v>
       </c>
       <c r="F380" t="n">
-        <v>0.773</v>
+        <v>0.744</v>
       </c>
       <c r="G380" t="n">
-        <v>0.826</v>
+        <v>0.8</v>
       </c>
       <c r="H380" t="n">
-        <v>0.603</v>
+        <v>0.615</v>
       </c>
       <c r="I380" t="n">
         <v>1</v>
@@ -17901,13 +17901,13 @@
         <v>15</v>
       </c>
       <c r="F384" t="n">
-        <v>0.783</v>
+        <v>0.756</v>
       </c>
       <c r="G384" t="n">
         <v>0.792</v>
       </c>
       <c r="H384" t="n">
-        <v>1</v>
+        <v>0.805</v>
       </c>
       <c r="I384" t="n">
         <v>1</v>
@@ -17938,13 +17938,13 @@
         <v>16</v>
       </c>
       <c r="F385" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="G385" t="n">
-        <v>0.651</v>
+        <v>0.432</v>
       </c>
       <c r="H385" t="n">
-        <v>0.819</v>
+        <v>0.486</v>
       </c>
       <c r="I385" t="n">
         <v>1</v>
@@ -18271,10 +18271,10 @@
         <v>9</v>
       </c>
       <c r="F394" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G394" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="H394" t="n">
         <v>1</v>
@@ -18308,13 +18308,13 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G395" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="H395" t="n">
-        <v>0.748</v>
+        <v>0.771</v>
       </c>
       <c r="I395" t="n">
         <v>1</v>
@@ -18345,10 +18345,10 @@
         <v>11</v>
       </c>
       <c r="F396" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G396" t="n">
         <v>0.667</v>
-      </c>
-      <c r="G396" t="n">
-        <v>0.7</v>
       </c>
       <c r="H396" t="n">
         <v>1</v>
@@ -18493,7 +18493,7 @@
         <v>15</v>
       </c>
       <c r="F400" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G400" t="n">
         <v>0.667</v>
@@ -18530,13 +18530,13 @@
         <v>16</v>
       </c>
       <c r="F401" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="G401" t="n">
-        <v>0.533</v>
+        <v>0.367</v>
       </c>
       <c r="H401" t="n">
-        <v>1</v>
+        <v>0.792</v>
       </c>
       <c r="I401" t="n">
         <v>1</v>
@@ -18903,7 +18903,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.864</v>
+        <v>0.85</v>
       </c>
       <c r="H411" t="n">
         <v>0.238</v>
@@ -18937,10 +18937,10 @@
         <v>11</v>
       </c>
       <c r="F412" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="G412" t="n">
         <v>0.895</v>
-      </c>
-      <c r="G412" t="n">
-        <v>0.9</v>
       </c>
       <c r="H412" t="n">
         <v>1</v>
@@ -19085,7 +19085,7 @@
         <v>15</v>
       </c>
       <c r="F416" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G416" t="n">
         <v>0.679</v>
@@ -19122,10 +19122,10 @@
         <v>16</v>
       </c>
       <c r="F417" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="G417" t="n">
-        <v>0.556</v>
+        <v>0.455</v>
       </c>
       <c r="H417" t="n">
         <v>1</v>
@@ -19455,10 +19455,10 @@
         <v>9</v>
       </c>
       <c r="F426" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G426" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="H426" t="n">
         <v>1</v>
@@ -19492,10 +19492,10 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.783</v>
+        <v>0.696</v>
       </c>
       <c r="G427" t="n">
-        <v>0.826</v>
+        <v>0.739</v>
       </c>
       <c r="H427" t="n">
         <v>1</v>
@@ -19529,10 +19529,10 @@
         <v>11</v>
       </c>
       <c r="F428" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G428" t="n">
         <v>0.68</v>
-      </c>
-      <c r="G428" t="n">
-        <v>0.72</v>
       </c>
       <c r="H428" t="n">
         <v>1</v>
@@ -19677,13 +19677,13 @@
         <v>15</v>
       </c>
       <c r="F432" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G432" t="n">
         <v>0.95</v>
       </c>
       <c r="H432" t="n">
-        <v>1</v>
+        <v>0.605</v>
       </c>
       <c r="I432" t="n">
         <v>1</v>
@@ -19714,10 +19714,10 @@
         <v>16</v>
       </c>
       <c r="F433" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="G433" t="n">
-        <v>0.882</v>
+        <v>0.588</v>
       </c>
       <c r="H433" t="n">
         <v>1</v>
@@ -20047,13 +20047,13 @@
         <v>9</v>
       </c>
       <c r="F442" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="G442" t="n">
-        <v>0.889</v>
+        <v>0.846</v>
       </c>
       <c r="H442" t="n">
-        <v>1</v>
+        <v>0.787</v>
       </c>
       <c r="I442" t="n">
         <v>1</v>
@@ -20084,13 +20084,13 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.878</v>
+        <v>0.821</v>
       </c>
       <c r="G443" t="n">
-        <v>0.844</v>
+        <v>0.791</v>
       </c>
       <c r="H443" t="n">
-        <v>0.76</v>
+        <v>0.786</v>
       </c>
       <c r="I443" t="n">
         <v>1</v>
@@ -20121,13 +20121,13 @@
         <v>11</v>
       </c>
       <c r="F444" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="G444" t="n">
         <v>0.773</v>
       </c>
-      <c r="G444" t="n">
-        <v>0.8</v>
-      </c>
       <c r="H444" t="n">
-        <v>0.8</v>
+        <v>0.806</v>
       </c>
       <c r="I444" t="n">
         <v>1</v>
@@ -20269,13 +20269,13 @@
         <v>15</v>
       </c>
       <c r="F448" t="n">
-        <v>0.783</v>
+        <v>0.756</v>
       </c>
       <c r="G448" t="n">
         <v>0.792</v>
       </c>
       <c r="H448" t="n">
-        <v>1</v>
+        <v>0.805</v>
       </c>
       <c r="I448" t="n">
         <v>1</v>
@@ -20306,13 +20306,13 @@
         <v>16</v>
       </c>
       <c r="F449" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="G449" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.513</v>
       </c>
       <c r="H449" t="n">
-        <v>1</v>
+        <v>0.823</v>
       </c>
       <c r="I449" t="n">
         <v>1</v>
@@ -20639,10 +20639,10 @@
         <v>9</v>
       </c>
       <c r="F458" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G458" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="H458" t="n">
         <v>1</v>
@@ -20676,13 +20676,13 @@
         <v>10</v>
       </c>
       <c r="F459" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G459" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="H459" t="n">
-        <v>0.748</v>
+        <v>1</v>
       </c>
       <c r="I459" t="n">
         <v>1</v>
@@ -20713,10 +20713,10 @@
         <v>11</v>
       </c>
       <c r="F460" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G460" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="H460" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>15</v>
       </c>
       <c r="F464" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G464" t="n">
         <v>0.633</v>
@@ -20898,13 +20898,13 @@
         <v>16</v>
       </c>
       <c r="F465" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="G465" t="n">
-        <v>0.533</v>
+        <v>0.367</v>
       </c>
       <c r="H465" t="n">
-        <v>1</v>
+        <v>0.792</v>
       </c>
       <c r="I465" t="n">
         <v>1</v>
@@ -21271,10 +21271,10 @@
         <v>1</v>
       </c>
       <c r="G475" t="n">
-        <v>0.864</v>
+        <v>0.857</v>
       </c>
       <c r="H475" t="n">
-        <v>0.238</v>
+        <v>0.243</v>
       </c>
       <c r="I475" t="n">
         <v>1</v>
@@ -21305,10 +21305,10 @@
         <v>11</v>
       </c>
       <c r="F476" t="n">
-        <v>0.895</v>
+        <v>0.889</v>
       </c>
       <c r="G476" t="n">
-        <v>0.85</v>
+        <v>0.842</v>
       </c>
       <c r="H476" t="n">
         <v>1</v>
@@ -21453,7 +21453,7 @@
         <v>15</v>
       </c>
       <c r="F480" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G480" t="n">
         <v>0.68</v>
@@ -21490,10 +21490,10 @@
         <v>16</v>
       </c>
       <c r="F481" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="G481" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="H481" t="n">
         <v>1</v>
@@ -21823,10 +21823,10 @@
         <v>9</v>
       </c>
       <c r="F490" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G490" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="H490" t="n">
         <v>1</v>
@@ -21860,13 +21860,13 @@
         <v>10</v>
       </c>
       <c r="F491" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="G491" t="n">
         <v>0.783</v>
       </c>
-      <c r="G491" t="n">
-        <v>0.826</v>
-      </c>
       <c r="H491" t="n">
-        <v>1</v>
+        <v>0.738</v>
       </c>
       <c r="I491" t="n">
         <v>1</v>
@@ -21897,10 +21897,10 @@
         <v>11</v>
       </c>
       <c r="F492" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G492" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H492" t="n">
         <v>1</v>
@@ -22045,7 +22045,7 @@
         <v>15</v>
       </c>
       <c r="F496" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G496" t="n">
         <v>0.85</v>
@@ -22082,10 +22082,10 @@
         <v>16</v>
       </c>
       <c r="F497" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="G497" t="n">
-        <v>0.824</v>
+        <v>0.529</v>
       </c>
       <c r="H497" t="n">
         <v>1</v>
@@ -22415,10 +22415,10 @@
         <v>9</v>
       </c>
       <c r="F506" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="G506" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="H506" t="n">
         <v>1</v>
@@ -22452,13 +22452,13 @@
         <v>10</v>
       </c>
       <c r="F507" t="n">
-        <v>0.878</v>
+        <v>0.821</v>
       </c>
       <c r="G507" t="n">
-        <v>0.844</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H507" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="I507" t="n">
         <v>1</v>
@@ -22489,10 +22489,10 @@
         <v>11</v>
       </c>
       <c r="F508" t="n">
-        <v>0.773</v>
+        <v>0.744</v>
       </c>
       <c r="G508" t="n">
-        <v>0.756</v>
+        <v>0.727</v>
       </c>
       <c r="H508" t="n">
         <v>1</v>
@@ -22637,13 +22637,13 @@
         <v>15</v>
       </c>
       <c r="F512" t="n">
-        <v>0.783</v>
+        <v>0.756</v>
       </c>
       <c r="G512" t="n">
         <v>0.756</v>
       </c>
       <c r="H512" t="n">
-        <v>0.8070000000000001</v>
+        <v>1</v>
       </c>
       <c r="I512" t="n">
         <v>1</v>
@@ -22674,13 +22674,13 @@
         <v>16</v>
       </c>
       <c r="F513" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="G513" t="n">
-        <v>0.667</v>
+        <v>0.486</v>
       </c>
       <c r="H513" t="n">
-        <v>1</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="I513" t="n">
         <v>1</v>
@@ -23007,10 +23007,10 @@
         <v>9</v>
       </c>
       <c r="F522" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G522" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="H522" t="n">
         <v>1</v>
@@ -23044,10 +23044,10 @@
         <v>10</v>
       </c>
       <c r="F523" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G523" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="H523" t="n">
         <v>1</v>
@@ -23081,10 +23081,10 @@
         <v>11</v>
       </c>
       <c r="F524" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G524" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="H524" t="n">
         <v>1</v>
@@ -23229,7 +23229,7 @@
         <v>15</v>
       </c>
       <c r="F528" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G528" t="n">
         <v>0.633</v>
@@ -23266,13 +23266,13 @@
         <v>16</v>
       </c>
       <c r="F529" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="G529" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H529" t="n">
-        <v>0.796</v>
+        <v>0.422</v>
       </c>
       <c r="I529" t="n">
         <v>1</v>
@@ -23639,7 +23639,7 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0.947</v>
+        <v>0.944</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -23673,10 +23673,10 @@
         <v>11</v>
       </c>
       <c r="F540" t="n">
-        <v>0.895</v>
+        <v>0.889</v>
       </c>
       <c r="G540" t="n">
-        <v>0.85</v>
+        <v>0.842</v>
       </c>
       <c r="H540" t="n">
         <v>1</v>
@@ -23821,7 +23821,7 @@
         <v>15</v>
       </c>
       <c r="F544" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G544" t="n">
         <v>0.655</v>
@@ -23858,13 +23858,13 @@
         <v>16</v>
       </c>
       <c r="F545" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="G545" t="n">
-        <v>0.536</v>
+        <v>0.409</v>
       </c>
       <c r="H545" t="n">
-        <v>0.785</v>
+        <v>0.757</v>
       </c>
       <c r="I545" t="n">
         <v>1</v>
@@ -24191,10 +24191,10 @@
         <v>9</v>
       </c>
       <c r="F554" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G554" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="H554" t="n">
         <v>1</v>
@@ -24228,10 +24228,10 @@
         <v>10</v>
       </c>
       <c r="F555" t="n">
-        <v>0.783</v>
+        <v>0.696</v>
       </c>
       <c r="G555" t="n">
-        <v>0.783</v>
+        <v>0.739</v>
       </c>
       <c r="H555" t="n">
         <v>1</v>
@@ -24265,10 +24265,10 @@
         <v>11</v>
       </c>
       <c r="F556" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G556" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H556" t="n">
         <v>1</v>
@@ -24413,13 +24413,13 @@
         <v>15</v>
       </c>
       <c r="F560" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G560" t="n">
         <v>0.95</v>
       </c>
       <c r="H560" t="n">
-        <v>1</v>
+        <v>0.605</v>
       </c>
       <c r="I560" t="n">
         <v>1</v>
@@ -24450,10 +24450,10 @@
         <v>16</v>
       </c>
       <c r="F561" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="G561" t="n">
-        <v>0.882</v>
+        <v>0.529</v>
       </c>
       <c r="H561" t="n">
         <v>1</v>
@@ -24783,13 +24783,13 @@
         <v>9</v>
       </c>
       <c r="F570" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="G570" t="n">
-        <v>0.868</v>
+        <v>0.846</v>
       </c>
       <c r="H570" t="n">
-        <v>0.776</v>
+        <v>0.787</v>
       </c>
       <c r="I570" t="n">
         <v>1</v>
@@ -24820,10 +24820,10 @@
         <v>10</v>
       </c>
       <c r="F571" t="n">
-        <v>0.878</v>
+        <v>0.821</v>
       </c>
       <c r="G571" t="n">
-        <v>0.857</v>
+        <v>0.829</v>
       </c>
       <c r="H571" t="n">
         <v>1</v>
@@ -24857,10 +24857,10 @@
         <v>11</v>
       </c>
       <c r="F572" t="n">
-        <v>0.773</v>
+        <v>0.744</v>
       </c>
       <c r="G572" t="n">
-        <v>0.756</v>
+        <v>0.727</v>
       </c>
       <c r="H572" t="n">
         <v>1</v>
@@ -25005,7 +25005,7 @@
         <v>15</v>
       </c>
       <c r="F576" t="n">
-        <v>0.783</v>
+        <v>0.756</v>
       </c>
       <c r="G576" t="n">
         <v>0.776</v>
@@ -25042,13 +25042,13 @@
         <v>16</v>
       </c>
       <c r="F577" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="G577" t="n">
-        <v>0.667</v>
+        <v>0.462</v>
       </c>
       <c r="H577" t="n">
-        <v>1</v>
+        <v>0.647</v>
       </c>
       <c r="I577" t="n">
         <v>1</v>
@@ -25375,13 +25375,13 @@
         <v>9</v>
       </c>
       <c r="F586" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G586" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="H586" t="n">
-        <v>0.158</v>
+        <v>0.103</v>
       </c>
       <c r="I586" t="n">
         <v>1</v>
@@ -25412,13 +25412,13 @@
         <v>10</v>
       </c>
       <c r="F587" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G587" t="n">
         <v>0.7</v>
       </c>
       <c r="H587" t="n">
-        <v>0.36</v>
+        <v>0.771</v>
       </c>
       <c r="I587" t="n">
         <v>1</v>
@@ -25449,13 +25449,13 @@
         <v>11</v>
       </c>
       <c r="F588" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G588" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H588" t="n">
-        <v>0.789</v>
+        <v>0.792</v>
       </c>
       <c r="I588" t="n">
         <v>1</v>
@@ -25597,7 +25597,7 @@
         <v>15</v>
       </c>
       <c r="F592" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G592" t="n">
         <v>0.633</v>
@@ -25634,13 +25634,13 @@
         <v>16</v>
       </c>
       <c r="F593" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="G593" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="H593" t="n">
-        <v>0.596</v>
+        <v>0.195</v>
       </c>
       <c r="I593" t="n">
         <v>1</v>
@@ -26041,10 +26041,10 @@
         <v>11</v>
       </c>
       <c r="F604" t="n">
-        <v>0.895</v>
+        <v>0.889</v>
       </c>
       <c r="G604" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.929</v>
       </c>
       <c r="H604" t="n">
         <v>1</v>
@@ -26189,7 +26189,7 @@
         <v>15</v>
       </c>
       <c r="F608" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G608" t="n">
         <v>0.696</v>
@@ -26226,13 +26226,13 @@
         <v>16</v>
       </c>
       <c r="F609" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="G609" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="H609" t="n">
-        <v>0.542</v>
+        <v>0.342</v>
       </c>
       <c r="I609" t="n">
         <v>1</v>
@@ -26272,7 +26272,7 @@
         <v>0.348</v>
       </c>
       <c r="I610" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="611">
@@ -26309,7 +26309,7 @@
         <v>0.4</v>
       </c>
       <c r="I611" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="612">
@@ -26383,7 +26383,7 @@
         <v>0.462</v>
       </c>
       <c r="I613" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="614">
@@ -26494,7 +26494,7 @@
         <v>0.23</v>
       </c>
       <c r="I616" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="617">
@@ -26559,16 +26559,16 @@
         <v>9</v>
       </c>
       <c r="F618" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G618" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="H618" t="n">
-        <v>0.158</v>
+        <v>0.103</v>
       </c>
       <c r="I618" t="n">
-        <v>0.923</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="619">
@@ -26596,16 +26596,16 @@
         <v>10</v>
       </c>
       <c r="F619" t="n">
-        <v>0.783</v>
+        <v>0.696</v>
       </c>
       <c r="G619" t="n">
         <v>0.609</v>
       </c>
       <c r="H619" t="n">
-        <v>0.337</v>
+        <v>0.758</v>
       </c>
       <c r="I619" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="620">
@@ -26633,16 +26633,16 @@
         <v>11</v>
       </c>
       <c r="F620" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G620" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H620" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I620" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="621">
@@ -26753,7 +26753,7 @@
         <v>0.407</v>
       </c>
       <c r="I623" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="624">
@@ -26781,13 +26781,13 @@
         <v>15</v>
       </c>
       <c r="F624" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G624" t="n">
         <v>0.8</v>
       </c>
       <c r="H624" t="n">
-        <v>0.661</v>
+        <v>1</v>
       </c>
       <c r="I624" t="n">
         <v>1</v>
@@ -26818,13 +26818,13 @@
         <v>16</v>
       </c>
       <c r="F625" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="G625" t="n">
-        <v>0.765</v>
+        <v>0.706</v>
       </c>
       <c r="H625" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
       <c r="I625" t="n">
         <v>1</v>
@@ -26975,7 +26975,7 @@
         <v>0.203</v>
       </c>
       <c r="I629" t="n">
-        <v>0.762</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="630">
@@ -27151,16 +27151,16 @@
         <v>9</v>
       </c>
       <c r="F634" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="G634" t="n">
-        <v>0.75</v>
+        <v>0.696</v>
       </c>
       <c r="H634" t="n">
-        <v>0.075</v>
+        <v>0.0489</v>
       </c>
       <c r="I634" t="n">
-        <v>0.547</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="635">
@@ -27188,16 +27188,16 @@
         <v>10</v>
       </c>
       <c r="F635" t="n">
-        <v>0.878</v>
+        <v>0.821</v>
       </c>
       <c r="G635" t="n">
         <v>0.757</v>
       </c>
       <c r="H635" t="n">
-        <v>0.238</v>
+        <v>0.579</v>
       </c>
       <c r="I635" t="n">
-        <v>0.762</v>
+        <v>1</v>
       </c>
     </row>
     <row r="636">
@@ -27225,13 +27225,13 @@
         <v>11</v>
       </c>
       <c r="F636" t="n">
-        <v>0.773</v>
+        <v>0.744</v>
       </c>
       <c r="G636" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H636" t="n">
-        <v>0.468</v>
+        <v>0.475</v>
       </c>
       <c r="I636" t="n">
         <v>1</v>
@@ -27373,13 +27373,13 @@
         <v>15</v>
       </c>
       <c r="F640" t="n">
-        <v>0.783</v>
+        <v>0.756</v>
       </c>
       <c r="G640" t="n">
         <v>0.744</v>
       </c>
       <c r="H640" t="n">
-        <v>0.804</v>
+        <v>1</v>
       </c>
       <c r="I640" t="n">
         <v>1</v>
@@ -27410,16 +27410,16 @@
         <v>16</v>
       </c>
       <c r="F641" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="G641" t="n">
-        <v>0.722</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H641" t="n">
-        <v>0.805</v>
+        <v>0.235</v>
       </c>
       <c r="I641" t="n">
-        <v>1</v>
+        <v>0.751</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -678,7 +678,7 @@
         <v>0.127</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="7">
@@ -758,7 +758,7 @@
         <v>0.216</v>
       </c>
       <c r="J8" t="n">
-        <v>0.889</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="9">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="F10" t="n">
         <v>0.781</v>
       </c>
       <c r="G10" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="H10" t="n">
         <v>0.172</v>
       </c>
       <c r="I10" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="J10" t="n">
-        <v>0.902</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="11">
@@ -869,13 +869,13 @@
         <v>0.781</v>
       </c>
       <c r="G11" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="H11" t="n">
         <v>0.172</v>
       </c>
       <c r="I11" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="J11" t="n">
         <v>0.705</v>
@@ -918,7 +918,7 @@
         <v>0.181</v>
       </c>
       <c r="J12" t="n">
-        <v>0.889</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="13">
@@ -1078,7 +1078,7 @@
         <v>0.224</v>
       </c>
       <c r="J16" t="n">
-        <v>0.889</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>0.158</v>
       </c>
       <c r="J22" t="n">
-        <v>0.889</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="23">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.323</v>
+        <v>0.271</v>
       </c>
       <c r="F24" t="n">
         <v>0.8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.785</v>
+        <v>0.783</v>
       </c>
       <c r="H24" t="n">
         <v>0.14</v>
       </c>
       <c r="I24" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="25">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.251</v>
+        <v>0.192</v>
       </c>
       <c r="F25" t="n">
         <v>0.8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.785</v>
+        <v>0.783</v>
       </c>
       <c r="H25" t="n">
         <v>0.14</v>
       </c>
       <c r="I25" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="J25" t="n">
-        <v>0.628</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="26">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0222</v>
+        <v>0.013</v>
       </c>
       <c r="F26" t="n">
         <v>0.8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="H26" t="n">
         <v>0.14</v>
@@ -1478,7 +1478,7 @@
         <v>0.158</v>
       </c>
       <c r="J26" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="27">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0259</v>
+        <v>0.015</v>
       </c>
       <c r="F27" t="n">
         <v>0.8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="H27" t="n">
         <v>0.14</v>
@@ -1518,7 +1518,7 @@
         <v>0.158</v>
       </c>
       <c r="J27" t="n">
-        <v>0.161</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="28">
@@ -1543,13 +1543,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0346</v>
+        <v>0.0179</v>
       </c>
       <c r="F28" t="n">
         <v>0.8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="H28" t="n">
         <v>0.14</v>
@@ -1558,7 +1558,7 @@
         <v>0.167</v>
       </c>
       <c r="J28" t="n">
-        <v>0.175</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="29">
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0242</v>
+        <v>0.0176</v>
       </c>
       <c r="F29" t="n">
         <v>0.8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="H29" t="n">
         <v>0.14</v>
@@ -1598,7 +1598,7 @@
         <v>0.167</v>
       </c>
       <c r="J29" t="n">
-        <v>0.161</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="30">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.0286</v>
+        <v>0.0287</v>
       </c>
       <c r="F40" t="n">
         <v>0.8139999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.877</v>
+        <v>0.876</v>
       </c>
       <c r="H40" t="n">
         <v>0.205</v>
@@ -2069,7 +2069,7 @@
         <v>0.8139999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.877</v>
+        <v>0.876</v>
       </c>
       <c r="H41" t="n">
         <v>0.205</v>
@@ -2518,7 +2518,7 @@
         <v>0.171</v>
       </c>
       <c r="J52" t="n">
-        <v>0.504</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="53">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.303</v>
+        <v>0.298</v>
       </c>
       <c r="F54" t="n">
         <v>0.853</v>
       </c>
       <c r="G54" t="n">
-        <v>0.834</v>
+        <v>0.833</v>
       </c>
       <c r="H54" t="n">
         <v>0.13</v>
@@ -2598,7 +2598,7 @@
         <v>0.163</v>
       </c>
       <c r="J54" t="n">
-        <v>0.504</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="55">
@@ -2629,7 +2629,7 @@
         <v>0.853</v>
       </c>
       <c r="G55" t="n">
-        <v>0.834</v>
+        <v>0.833</v>
       </c>
       <c r="H55" t="n">
         <v>0.13</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.336</v>
+        <v>0.33</v>
       </c>
       <c r="F56" t="n">
         <v>0.853</v>
@@ -2678,7 +2678,7 @@
         <v>0.144</v>
       </c>
       <c r="J56" t="n">
-        <v>0.504</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="57">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.134</v>
+        <v>0.132</v>
       </c>
       <c r="F58" t="n">
         <v>0.853</v>
@@ -2758,7 +2758,7 @@
         <v>0.16</v>
       </c>
       <c r="J58" t="n">
-        <v>0.287</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="59">
@@ -2958,7 +2958,7 @@
         <v>0.223</v>
       </c>
       <c r="J63" t="n">
-        <v>0.375</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="64">
@@ -2998,7 +2998,7 @@
         <v>0.291</v>
       </c>
       <c r="J64" t="n">
-        <v>0.532</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="65">
@@ -3038,7 +3038,7 @@
         <v>0.291</v>
       </c>
       <c r="J65" t="n">
-        <v>0.582</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="66">
@@ -3078,7 +3078,7 @@
         <v>0.214</v>
       </c>
       <c r="J66" t="n">
-        <v>0.532</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="67">
@@ -3158,7 +3158,7 @@
         <v>0.304</v>
       </c>
       <c r="J68" t="n">
-        <v>0.332</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="69">
@@ -3223,22 +3223,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.111</v>
+        <v>0.0973</v>
       </c>
       <c r="F70" t="n">
         <v>0.797</v>
       </c>
       <c r="G70" t="n">
-        <v>0.7</v>
+        <v>0.697</v>
       </c>
       <c r="H70" t="n">
         <v>0.225</v>
       </c>
       <c r="I70" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="J70" t="n">
-        <v>0.41</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="71">
@@ -3263,22 +3263,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.125</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="F71" t="n">
         <v>0.797</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7</v>
+        <v>0.697</v>
       </c>
       <c r="H71" t="n">
         <v>0.225</v>
       </c>
       <c r="I71" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="J71" t="n">
-        <v>0.375</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="72">
@@ -3358,7 +3358,7 @@
         <v>0.292</v>
       </c>
       <c r="J73" t="n">
-        <v>0.38</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="74">
@@ -3398,7 +3398,7 @@
         <v>0.184</v>
       </c>
       <c r="J74" t="n">
-        <v>0.829</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="75">
@@ -3438,7 +3438,7 @@
         <v>0.184</v>
       </c>
       <c r="J75" t="n">
-        <v>0.582</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="76">
@@ -3783,13 +3783,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.674</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F84" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>0.804</v>
+        <v>0.801</v>
       </c>
       <c r="H84" t="n">
         <v>0.218</v>
@@ -3798,7 +3798,7 @@
         <v>0.214</v>
       </c>
       <c r="J84" t="n">
-        <v>0.843</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="85">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.789</v>
+        <v>0.722</v>
       </c>
       <c r="F85" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>0.804</v>
+        <v>0.801</v>
       </c>
       <c r="H85" t="n">
         <v>0.218</v>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.0789</v>
+        <v>0.0532</v>
       </c>
       <c r="F86" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>0.766</v>
+        <v>0.763</v>
       </c>
       <c r="H86" t="n">
         <v>0.218</v>
@@ -3878,7 +3878,7 @@
         <v>0.203</v>
       </c>
       <c r="J86" t="n">
-        <v>0.395</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="87">
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0663</v>
+        <v>0.0506</v>
       </c>
       <c r="F87" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>0.766</v>
+        <v>0.763</v>
       </c>
       <c r="H87" t="n">
         <v>0.218</v>
@@ -3918,7 +3918,7 @@
         <v>0.203</v>
       </c>
       <c r="J87" t="n">
-        <v>0.331</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="88">
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.342</v>
+        <v>0.21</v>
       </c>
       <c r="F88" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
       <c r="H88" t="n">
         <v>0.218</v>
@@ -3958,7 +3958,7 @@
         <v>0.216</v>
       </c>
       <c r="J88" t="n">
-        <v>0.532</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="89">
@@ -3983,13 +3983,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.374</v>
+        <v>0.173</v>
       </c>
       <c r="F89" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
       <c r="H89" t="n">
         <v>0.218</v>
@@ -3998,7 +3998,7 @@
         <v>0.216</v>
       </c>
       <c r="J89" t="n">
-        <v>0.582</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="90">
@@ -4423,19 +4423,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.601</v>
+        <v>0.572</v>
       </c>
       <c r="F100" t="n">
         <v>0.78</v>
       </c>
       <c r="G100" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="H100" t="n">
         <v>0.194</v>
       </c>
       <c r="I100" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="J100" t="n">
         <v>0.775</v>
@@ -4463,19 +4463,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.528</v>
+        <v>0.495</v>
       </c>
       <c r="F101" t="n">
         <v>0.78</v>
       </c>
       <c r="G101" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="H101" t="n">
         <v>0.194</v>
       </c>
       <c r="I101" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="J101" t="n">
         <v>0.861</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.463</v>
+        <v>0.401</v>
       </c>
       <c r="F114" t="n">
         <v>0.803</v>
       </c>
       <c r="G114" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="H114" t="n">
         <v>0.165</v>
@@ -5023,13 +5023,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.754</v>
+        <v>0.695</v>
       </c>
       <c r="F115" t="n">
         <v>0.803</v>
       </c>
       <c r="G115" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="H115" t="n">
         <v>0.165</v>
@@ -5063,22 +5063,22 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.0771</v>
+        <v>0.0575</v>
       </c>
       <c r="F116" t="n">
         <v>0.803</v>
       </c>
       <c r="G116" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="H116" t="n">
         <v>0.165</v>
       </c>
       <c r="I116" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="J116" t="n">
-        <v>0.386</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="117">
@@ -5103,22 +5103,22 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.0597</v>
+        <v>0.0414</v>
       </c>
       <c r="F117" t="n">
         <v>0.803</v>
       </c>
       <c r="G117" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="H117" t="n">
         <v>0.165</v>
       </c>
       <c r="I117" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="J117" t="n">
-        <v>0.299</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="118">
@@ -5143,22 +5143,22 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.0461</v>
+        <v>0.0235</v>
       </c>
       <c r="F118" t="n">
         <v>0.803</v>
       </c>
       <c r="G118" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="H118" t="n">
         <v>0.165</v>
       </c>
       <c r="I118" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="J118" t="n">
-        <v>0.346</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="119">
@@ -5183,22 +5183,22 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.0414</v>
+        <v>0.0186</v>
       </c>
       <c r="F119" t="n">
         <v>0.803</v>
       </c>
       <c r="G119" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="H119" t="n">
         <v>0.165</v>
       </c>
       <c r="I119" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="J119" t="n">
-        <v>0.299</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="120">
@@ -5238,7 +5238,7 @@
         <v>0.191</v>
       </c>
       <c r="J120" t="n">
-        <v>0.346</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="121">
@@ -5278,7 +5278,7 @@
         <v>0.191</v>
       </c>
       <c r="J121" t="n">
-        <v>0.299</v>
+        <v>0.201</v>
       </c>
     </row>
   </sheetData>
@@ -15175,10 +15175,10 @@
         <v>0.533</v>
       </c>
       <c r="G267" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="H267" t="n">
-        <v>0.103</v>
+        <v>0.18</v>
       </c>
       <c r="I267" t="n">
         <v>1</v>
@@ -15767,10 +15767,10 @@
         <v>0.765</v>
       </c>
       <c r="G283" t="n">
-        <v>0.944</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H283" t="n">
-        <v>0.177</v>
+        <v>0.335</v>
       </c>
       <c r="I283" t="n">
         <v>1</v>
@@ -16032,7 +16032,7 @@
         <v>0.109</v>
       </c>
       <c r="I290" t="n">
-        <v>0.67</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="291">
@@ -16106,7 +16106,7 @@
         <v>0.462</v>
       </c>
       <c r="I292" t="n">
-        <v>0.738</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="293">
@@ -16217,7 +16217,7 @@
         <v>0.343</v>
       </c>
       <c r="I295" t="n">
-        <v>0.67</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="296">
@@ -16291,7 +16291,7 @@
         <v>0.242</v>
       </c>
       <c r="I297" t="n">
-        <v>0.67</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="298">
@@ -16359,13 +16359,13 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="G299" t="n">
-        <v>0.739</v>
+        <v>0.696</v>
       </c>
       <c r="H299" t="n">
-        <v>0.353</v>
+        <v>0.542</v>
       </c>
       <c r="I299" t="n">
-        <v>0.67</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="300">
@@ -16402,7 +16402,7 @@
         <v>0.377</v>
       </c>
       <c r="I300" t="n">
-        <v>0.67</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="301">
@@ -16439,7 +16439,7 @@
         <v>0.232</v>
       </c>
       <c r="I301" t="n">
-        <v>0.67</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="302">
@@ -16513,7 +16513,7 @@
         <v>0.342</v>
       </c>
       <c r="I303" t="n">
-        <v>0.67</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="304">
@@ -16550,7 +16550,7 @@
         <v>0.273</v>
       </c>
       <c r="I304" t="n">
-        <v>0.67</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="305">
@@ -16883,7 +16883,7 @@
         <v>0.0584</v>
       </c>
       <c r="I313" t="n">
-        <v>0.425</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="314">
@@ -16951,13 +16951,13 @@
         <v>0.65</v>
       </c>
       <c r="G315" t="n">
-        <v>0.829</v>
+        <v>0.8</v>
       </c>
       <c r="H315" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="I315" t="n">
-        <v>0.425</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="316">
@@ -31751,10 +31751,10 @@
         <v>0.767</v>
       </c>
       <c r="G715" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H715" t="n">
-        <v>1</v>
+        <v>0.771</v>
       </c>
       <c r="I715" t="n">
         <v>1</v>
@@ -32343,10 +32343,10 @@
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="H731" t="n">
-        <v>0.243</v>
+        <v>0.238</v>
       </c>
       <c r="I731" t="n">
         <v>1</v>
@@ -32935,10 +32935,10 @@
         <v>0.696</v>
       </c>
       <c r="G747" t="n">
-        <v>0.783</v>
+        <v>0.739</v>
       </c>
       <c r="H747" t="n">
-        <v>0.738</v>
+        <v>1</v>
       </c>
       <c r="I747" t="n">
         <v>1</v>
@@ -33527,10 +33527,10 @@
         <v>0.821</v>
       </c>
       <c r="G763" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.791</v>
       </c>
       <c r="H763" t="n">
-        <v>1</v>
+        <v>0.786</v>
       </c>
       <c r="I763" t="n">
         <v>1</v>
@@ -34119,7 +34119,7 @@
         <v>0.767</v>
       </c>
       <c r="G779" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="H779" t="n">
         <v>1</v>
@@ -34711,10 +34711,10 @@
         <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>0.864</v>
+        <v>0.857</v>
       </c>
       <c r="H795" t="n">
-        <v>0.249</v>
+        <v>0.243</v>
       </c>
       <c r="I795" t="n">
         <v>1</v>
@@ -35303,10 +35303,10 @@
         <v>0.696</v>
       </c>
       <c r="G811" t="n">
-        <v>0.826</v>
+        <v>0.783</v>
       </c>
       <c r="H811" t="n">
-        <v>0.491</v>
+        <v>0.738</v>
       </c>
       <c r="I811" t="n">
         <v>1</v>
@@ -35895,10 +35895,10 @@
         <v>0.821</v>
       </c>
       <c r="G827" t="n">
-        <v>0.844</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H827" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="I827" t="n">
         <v>1</v>
@@ -36487,7 +36487,7 @@
         <v>0.767</v>
       </c>
       <c r="G843" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="H843" t="n">
         <v>1</v>
@@ -37079,7 +37079,7 @@
         <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>0.947</v>
+        <v>0.944</v>
       </c>
       <c r="H859" t="n">
         <v>1</v>
@@ -37671,10 +37671,10 @@
         <v>0.696</v>
       </c>
       <c r="G875" t="n">
-        <v>0.783</v>
+        <v>0.739</v>
       </c>
       <c r="H875" t="n">
-        <v>0.738</v>
+        <v>1</v>
       </c>
       <c r="I875" t="n">
         <v>1</v>
@@ -38263,10 +38263,10 @@
         <v>0.821</v>
       </c>
       <c r="G891" t="n">
-        <v>0.857</v>
+        <v>0.829</v>
       </c>
       <c r="H891" t="n">
-        <v>0.766</v>
+        <v>1</v>
       </c>
       <c r="I891" t="n">
         <v>1</v>

--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -558,7 +558,7 @@
         <v>0.141</v>
       </c>
       <c r="J3" t="n">
-        <v>0.833</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
         <v>0.201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.902</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.201</v>
       </c>
       <c r="J5" t="n">
-        <v>0.833</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="6">
@@ -678,7 +678,7 @@
         <v>0.127</v>
       </c>
       <c r="J6" t="n">
-        <v>0.675</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>0.127</v>
       </c>
       <c r="J7" t="n">
-        <v>0.705</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>0.216</v>
       </c>
       <c r="J8" t="n">
-        <v>0.845</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.216</v>
       </c>
       <c r="J9" t="n">
-        <v>0.833</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +838,7 @@
         <v>0.138</v>
       </c>
       <c r="J10" t="n">
-        <v>0.845</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         <v>0.138</v>
       </c>
       <c r="J11" t="n">
-        <v>0.705</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="12">
@@ -918,7 +918,7 @@
         <v>0.181</v>
       </c>
       <c r="J12" t="n">
-        <v>0.845</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="13">
@@ -958,7 +958,7 @@
         <v>0.181</v>
       </c>
       <c r="J13" t="n">
-        <v>0.833</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="14">
@@ -998,7 +998,7 @@
         <v>0.117</v>
       </c>
       <c r="J14" t="n">
-        <v>0.804</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="15">
@@ -1078,7 +1078,7 @@
         <v>0.224</v>
       </c>
       <c r="J16" t="n">
-        <v>0.845</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="17">
@@ -1158,7 +1158,7 @@
         <v>0.146</v>
       </c>
       <c r="J18" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="19">
@@ -1238,7 +1238,7 @@
         <v>0.101</v>
       </c>
       <c r="J20" t="n">
-        <v>0.175</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="21">
@@ -1278,7 +1278,7 @@
         <v>0.101</v>
       </c>
       <c r="J21" t="n">
-        <v>0.161</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="22">
@@ -1318,7 +1318,7 @@
         <v>0.158</v>
       </c>
       <c r="J22" t="n">
-        <v>0.845</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="23">
@@ -1358,7 +1358,7 @@
         <v>0.158</v>
       </c>
       <c r="J23" t="n">
-        <v>0.833</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="24">
@@ -1398,7 +1398,7 @@
         <v>0.166</v>
       </c>
       <c r="J24" t="n">
-        <v>0.675</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25">
@@ -1438,7 +1438,7 @@
         <v>0.166</v>
       </c>
       <c r="J25" t="n">
-        <v>0.48</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="26">
@@ -1478,7 +1478,7 @@
         <v>0.158</v>
       </c>
       <c r="J26" t="n">
-        <v>0.134</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="27">
@@ -1518,7 +1518,7 @@
         <v>0.158</v>
       </c>
       <c r="J27" t="n">
-        <v>0.132</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="28">
@@ -1558,7 +1558,7 @@
         <v>0.167</v>
       </c>
       <c r="J28" t="n">
-        <v>0.134</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="29">
@@ -1598,7 +1598,7 @@
         <v>0.167</v>
       </c>
       <c r="J29" t="n">
-        <v>0.132</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="30">
@@ -1638,7 +1638,7 @@
         <v>0.124</v>
       </c>
       <c r="J30" t="n">
-        <v>0.315</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="31">
@@ -1678,7 +1678,7 @@
         <v>0.124</v>
       </c>
       <c r="J31" t="n">
-        <v>0.298</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="32">
@@ -1718,7 +1718,7 @@
         <v>0.0921</v>
       </c>
       <c r="J32" t="n">
-        <v>0.165</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="33">
@@ -1758,7 +1758,7 @@
         <v>0.0921</v>
       </c>
       <c r="J33" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="34">
@@ -1798,7 +1798,7 @@
         <v>0.251</v>
       </c>
       <c r="J34" t="n">
-        <v>0.914</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="35">
@@ -1838,7 +1838,7 @@
         <v>0.251</v>
       </c>
       <c r="J35" t="n">
-        <v>0.29</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="36">
@@ -1878,7 +1878,7 @@
         <v>0.104</v>
       </c>
       <c r="J36" t="n">
-        <v>0.175</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="37">
@@ -1918,7 +1918,7 @@
         <v>0.104</v>
       </c>
       <c r="J37" t="n">
-        <v>0.125</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="38">
@@ -1958,7 +1958,7 @@
         <v>0.26</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1998,7 +1998,7 @@
         <v>0.26</v>
       </c>
       <c r="J39" t="n">
-        <v>0.134</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="40">
@@ -2038,7 +2038,7 @@
         <v>0.132</v>
       </c>
       <c r="J40" t="n">
-        <v>0.143</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="41">
@@ -2078,7 +2078,7 @@
         <v>0.132</v>
       </c>
       <c r="J41" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="42">
@@ -2118,7 +2118,7 @@
         <v>0.246</v>
       </c>
       <c r="J42" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="43">
@@ -2158,7 +2158,7 @@
         <v>0.246</v>
       </c>
       <c r="J43" t="n">
-        <v>0.299</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="44">
@@ -2198,7 +2198,7 @@
         <v>0.147</v>
       </c>
       <c r="J44" t="n">
-        <v>0.143</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="45">
@@ -2238,7 +2238,7 @@
         <v>0.147</v>
       </c>
       <c r="J45" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="46">
@@ -2278,7 +2278,7 @@
         <v>0.236</v>
       </c>
       <c r="J46" t="n">
-        <v>0.984</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2318,7 +2318,7 @@
         <v>0.236</v>
       </c>
       <c r="J47" t="n">
-        <v>0.37</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="48">
@@ -2358,7 +2358,7 @@
         <v>0.115</v>
       </c>
       <c r="J48" t="n">
-        <v>0.165</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="49">
@@ -2398,7 +2398,7 @@
         <v>0.115</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0852</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="50">
@@ -2438,7 +2438,7 @@
         <v>0.127</v>
       </c>
       <c r="J50" t="n">
-        <v>0.143</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="51">
@@ -2478,7 +2478,7 @@
         <v>0.127</v>
       </c>
       <c r="J51" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="52">
@@ -2518,7 +2518,7 @@
         <v>0.171</v>
       </c>
       <c r="J52" t="n">
-        <v>0.495</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="53">
@@ -2558,7 +2558,7 @@
         <v>0.171</v>
       </c>
       <c r="J53" t="n">
-        <v>0.463</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="54">
@@ -2598,7 +2598,7 @@
         <v>0.163</v>
       </c>
       <c r="J54" t="n">
-        <v>0.495</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="55">
@@ -2638,7 +2638,7 @@
         <v>0.163</v>
       </c>
       <c r="J55" t="n">
-        <v>0.33</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="56">
@@ -2678,7 +2678,7 @@
         <v>0.144</v>
       </c>
       <c r="J56" t="n">
-        <v>0.495</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="57">
@@ -2718,7 +2718,7 @@
         <v>0.144</v>
       </c>
       <c r="J57" t="n">
-        <v>0.29</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="58">
@@ -2758,7 +2758,7 @@
         <v>0.16</v>
       </c>
       <c r="J58" t="n">
-        <v>0.283</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="59">
@@ -2798,7 +2798,7 @@
         <v>0.16</v>
       </c>
       <c r="J59" t="n">
-        <v>0.258</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="60">
@@ -2838,7 +2838,7 @@
         <v>0.178</v>
       </c>
       <c r="J60" t="n">
-        <v>0.747</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2878,7 +2878,7 @@
         <v>0.178</v>
       </c>
       <c r="J61" t="n">
-        <v>0.134</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="62">
@@ -2918,7 +2918,7 @@
         <v>0.223</v>
       </c>
       <c r="J62" t="n">
-        <v>0.41</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="63">
@@ -2958,7 +2958,7 @@
         <v>0.223</v>
       </c>
       <c r="J63" t="n">
-        <v>0.348</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="64">
@@ -2998,7 +2998,7 @@
         <v>0.291</v>
       </c>
       <c r="J64" t="n">
-        <v>0.518</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="65">
@@ -3038,7 +3038,7 @@
         <v>0.291</v>
       </c>
       <c r="J65" t="n">
-        <v>0.575</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="66">
@@ -3078,7 +3078,7 @@
         <v>0.214</v>
       </c>
       <c r="J66" t="n">
-        <v>0.518</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="67">
@@ -3118,7 +3118,7 @@
         <v>0.214</v>
       </c>
       <c r="J67" t="n">
-        <v>0.582</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="68">
@@ -3158,7 +3158,7 @@
         <v>0.304</v>
       </c>
       <c r="J68" t="n">
-        <v>0.266</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="69">
@@ -3198,7 +3198,7 @@
         <v>0.304</v>
       </c>
       <c r="J69" t="n">
-        <v>0.247</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="70">
@@ -3238,7 +3238,7 @@
         <v>0.184</v>
       </c>
       <c r="J70" t="n">
-        <v>0.365</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="71">
@@ -3278,7 +3278,7 @@
         <v>0.184</v>
       </c>
       <c r="J71" t="n">
-        <v>0.259</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="72">
@@ -3318,7 +3318,7 @@
         <v>0.292</v>
       </c>
       <c r="J72" t="n">
-        <v>0.41</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="73">
@@ -3358,7 +3358,7 @@
         <v>0.292</v>
       </c>
       <c r="J73" t="n">
-        <v>0.371</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="74">
@@ -3398,7 +3398,7 @@
         <v>0.184</v>
       </c>
       <c r="J74" t="n">
-        <v>0.76</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="75">
@@ -3438,7 +3438,7 @@
         <v>0.184</v>
       </c>
       <c r="J75" t="n">
-        <v>0.575</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="76">
@@ -3478,7 +3478,7 @@
         <v>0.281</v>
       </c>
       <c r="J76" t="n">
-        <v>0.532</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="77">
@@ -3518,7 +3518,7 @@
         <v>0.281</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="78">
@@ -3558,7 +3558,7 @@
         <v>0.191</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3598,7 +3598,7 @@
         <v>0.191</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="80">
@@ -3638,7 +3638,7 @@
         <v>0.204</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="81">
@@ -3678,7 +3678,7 @@
         <v>0.204</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="82">
@@ -3718,7 +3718,7 @@
         <v>0.214</v>
       </c>
       <c r="J82" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="83">
@@ -3758,7 +3758,7 @@
         <v>0.214</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="84">
@@ -3798,7 +3798,7 @@
         <v>0.214</v>
       </c>
       <c r="J84" t="n">
-        <v>0.76</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -3838,7 +3838,7 @@
         <v>0.214</v>
       </c>
       <c r="J85" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="86">
@@ -3878,7 +3878,7 @@
         <v>0.203</v>
       </c>
       <c r="J86" t="n">
-        <v>0.266</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="87">
@@ -3918,7 +3918,7 @@
         <v>0.203</v>
       </c>
       <c r="J87" t="n">
-        <v>0.253</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="88">
@@ -3958,7 +3958,7 @@
         <v>0.216</v>
       </c>
       <c r="J88" t="n">
-        <v>0.45</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="89">
@@ -3998,7 +3998,7 @@
         <v>0.216</v>
       </c>
       <c r="J89" t="n">
-        <v>0.371</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="90">
@@ -4038,7 +4038,7 @@
         <v>0.227</v>
       </c>
       <c r="J90" t="n">
-        <v>0.104</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="91">
@@ -4078,7 +4078,7 @@
         <v>0.227</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0333</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="92">
@@ -4118,7 +4118,7 @@
         <v>0.13</v>
       </c>
       <c r="J92" t="n">
-        <v>0.911</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="93">
@@ -4158,7 +4158,7 @@
         <v>0.13</v>
       </c>
       <c r="J93" t="n">
-        <v>0.861</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="94">
@@ -4198,7 +4198,7 @@
         <v>0.264</v>
       </c>
       <c r="J94" t="n">
-        <v>0.786</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="95">
@@ -4278,7 +4278,7 @@
         <v>0.144</v>
       </c>
       <c r="J96" t="n">
-        <v>0.775</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -4318,7 +4318,7 @@
         <v>0.144</v>
       </c>
       <c r="J97" t="n">
-        <v>0.861</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="98">
@@ -4358,7 +4358,7 @@
         <v>0.276</v>
       </c>
       <c r="J98" t="n">
-        <v>0.735</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="99">
@@ -4398,7 +4398,7 @@
         <v>0.276</v>
       </c>
       <c r="J99" t="n">
-        <v>0.861</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="100">
@@ -4438,7 +4438,7 @@
         <v>0.149</v>
       </c>
       <c r="J100" t="n">
-        <v>0.775</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -4478,7 +4478,7 @@
         <v>0.149</v>
       </c>
       <c r="J101" t="n">
-        <v>0.861</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="102">
@@ -4518,7 +4518,7 @@
         <v>0.258</v>
       </c>
       <c r="J102" t="n">
-        <v>0.775</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -4558,7 +4558,7 @@
         <v>0.258</v>
       </c>
       <c r="J103" t="n">
-        <v>0.861</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="104">
@@ -4598,7 +4598,7 @@
         <v>0.121</v>
       </c>
       <c r="J104" t="n">
-        <v>0.775</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="105">
@@ -4638,7 +4638,7 @@
         <v>0.121</v>
       </c>
       <c r="J105" t="n">
-        <v>0.861</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="106">
@@ -4678,7 +4678,7 @@
         <v>0.241</v>
       </c>
       <c r="J106" t="n">
-        <v>0.786</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="107">
@@ -4718,7 +4718,7 @@
         <v>0.241</v>
       </c>
       <c r="J107" t="n">
-        <v>0.861</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="108">
@@ -4758,7 +4758,7 @@
         <v>0.128</v>
       </c>
       <c r="J108" t="n">
-        <v>0.705</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="109">
@@ -4798,7 +4798,7 @@
         <v>0.128</v>
       </c>
       <c r="J109" t="n">
-        <v>0.861</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="110">
@@ -4838,7 +4838,7 @@
         <v>0.137</v>
       </c>
       <c r="J110" t="n">
-        <v>0.705</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="111">
@@ -4878,7 +4878,7 @@
         <v>0.137</v>
       </c>
       <c r="J111" t="n">
-        <v>0.465</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="112">
@@ -4918,7 +4918,7 @@
         <v>0.179</v>
       </c>
       <c r="J112" t="n">
-        <v>0.775</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -4958,7 +4958,7 @@
         <v>0.179</v>
       </c>
       <c r="J113" t="n">
-        <v>0.861</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="114">
@@ -4998,7 +4998,7 @@
         <v>0.181</v>
       </c>
       <c r="J114" t="n">
-        <v>0.775</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="115">
@@ -5038,7 +5038,7 @@
         <v>0.181</v>
       </c>
       <c r="J115" t="n">
-        <v>0.861</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="116">
@@ -5078,7 +5078,7 @@
         <v>0.169</v>
       </c>
       <c r="J116" t="n">
-        <v>0.288</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="117">
@@ -5118,7 +5118,7 @@
         <v>0.169</v>
       </c>
       <c r="J117" t="n">
-        <v>0.207</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="118">
@@ -5158,7 +5158,7 @@
         <v>0.168</v>
       </c>
       <c r="J118" t="n">
-        <v>0.288</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="119">
@@ -5198,7 +5198,7 @@
         <v>0.168</v>
       </c>
       <c r="J119" t="n">
-        <v>0.201</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="120">
@@ -5238,7 +5238,7 @@
         <v>0.191</v>
       </c>
       <c r="J120" t="n">
-        <v>0.288</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="121">
@@ -5278,7 +5278,7 @@
         <v>0.191</v>
       </c>
       <c r="J121" t="n">
-        <v>0.201</v>
+        <v>0.165</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -5413,7 +5413,7 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>0.369</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="4">
@@ -5783,7 +5783,7 @@
         <v>0.104</v>
       </c>
       <c r="I13" t="n">
-        <v>0.417</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5857,7 +5857,7 @@
         <v>0.0575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.369</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="16">
@@ -5931,7 +5931,7 @@
         <v>0.0692</v>
       </c>
       <c r="I17" t="n">
-        <v>0.369</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="18">
@@ -5968,7 +5968,7 @@
         <v>0.219</v>
       </c>
       <c r="I18" t="n">
-        <v>0.979</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="19">
@@ -6005,7 +6005,7 @@
         <v>0.245</v>
       </c>
       <c r="I19" t="n">
-        <v>0.979</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="20">
@@ -6301,7 +6301,7 @@
         <v>0.664</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -6338,7 +6338,7 @@
         <v>0.216</v>
       </c>
       <c r="I28" t="n">
-        <v>0.979</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="29">
@@ -6523,7 +6523,7 @@
         <v>0.141</v>
       </c>
       <c r="I33" t="n">
-        <v>0.979</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="34">
@@ -6560,7 +6560,7 @@
         <v>0.0496</v>
       </c>
       <c r="I34" t="n">
-        <v>0.265</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="35">
@@ -6819,7 +6819,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="42">
@@ -6967,7 +6967,7 @@
         <v>0.0293</v>
       </c>
       <c r="I45" t="n">
-        <v>0.234</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="46">
@@ -7041,7 +7041,7 @@
         <v>0.008359999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.134</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="48">
@@ -7115,7 +7115,7 @@
         <v>0.0707</v>
       </c>
       <c r="I49" t="n">
-        <v>0.283</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="50">
@@ -7152,7 +7152,7 @@
         <v>0.763</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="51">
@@ -7189,7 +7189,7 @@
         <v>0.158</v>
       </c>
       <c r="I51" t="n">
-        <v>0.631</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="52">
@@ -7226,7 +7226,7 @@
         <v>0.485</v>
       </c>
       <c r="I52" t="n">
-        <v>0.776</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -7263,7 +7263,7 @@
         <v>0.481</v>
       </c>
       <c r="I53" t="n">
-        <v>0.776</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="54">
@@ -7300,7 +7300,7 @@
         <v>0.427</v>
       </c>
       <c r="I54" t="n">
-        <v>0.776</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -7411,7 +7411,7 @@
         <v>0.321</v>
       </c>
       <c r="I57" t="n">
-        <v>0.776</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="58">
@@ -7448,7 +7448,7 @@
         <v>0.463</v>
       </c>
       <c r="I58" t="n">
-        <v>0.776</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="59">
@@ -7559,7 +7559,7 @@
         <v>0.0242</v>
       </c>
       <c r="I61" t="n">
-        <v>0.129</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="62">
@@ -7633,7 +7633,7 @@
         <v>0.0124</v>
       </c>
       <c r="I63" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="64">
@@ -7670,7 +7670,7 @@
         <v>0.431</v>
       </c>
       <c r="I64" t="n">
-        <v>0.776</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -7707,7 +7707,7 @@
         <v>0.006</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0961</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="66">
@@ -7781,7 +7781,7 @@
         <v>0.0105</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0843</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="68">
@@ -7855,7 +7855,7 @@
         <v>1.88e-11</v>
       </c>
       <c r="I69" t="n">
-        <v>3e-10</v>
+        <v>9.4e-11</v>
       </c>
     </row>
     <row r="70">
@@ -8077,7 +8077,7 @@
         <v>0.0539</v>
       </c>
       <c r="I75" t="n">
-        <v>0.287</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="76">
@@ -8299,7 +8299,7 @@
         <v>0.12</v>
       </c>
       <c r="I81" t="n">
-        <v>0.482</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="82">
@@ -8336,7 +8336,7 @@
         <v>0.487</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="83">
@@ -8373,7 +8373,7 @@
         <v>0.0699</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="84">
@@ -8447,7 +8447,7 @@
         <v>5.65e-06</v>
       </c>
       <c r="I85" t="n">
-        <v>9.03e-05</v>
+        <v>2.82e-05</v>
       </c>
     </row>
     <row r="86">
@@ -8669,7 +8669,7 @@
         <v>0.167</v>
       </c>
       <c r="I91" t="n">
-        <v>0.669</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="92">
@@ -8706,7 +8706,7 @@
         <v>0.42</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="93">
@@ -8891,7 +8891,7 @@
         <v>0.162</v>
       </c>
       <c r="I97" t="n">
-        <v>0.669</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="98">
@@ -8928,7 +8928,7 @@
         <v>0.489</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -9039,7 +9039,7 @@
         <v>0.00466</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0746</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="102">
@@ -9187,7 +9187,7 @@
         <v>0.242</v>
       </c>
       <c r="I105" t="n">
-        <v>0.97</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="106">
@@ -9261,7 +9261,7 @@
         <v>0.208</v>
       </c>
       <c r="I107" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -9409,7 +9409,7 @@
         <v>0.605</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="112">
@@ -9483,7 +9483,7 @@
         <v>0.141</v>
       </c>
       <c r="I113" t="n">
-        <v>0.97</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="114">
@@ -9557,7 +9557,7 @@
         <v>0.0436</v>
       </c>
       <c r="I115" t="n">
-        <v>0.174</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="116">
@@ -9631,7 +9631,7 @@
         <v>3.32e-09</v>
       </c>
       <c r="I117" t="n">
-        <v>5.32e-08</v>
+        <v>1.66e-08</v>
       </c>
     </row>
     <row r="118">
@@ -9742,7 +9742,7 @@
         <v>0.348</v>
       </c>
       <c r="I120" t="n">
-        <v>0.929</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="121">
@@ -9779,7 +9779,7 @@
         <v>0.0584</v>
       </c>
       <c r="I121" t="n">
-        <v>0.187</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="122">
@@ -9853,7 +9853,7 @@
         <v>0.0398</v>
       </c>
       <c r="I123" t="n">
-        <v>0.174</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="124">
@@ -9927,7 +9927,7 @@
         <v>0.711</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="126">
@@ -10075,7 +10075,7 @@
         <v>0.0229</v>
       </c>
       <c r="I129" t="n">
-        <v>0.174</v>
+        <v>0.0859</v>
       </c>
     </row>
     <row r="130">
@@ -10149,7 +10149,7 @@
         <v>0.0105</v>
       </c>
       <c r="I131" t="n">
-        <v>0.169</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="132">
@@ -10445,7 +10445,7 @@
         <v>0.43</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="140">
@@ -10667,7 +10667,7 @@
         <v>0.196</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="146">
@@ -10704,7 +10704,7 @@
         <v>0.123</v>
       </c>
       <c r="I146" t="n">
-        <v>0.984</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="147">
@@ -10741,7 +10741,7 @@
         <v>0.0699</v>
       </c>
       <c r="I147" t="n">
-        <v>0.984</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="148">
@@ -11037,7 +11037,7 @@
         <v>0.656</v>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -11074,7 +11074,7 @@
         <v>0.428</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="157">
@@ -11259,7 +11259,7 @@
         <v>0.266</v>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="162">
@@ -11296,7 +11296,7 @@
         <v>0.489</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -11555,7 +11555,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="170">
@@ -11703,7 +11703,7 @@
         <v>0.232</v>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="174">
@@ -11777,7 +11777,7 @@
         <v>0.182</v>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="176">
@@ -11851,7 +11851,7 @@
         <v>0.438</v>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="178">
@@ -11888,7 +11888,7 @@
         <v>0.498</v>
       </c>
       <c r="I178" t="n">
-        <v>0.885</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="179">
@@ -11925,7 +11925,7 @@
         <v>0.0436</v>
       </c>
       <c r="I179" t="n">
-        <v>0.698</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="180">
@@ -11999,7 +11999,7 @@
         <v>0.481</v>
       </c>
       <c r="I181" t="n">
-        <v>0.885</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="182">
@@ -12073,7 +12073,7 @@
         <v>0.484</v>
       </c>
       <c r="I183" t="n">
-        <v>0.885</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -12110,7 +12110,7 @@
         <v>0.737</v>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="185">
@@ -12147,7 +12147,7 @@
         <v>0.321</v>
       </c>
       <c r="I185" t="n">
-        <v>0.885</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="186">
@@ -12184,7 +12184,7 @@
         <v>0.804</v>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="187">
@@ -12221,7 +12221,7 @@
         <v>0.465</v>
       </c>
       <c r="I187" t="n">
-        <v>0.885</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="188">
@@ -12295,7 +12295,7 @@
         <v>0.285</v>
       </c>
       <c r="I189" t="n">
-        <v>0.885</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="190">
@@ -12369,7 +12369,7 @@
         <v>0.459</v>
       </c>
       <c r="I191" t="n">
-        <v>0.885</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -12406,7 +12406,7 @@
         <v>0.5610000000000001</v>
       </c>
       <c r="I192" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -12443,7 +12443,7 @@
         <v>0.135</v>
       </c>
       <c r="I193" t="n">
-        <v>0.885</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="194">
@@ -12517,7 +12517,7 @@
         <v>0.299</v>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="196">
@@ -12591,7 +12591,7 @@
         <v>2.36e-12</v>
       </c>
       <c r="I197" t="n">
-        <v>3.77e-11</v>
+        <v>1.77e-11</v>
       </c>
     </row>
     <row r="198">
@@ -12813,7 +12813,7 @@
         <v>0.18</v>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="204">
@@ -13035,7 +13035,7 @@
         <v>0.604</v>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="210">
@@ -13109,7 +13109,7 @@
         <v>0.58</v>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="212">
@@ -13183,7 +13183,7 @@
         <v>4.34e-06</v>
       </c>
       <c r="I213" t="n">
-        <v>6.95e-05</v>
+        <v>2.82e-05</v>
       </c>
     </row>
     <row r="214">
@@ -13405,7 +13405,7 @@
         <v>0.335</v>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="220">
@@ -13442,7 +13442,7 @@
         <v>0.42</v>
       </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="221">
@@ -13627,7 +13627,7 @@
         <v>0.592</v>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="226">
@@ -13664,7 +13664,7 @@
         <v>0.489</v>
       </c>
       <c r="I226" t="n">
-        <v>1</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -13775,7 +13775,7 @@
         <v>0.00466</v>
       </c>
       <c r="I229" t="n">
-        <v>0.0746</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="230">
@@ -13923,7 +13923,7 @@
         <v>0.242</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="234">
@@ -14071,7 +14071,7 @@
         <v>0.232</v>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="238">
@@ -14145,7 +14145,7 @@
         <v>0.605</v>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="240">
@@ -14256,7 +14256,7 @@
         <v>0.772</v>
       </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="243">
@@ -14367,7 +14367,7 @@
         <v>2.33e-09</v>
       </c>
       <c r="I245" t="n">
-        <v>3.72e-08</v>
+        <v>1.66e-08</v>
       </c>
     </row>
     <row r="246">
@@ -14478,7 +14478,7 @@
         <v>0.737</v>
       </c>
       <c r="I248" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="249">
@@ -14515,7 +14515,7 @@
         <v>0.0584</v>
       </c>
       <c r="I249" t="n">
-        <v>0.467</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="250">
@@ -14552,7 +14552,7 @@
         <v>0.804</v>
       </c>
       <c r="I250" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="251">
@@ -14589,7 +14589,7 @@
         <v>0.21</v>
       </c>
       <c r="I251" t="n">
-        <v>0.841</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="252">
@@ -14663,7 +14663,7 @@
         <v>0.173</v>
       </c>
       <c r="I253" t="n">
-        <v>0.841</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="254">
@@ -14811,7 +14811,7 @@
         <v>0.534</v>
       </c>
       <c r="I257" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="258">
@@ -14885,7 +14885,7 @@
         <v>0.145</v>
       </c>
       <c r="I259" t="n">
-        <v>1</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="260">
@@ -15181,7 +15181,7 @@
         <v>0.18</v>
       </c>
       <c r="I267" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="268">
@@ -15403,7 +15403,7 @@
         <v>0.438</v>
       </c>
       <c r="I273" t="n">
-        <v>1</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="274">
@@ -15477,7 +15477,7 @@
         <v>0.51</v>
       </c>
       <c r="I275" t="n">
-        <v>1</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="276">
@@ -15773,7 +15773,7 @@
         <v>0.335</v>
       </c>
       <c r="I283" t="n">
-        <v>1</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="284">
@@ -15995,7 +15995,7 @@
         <v>0.665</v>
       </c>
       <c r="I289" t="n">
-        <v>1</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="290">
@@ -16032,7 +16032,7 @@
         <v>0.109</v>
       </c>
       <c r="I290" t="n">
-        <v>0.754</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="291">
@@ -16106,7 +16106,7 @@
         <v>0.462</v>
       </c>
       <c r="I292" t="n">
-        <v>0.805</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -16180,7 +16180,7 @@
         <v>0.556</v>
       </c>
       <c r="I294" t="n">
-        <v>0.805</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -16217,7 +16217,7 @@
         <v>0.343</v>
       </c>
       <c r="I295" t="n">
-        <v>0.754</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -16254,7 +16254,7 @@
         <v>0.604</v>
       </c>
       <c r="I296" t="n">
-        <v>0.805</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -16291,7 +16291,7 @@
         <v>0.242</v>
       </c>
       <c r="I297" t="n">
-        <v>0.754</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="298">
@@ -16328,7 +16328,7 @@
         <v>0.785</v>
       </c>
       <c r="I298" t="n">
-        <v>0.966</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -16365,7 +16365,7 @@
         <v>0.542</v>
       </c>
       <c r="I299" t="n">
-        <v>0.805</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
@@ -16402,7 +16402,7 @@
         <v>0.377</v>
       </c>
       <c r="I300" t="n">
-        <v>0.754</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -16439,7 +16439,7 @@
         <v>0.232</v>
       </c>
       <c r="I301" t="n">
-        <v>0.754</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="302">
@@ -16513,7 +16513,7 @@
         <v>0.342</v>
       </c>
       <c r="I303" t="n">
-        <v>0.754</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="304">
@@ -16550,7 +16550,7 @@
         <v>0.273</v>
       </c>
       <c r="I304" t="n">
-        <v>0.754</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -16587,7 +16587,7 @@
         <v>0.0134</v>
       </c>
       <c r="I305" t="n">
-        <v>0.214</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="306">
@@ -16624,7 +16624,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="I306" t="n">
-        <v>0.728</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="307">
@@ -16661,7 +16661,7 @@
         <v>0.628</v>
       </c>
       <c r="I307" t="n">
-        <v>0.728</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="308">
@@ -16698,7 +16698,7 @@
         <v>0.203</v>
       </c>
       <c r="I308" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -16735,7 +16735,7 @@
         <v>0.593</v>
       </c>
       <c r="I309" t="n">
-        <v>0.728</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -16772,7 +16772,7 @@
         <v>0.475</v>
       </c>
       <c r="I310" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -16809,7 +16809,7 @@
         <v>0.468</v>
       </c>
       <c r="I311" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -16846,7 +16846,7 @@
         <v>0.731</v>
       </c>
       <c r="I312" t="n">
-        <v>0.779</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="313">
@@ -16883,7 +16883,7 @@
         <v>0.0584</v>
       </c>
       <c r="I313" t="n">
-        <v>0.467</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="314">
@@ -16920,7 +16920,7 @@
         <v>0.622</v>
       </c>
       <c r="I314" t="n">
-        <v>0.728</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="315">
@@ -16957,7 +16957,7 @@
         <v>0.21</v>
       </c>
       <c r="I315" t="n">
-        <v>0.728</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="316">
@@ -16994,7 +16994,7 @@
         <v>0.637</v>
       </c>
       <c r="I316" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -17031,7 +17031,7 @@
         <v>0.285</v>
       </c>
       <c r="I317" t="n">
-        <v>0.728</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="318">
@@ -17105,7 +17105,7 @@
         <v>0.466</v>
       </c>
       <c r="I319" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -17142,7 +17142,7 @@
         <v>0.584</v>
       </c>
       <c r="I320" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -17179,7 +17179,7 @@
         <v>0.00839</v>
       </c>
       <c r="I321" t="n">
-        <v>0.134</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="322">
@@ -17253,7 +17253,7 @@
         <v>0.0523</v>
       </c>
       <c r="I323" t="n">
-        <v>0.419</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="324">
@@ -17327,7 +17327,7 @@
         <v>3.42e-09</v>
       </c>
       <c r="I325" t="n">
-        <v>5.47e-08</v>
+        <v>1.28e-08</v>
       </c>
     </row>
     <row r="326">
@@ -17364,7 +17364,7 @@
         <v>0.399</v>
       </c>
       <c r="I326" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -17475,7 +17475,7 @@
         <v>0.424</v>
       </c>
       <c r="I329" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -17549,7 +17549,7 @@
         <v>0.103</v>
       </c>
       <c r="I331" t="n">
-        <v>0.551</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="332">
@@ -17623,7 +17623,7 @@
         <v>0.299</v>
       </c>
       <c r="I333" t="n">
-        <v>0.965</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -17771,7 +17771,7 @@
         <v>0.301</v>
       </c>
       <c r="I337" t="n">
-        <v>0.965</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="338">
@@ -17808,7 +17808,7 @@
         <v>0.216</v>
       </c>
       <c r="I338" t="n">
-        <v>0.979</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="339">
@@ -17845,7 +17845,7 @@
         <v>0.245</v>
       </c>
       <c r="I339" t="n">
-        <v>0.979</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="340">
@@ -17919,7 +17919,7 @@
         <v>1.34e-05</v>
       </c>
       <c r="I341" t="n">
-        <v>0.000214</v>
+        <v>5.03e-05</v>
       </c>
     </row>
     <row r="342">
@@ -18141,7 +18141,7 @@
         <v>0.383</v>
       </c>
       <c r="I347" t="n">
-        <v>1</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="348">
@@ -18178,7 +18178,7 @@
         <v>0.205</v>
       </c>
       <c r="I348" t="n">
-        <v>0.979</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="349">
@@ -18363,7 +18363,7 @@
         <v>0.35</v>
       </c>
       <c r="I353" t="n">
-        <v>1</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="354">
@@ -18400,7 +18400,7 @@
         <v>0.234</v>
       </c>
       <c r="I354" t="n">
-        <v>0.828</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="355">
@@ -18511,7 +18511,7 @@
         <v>0.00466</v>
       </c>
       <c r="I357" t="n">
-        <v>0.0746</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="358">
@@ -18659,7 +18659,7 @@
         <v>0.242</v>
       </c>
       <c r="I361" t="n">
-        <v>0.828</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="362">
@@ -18733,7 +18733,7 @@
         <v>0.208</v>
       </c>
       <c r="I363" t="n">
-        <v>0.828</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -18807,7 +18807,7 @@
         <v>0.405</v>
       </c>
       <c r="I365" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="366">
@@ -18881,7 +18881,7 @@
         <v>0.605</v>
       </c>
       <c r="I367" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="368">
@@ -18955,7 +18955,7 @@
         <v>0.259</v>
       </c>
       <c r="I369" t="n">
-        <v>0.828</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="370">
@@ -18992,7 +18992,7 @@
         <v>0.75</v>
       </c>
       <c r="I370" t="n">
-        <v>0.919</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="371">
@@ -19029,7 +19029,7 @@
         <v>0.158</v>
       </c>
       <c r="I371" t="n">
-        <v>0.489</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="372">
@@ -19103,7 +19103,7 @@
         <v>1.04e-08</v>
       </c>
       <c r="I373" t="n">
-        <v>1.66e-07</v>
+        <v>3.9e-08</v>
       </c>
     </row>
     <row r="374">
@@ -19140,7 +19140,7 @@
         <v>0.427</v>
       </c>
       <c r="I374" t="n">
-        <v>0.847</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375">
@@ -19177,7 +19177,7 @@
         <v>0.713</v>
       </c>
       <c r="I375" t="n">
-        <v>0.919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -19214,7 +19214,7 @@
         <v>0.348</v>
       </c>
       <c r="I376" t="n">
-        <v>0.796</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="377">
@@ -19251,7 +19251,7 @@
         <v>0.0584</v>
       </c>
       <c r="I377" t="n">
-        <v>0.336</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="378">
@@ -19288,7 +19288,7 @@
         <v>0.804</v>
       </c>
       <c r="I378" t="n">
-        <v>0.919</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="379">
@@ -19325,7 +19325,7 @@
         <v>0.0761</v>
       </c>
       <c r="I379" t="n">
-        <v>0.336</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="380">
@@ -19362,7 +19362,7 @@
         <v>0.804</v>
       </c>
       <c r="I380" t="n">
-        <v>0.919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -19399,7 +19399,7 @@
         <v>0.183</v>
       </c>
       <c r="I381" t="n">
-        <v>0.489</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="382">
@@ -19473,7 +19473,7 @@
         <v>0.476</v>
       </c>
       <c r="I383" t="n">
-        <v>0.847</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -19510,7 +19510,7 @@
         <v>0.787</v>
       </c>
       <c r="I384" t="n">
-        <v>0.919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
@@ -19547,7 +19547,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I385" t="n">
-        <v>0.336</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="386">
@@ -19621,7 +19621,7 @@
         <v>0.299</v>
       </c>
       <c r="I387" t="n">
-        <v>1</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="388">
@@ -20139,7 +20139,7 @@
         <v>0.0182</v>
       </c>
       <c r="I401" t="n">
-        <v>0.292</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="402">
@@ -20176,7 +20176,7 @@
         <v>0.224</v>
       </c>
       <c r="I402" t="n">
-        <v>1</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="403">
@@ -20213,7 +20213,7 @@
         <v>0.607</v>
       </c>
       <c r="I403" t="n">
-        <v>1</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="404">
@@ -20509,7 +20509,7 @@
         <v>0.6909999999999999</v>
       </c>
       <c r="I411" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="412">
@@ -20546,7 +20546,7 @@
         <v>0.37</v>
       </c>
       <c r="I412" t="n">
-        <v>1</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="413">
@@ -20731,7 +20731,7 @@
         <v>0.122</v>
       </c>
       <c r="I417" t="n">
-        <v>1</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="418">
@@ -20768,7 +20768,7 @@
         <v>0.0219</v>
       </c>
       <c r="I418" t="n">
-        <v>0.175</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="419">
@@ -21027,7 +21027,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I425" t="n">
-        <v>1</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="426">
@@ -21175,7 +21175,7 @@
         <v>0.405</v>
       </c>
       <c r="I429" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="430">
@@ -21249,7 +21249,7 @@
         <v>0.342</v>
       </c>
       <c r="I431" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="432">
@@ -21323,7 +21323,7 @@
         <v>0.0134</v>
       </c>
       <c r="I433" t="n">
-        <v>0.175</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="434">
@@ -21360,7 +21360,7 @@
         <v>0.553</v>
       </c>
       <c r="I434" t="n">
-        <v>0.904</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="435">
@@ -21397,7 +21397,7 @@
         <v>0.415</v>
       </c>
       <c r="I435" t="n">
-        <v>0.904</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="436">
@@ -21471,7 +21471,7 @@
         <v>0.481</v>
       </c>
       <c r="I437" t="n">
-        <v>0.904</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="438">
@@ -21508,7 +21508,7 @@
         <v>0.604</v>
       </c>
       <c r="I438" t="n">
-        <v>0.904</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -21545,7 +21545,7 @@
         <v>0.313</v>
       </c>
       <c r="I439" t="n">
-        <v>0.904</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440">
@@ -21582,7 +21582,7 @@
         <v>0.737</v>
       </c>
       <c r="I440" t="n">
-        <v>0.907</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="441">
@@ -21619,7 +21619,7 @@
         <v>0.321</v>
       </c>
       <c r="I441" t="n">
-        <v>0.904</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="442">
@@ -21656,7 +21656,7 @@
         <v>0.622</v>
       </c>
       <c r="I442" t="n">
-        <v>0.904</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="443">
@@ -21693,7 +21693,7 @@
         <v>0.477</v>
       </c>
       <c r="I443" t="n">
-        <v>0.904</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="444">
@@ -21767,7 +21767,7 @@
         <v>0.462</v>
       </c>
       <c r="I445" t="n">
-        <v>0.904</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="446">
@@ -21841,7 +21841,7 @@
         <v>0.699</v>
       </c>
       <c r="I447" t="n">
-        <v>0.907</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -21878,7 +21878,7 @@
         <v>0.396</v>
       </c>
       <c r="I448" t="n">
-        <v>0.904</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -21915,7 +21915,7 @@
         <v>0.000829</v>
       </c>
       <c r="I449" t="n">
-        <v>0.0133</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="450">
@@ -21989,7 +21989,7 @@
         <v>0.0523</v>
       </c>
       <c r="I451" t="n">
-        <v>0.419</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="452">
@@ -22063,7 +22063,7 @@
         <v>1.52e-14</v>
       </c>
       <c r="I453" t="n">
-        <v>2.44e-13</v>
+        <v>2.28e-13</v>
       </c>
     </row>
     <row r="454">
@@ -22100,7 +22100,7 @@
         <v>0.399</v>
       </c>
       <c r="I454" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -22248,7 +22248,7 @@
         <v>0.552</v>
       </c>
       <c r="I458" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
@@ -22285,7 +22285,7 @@
         <v>0.288</v>
       </c>
       <c r="I459" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="460">
@@ -22322,7 +22322,7 @@
         <v>0.412</v>
       </c>
       <c r="I460" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
@@ -22359,7 +22359,7 @@
         <v>0.472</v>
       </c>
       <c r="I461" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -22433,7 +22433,7 @@
         <v>0.181</v>
       </c>
       <c r="I463" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
@@ -22507,7 +22507,7 @@
         <v>0.301</v>
       </c>
       <c r="I465" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="466">
@@ -22581,7 +22581,7 @@
         <v>0.245</v>
       </c>
       <c r="I467" t="n">
-        <v>1</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="468">
@@ -22655,7 +22655,7 @@
         <v>2.65e-06</v>
       </c>
       <c r="I469" t="n">
-        <v>4.25e-05</v>
+        <v>2.82e-05</v>
       </c>
     </row>
     <row r="470">
@@ -22877,7 +22877,7 @@
         <v>0.402</v>
       </c>
       <c r="I475" t="n">
-        <v>1</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="476">
@@ -23099,7 +23099,7 @@
         <v>0.35</v>
       </c>
       <c r="I481" t="n">
-        <v>1</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="482">
@@ -23247,7 +23247,7 @@
         <v>0.00466</v>
       </c>
       <c r="I485" t="n">
-        <v>0.0746</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="486">
@@ -23395,7 +23395,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I489" t="n">
-        <v>1</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="490">
@@ -23617,7 +23617,7 @@
         <v>0.182</v>
       </c>
       <c r="I495" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="496">
@@ -23691,7 +23691,7 @@
         <v>0.259</v>
       </c>
       <c r="I497" t="n">
-        <v>1</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="498">
@@ -23728,7 +23728,7 @@
         <v>0.776</v>
       </c>
       <c r="I498" t="n">
-        <v>0.975</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="499">
@@ -23765,7 +23765,7 @@
         <v>0.158</v>
       </c>
       <c r="I499" t="n">
-        <v>0.631</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="500">
@@ -23839,7 +23839,7 @@
         <v>1.18e-09</v>
       </c>
       <c r="I501" t="n">
-        <v>1.88e-08</v>
+        <v>1.66e-08</v>
       </c>
     </row>
     <row r="502">
@@ -23876,7 +23876,7 @@
         <v>0.427</v>
       </c>
       <c r="I502" t="n">
-        <v>0.768</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -23913,7 +23913,7 @@
         <v>0.713</v>
       </c>
       <c r="I503" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -23987,7 +23987,7 @@
         <v>0.321</v>
       </c>
       <c r="I505" t="n">
-        <v>0.768</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="506">
@@ -24024,7 +24024,7 @@
         <v>0.409</v>
       </c>
       <c r="I506" t="n">
-        <v>0.768</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="507">
@@ -24061,7 +24061,7 @@
         <v>0.225</v>
       </c>
       <c r="I507" t="n">
-        <v>0.719</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="508">
@@ -24098,7 +24098,7 @@
         <v>0.452</v>
       </c>
       <c r="I508" t="n">
-        <v>0.768</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -24135,7 +24135,7 @@
         <v>0.48</v>
       </c>
       <c r="I509" t="n">
-        <v>0.768</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="510">
@@ -24209,7 +24209,7 @@
         <v>0.107</v>
       </c>
       <c r="I511" t="n">
-        <v>0.571</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="512">
@@ -24246,7 +24246,7 @@
         <v>0.792</v>
       </c>
       <c r="I512" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513">
@@ -24283,7 +24283,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I513" t="n">
-        <v>0.571</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="514">
@@ -24357,7 +24357,7 @@
         <v>0.0523</v>
       </c>
       <c r="I515" t="n">
-        <v>0.837</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="516">
@@ -24875,7 +24875,7 @@
         <v>0.301</v>
       </c>
       <c r="I529" t="n">
-        <v>1</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="530">
@@ -24912,7 +24912,7 @@
         <v>0.277</v>
       </c>
       <c r="I530" t="n">
-        <v>1</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="531">
@@ -24949,7 +24949,7 @@
         <v>0.245</v>
       </c>
       <c r="I531" t="n">
-        <v>1</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="532">
@@ -25282,7 +25282,7 @@
         <v>0.42</v>
       </c>
       <c r="I540" t="n">
-        <v>1</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="541">
@@ -25467,7 +25467,7 @@
         <v>0.35</v>
       </c>
       <c r="I545" t="n">
-        <v>1</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="546">
@@ -25504,7 +25504,7 @@
         <v>0.489</v>
       </c>
       <c r="I546" t="n">
-        <v>1</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="547">
@@ -26059,7 +26059,7 @@
         <v>0.259</v>
       </c>
       <c r="I561" t="n">
-        <v>1</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="562">
@@ -26096,7 +26096,7 @@
         <v>0.746</v>
       </c>
       <c r="I562" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="563">
@@ -26133,7 +26133,7 @@
         <v>0.158</v>
       </c>
       <c r="I563" t="n">
-        <v>1</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="564">
@@ -26355,7 +26355,7 @@
         <v>0.628</v>
       </c>
       <c r="I569" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="570">
@@ -26392,7 +26392,7 @@
         <v>0.796</v>
       </c>
       <c r="I570" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="571">
@@ -26503,7 +26503,7 @@
         <v>0.711</v>
       </c>
       <c r="I573" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="574">
@@ -26651,7 +26651,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I577" t="n">
-        <v>1</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="578">
@@ -26725,7 +26725,7 @@
         <v>0.145</v>
       </c>
       <c r="I579" t="n">
-        <v>0.719</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="580">
@@ -27021,7 +27021,7 @@
         <v>0.18</v>
       </c>
       <c r="I587" t="n">
-        <v>0.719</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="588">
@@ -27058,7 +27058,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I588" t="n">
-        <v>0.719</v>
+        <v>1</v>
       </c>
     </row>
     <row r="589">
@@ -27243,7 +27243,7 @@
         <v>0.12</v>
       </c>
       <c r="I593" t="n">
-        <v>0.719</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="594">
@@ -27280,7 +27280,7 @@
         <v>0.481</v>
       </c>
       <c r="I594" t="n">
-        <v>1</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="595">
@@ -27317,7 +27317,7 @@
         <v>0.329</v>
       </c>
       <c r="I595" t="n">
-        <v>1</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="596">
@@ -27613,7 +27613,7 @@
         <v>0.391</v>
       </c>
       <c r="I603" t="n">
-        <v>1</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="604">
@@ -27650,7 +27650,7 @@
         <v>0.187</v>
       </c>
       <c r="I604" t="n">
-        <v>1</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="605">
@@ -27835,7 +27835,7 @@
         <v>0.119</v>
       </c>
       <c r="I609" t="n">
-        <v>1</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="610">
@@ -28131,7 +28131,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I617" t="n">
-        <v>1</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="618">
@@ -28279,7 +28279,7 @@
         <v>0.405</v>
       </c>
       <c r="I621" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="622">
@@ -28353,7 +28353,7 @@
         <v>0.605</v>
       </c>
       <c r="I623" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="624">
@@ -28427,7 +28427,7 @@
         <v>0.259</v>
       </c>
       <c r="I625" t="n">
-        <v>1</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="626">
@@ -28464,7 +28464,7 @@
         <v>0.743</v>
       </c>
       <c r="I626" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="627">
@@ -28501,7 +28501,7 @@
         <v>0.367</v>
       </c>
       <c r="I627" t="n">
-        <v>1</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="628">
@@ -28575,7 +28575,7 @@
         <v>0.481</v>
       </c>
       <c r="I629" t="n">
-        <v>1</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="630">
@@ -28686,7 +28686,7 @@
         <v>0.731</v>
       </c>
       <c r="I632" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="633">
@@ -28723,7 +28723,7 @@
         <v>0.321</v>
       </c>
       <c r="I633" t="n">
-        <v>1</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="634">
@@ -28760,7 +28760,7 @@
         <v>0.594</v>
       </c>
       <c r="I634" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="635">
@@ -28797,7 +28797,7 @@
         <v>0.136</v>
       </c>
       <c r="I635" t="n">
-        <v>0.727</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="636">
@@ -28834,7 +28834,7 @@
         <v>0.107</v>
       </c>
       <c r="I636" t="n">
-        <v>0.727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637">
@@ -28871,7 +28871,7 @@
         <v>0.462</v>
       </c>
       <c r="I637" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="638">
@@ -29019,7 +29019,7 @@
         <v>0.0421</v>
       </c>
       <c r="I641" t="n">
-        <v>0.673</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="642">
@@ -29611,7 +29611,7 @@
         <v>0.604</v>
       </c>
       <c r="I657" t="n">
-        <v>1</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="658">
@@ -30203,7 +30203,7 @@
         <v>0.768</v>
       </c>
       <c r="I673" t="n">
-        <v>1</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="674">
@@ -30832,7 +30832,7 @@
         <v>0.776</v>
       </c>
       <c r="I690" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="691">
@@ -31054,7 +31054,7 @@
         <v>0.705</v>
       </c>
       <c r="I696" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="697">
@@ -31128,7 +31128,7 @@
         <v>0.3</v>
       </c>
       <c r="I698" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="699">
@@ -31165,7 +31165,7 @@
         <v>0.536</v>
       </c>
       <c r="I699" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="700">
@@ -31239,7 +31239,7 @@
         <v>0.752</v>
       </c>
       <c r="I701" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="702">
@@ -31387,7 +31387,7 @@
         <v>0.65</v>
       </c>
       <c r="I705" t="n">
-        <v>1</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="706">
@@ -31979,7 +31979,7 @@
         <v>0.435</v>
       </c>
       <c r="I721" t="n">
-        <v>1</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="722">
@@ -32349,7 +32349,7 @@
         <v>0.238</v>
       </c>
       <c r="I731" t="n">
-        <v>1</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="732">
@@ -32571,7 +32571,7 @@
         <v>0.763</v>
       </c>
       <c r="I737" t="n">
-        <v>1</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="738">
@@ -33089,7 +33089,7 @@
         <v>0.661</v>
       </c>
       <c r="I751" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="752">
@@ -33422,7 +33422,7 @@
         <v>0.712</v>
       </c>
       <c r="I760" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="761">
@@ -33496,7 +33496,7 @@
         <v>0.787</v>
       </c>
       <c r="I762" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="763">
@@ -33607,7 +33607,7 @@
         <v>0.734</v>
       </c>
       <c r="I765" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="766">
@@ -33755,7 +33755,7 @@
         <v>0.494</v>
       </c>
       <c r="I769" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="770">
@@ -34347,7 +34347,7 @@
         <v>0.796</v>
       </c>
       <c r="I785" t="n">
-        <v>1</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="786">
@@ -34717,7 +34717,7 @@
         <v>0.243</v>
       </c>
       <c r="I795" t="n">
-        <v>1</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="796">
@@ -34976,7 +34976,7 @@
         <v>0.609</v>
       </c>
       <c r="I802" t="n">
-        <v>1</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="803">
@@ -35457,7 +35457,7 @@
         <v>0.661</v>
       </c>
       <c r="I815" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="816">
@@ -35568,7 +35568,7 @@
         <v>0.594</v>
       </c>
       <c r="I818" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="819">
@@ -35605,7 +35605,7 @@
         <v>0.5590000000000001</v>
       </c>
       <c r="I819" t="n">
-        <v>1</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="820">
@@ -35679,7 +35679,7 @@
         <v>0.481</v>
       </c>
       <c r="I821" t="n">
-        <v>1</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="822">
@@ -35790,7 +35790,7 @@
         <v>0.712</v>
       </c>
       <c r="I824" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="825">
@@ -35975,7 +35975,7 @@
         <v>0.765</v>
       </c>
       <c r="I829" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="830">
@@ -36123,7 +36123,7 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="I833" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="834">
@@ -36715,7 +36715,7 @@
         <v>0.435</v>
       </c>
       <c r="I849" t="n">
-        <v>1</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="850">
@@ -37307,7 +37307,7 @@
         <v>0.768</v>
       </c>
       <c r="I865" t="n">
-        <v>1</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="866">
@@ -37936,7 +37936,7 @@
         <v>0.787</v>
       </c>
       <c r="I882" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="883">
@@ -38158,7 +38158,7 @@
         <v>0.476</v>
       </c>
       <c r="I888" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="889">
@@ -38232,7 +38232,7 @@
         <v>0.787</v>
       </c>
       <c r="I890" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="891">
@@ -38491,7 +38491,7 @@
         <v>0.506</v>
       </c>
       <c r="I897" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="898">
@@ -38565,7 +38565,7 @@
         <v>0.353</v>
       </c>
       <c r="I899" t="n">
-        <v>1</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="900">
@@ -39083,7 +39083,7 @@
         <v>0.435</v>
       </c>
       <c r="I913" t="n">
-        <v>1</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="914">
@@ -39120,7 +39120,7 @@
         <v>0.44</v>
       </c>
       <c r="I914" t="n">
-        <v>1</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="915">
@@ -39157,7 +39157,7 @@
         <v>0.486</v>
       </c>
       <c r="I915" t="n">
-        <v>1</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="916">
@@ -39675,7 +39675,7 @@
         <v>0.526</v>
       </c>
       <c r="I929" t="n">
-        <v>1</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="930">
@@ -39712,7 +39712,7 @@
         <v>0.348</v>
       </c>
       <c r="I930" t="n">
-        <v>1</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="931">
@@ -39786,7 +39786,7 @@
         <v>0.021</v>
       </c>
       <c r="I932" t="n">
-        <v>0.336</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="933">
@@ -40008,7 +40008,7 @@
         <v>0.103</v>
       </c>
       <c r="I938" t="n">
-        <v>0.827</v>
+        <v>1</v>
       </c>
     </row>
     <row r="939">
@@ -40193,7 +40193,7 @@
         <v>0.407</v>
       </c>
       <c r="I943" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="944">
@@ -40341,7 +40341,7 @@
         <v>0.103</v>
       </c>
       <c r="I947" t="n">
-        <v>0.547</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="948">
@@ -40378,7 +40378,7 @@
         <v>0.0147</v>
       </c>
       <c r="I948" t="n">
-        <v>0.235</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="949">
@@ -40415,7 +40415,7 @@
         <v>0.203</v>
       </c>
       <c r="I949" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="950">
@@ -40526,7 +40526,7 @@
         <v>0.3</v>
       </c>
       <c r="I952" t="n">
-        <v>0.96</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="953">
@@ -40600,7 +40600,7 @@
         <v>0.0489</v>
       </c>
       <c r="I954" t="n">
-        <v>0.391</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="955">
@@ -40637,7 +40637,7 @@
         <v>0.579</v>
       </c>
       <c r="I955" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="956">
@@ -40711,7 +40711,7 @@
         <v>0.554</v>
       </c>
       <c r="I957" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="958">
@@ -40859,7 +40859,7 @@
         <v>0.628</v>
       </c>
       <c r="I961" t="n">
-        <v>1</v>
+        <v>0.696</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_new30.xlsx
+++ b/eval/learning-curve/results/statistical_tests_new30.xlsx
@@ -558,7 +558,7 @@
         <v>0.141</v>
       </c>
       <c r="J3" t="n">
-        <v>0.847</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
         <v>0.201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.201</v>
       </c>
       <c r="J5" t="n">
-        <v>0.846</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="6">
@@ -678,7 +678,7 @@
         <v>0.127</v>
       </c>
       <c r="J6" t="n">
-        <v>0.61</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>0.127</v>
       </c>
       <c r="J7" t="n">
-        <v>0.627</v>
+        <v>0.6266666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>0.216</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.216</v>
       </c>
       <c r="J9" t="n">
-        <v>0.847</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +838,7 @@
         <v>0.138</v>
       </c>
       <c r="J10" t="n">
-        <v>0.864</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         <v>0.138</v>
       </c>
       <c r="J11" t="n">
-        <v>0.627</v>
+        <v>0.6266666666666666</v>
       </c>
     </row>
     <row r="12">
@@ -918,7 +918,7 @@
         <v>0.181</v>
       </c>
       <c r="J12" t="n">
-        <v>0.864</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="13">
@@ -958,7 +958,7 @@
         <v>0.181</v>
       </c>
       <c r="J13" t="n">
-        <v>0.847</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="14">
@@ -998,7 +998,7 @@
         <v>0.117</v>
       </c>
       <c r="J14" t="n">
-        <v>0.735</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="15">
@@ -1038,7 +1038,7 @@
         <v>0.117</v>
       </c>
       <c r="J15" t="n">
-        <v>0.833</v>
+        <v>0.7124999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1078,7 +1078,7 @@
         <v>0.224</v>
       </c>
       <c r="J16" t="n">
-        <v>0.864</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="17">
@@ -1158,7 +1158,7 @@
         <v>0.146</v>
       </c>
       <c r="J18" t="n">
-        <v>0.33</v>
+        <v>0.4395</v>
       </c>
     </row>
     <row r="19">
@@ -1198,7 +1198,7 @@
         <v>0.146</v>
       </c>
       <c r="J19" t="n">
-        <v>0.327</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="20">
@@ -1238,7 +1238,7 @@
         <v>0.101</v>
       </c>
       <c r="J20" t="n">
-        <v>0.246</v>
+        <v>0.1755</v>
       </c>
     </row>
     <row r="21">
@@ -1278,7 +1278,7 @@
         <v>0.101</v>
       </c>
       <c r="J21" t="n">
-        <v>0.165</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="22">
@@ -1318,7 +1318,7 @@
         <v>0.158</v>
       </c>
       <c r="J22" t="n">
-        <v>0.836</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="23">
@@ -1358,7 +1358,7 @@
         <v>0.158</v>
       </c>
       <c r="J23" t="n">
-        <v>0.846</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="24">
@@ -1398,7 +1398,7 @@
         <v>0.166</v>
       </c>
       <c r="J24" t="n">
-        <v>0.61</v>
+        <v>0.3613333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -1438,7 +1438,7 @@
         <v>0.166</v>
       </c>
       <c r="J25" t="n">
-        <v>0.443</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="26">
@@ -1478,7 +1478,7 @@
         <v>0.158</v>
       </c>
       <c r="J26" t="n">
-        <v>0.246</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="27">
@@ -1518,7 +1518,7 @@
         <v>0.158</v>
       </c>
       <c r="J27" t="n">
-        <v>0.144</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="28">
@@ -1558,7 +1558,7 @@
         <v>0.167</v>
       </c>
       <c r="J28" t="n">
-        <v>0.246</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="29">
@@ -1598,7 +1598,7 @@
         <v>0.167</v>
       </c>
       <c r="J29" t="n">
-        <v>0.144</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="30">
@@ -1638,7 +1638,7 @@
         <v>0.124</v>
       </c>
       <c r="J30" t="n">
-        <v>0.35</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="31">
@@ -1678,7 +1678,7 @@
         <v>0.124</v>
       </c>
       <c r="J31" t="n">
-        <v>0.251</v>
+        <v>0.0796</v>
       </c>
     </row>
     <row r="32">
@@ -1718,7 +1718,7 @@
         <v>0.0921</v>
       </c>
       <c r="J32" t="n">
-        <v>0.246</v>
+        <v>0.06887500000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1758,7 +1758,7 @@
         <v>0.0921</v>
       </c>
       <c r="J33" t="n">
-        <v>0.144</v>
+        <v>0.03199999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1798,7 +1798,7 @@
         <v>0.251</v>
       </c>
       <c r="J34" t="n">
-        <v>0.864</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="35">
@@ -1838,7 +1838,7 @@
         <v>0.251</v>
       </c>
       <c r="J35" t="n">
-        <v>0.456</v>
+        <v>0.29875</v>
       </c>
     </row>
     <row r="36">
@@ -1878,7 +1878,7 @@
         <v>0.104</v>
       </c>
       <c r="J36" t="n">
-        <v>0.28</v>
+        <v>0.0701</v>
       </c>
     </row>
     <row r="37">
@@ -1918,7 +1918,7 @@
         <v>0.104</v>
       </c>
       <c r="J37" t="n">
-        <v>0.202</v>
+        <v>0.0499</v>
       </c>
     </row>
     <row r="38">
@@ -1958,7 +1958,7 @@
         <v>0.26</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="39">
@@ -1998,7 +1998,7 @@
         <v>0.26</v>
       </c>
       <c r="J39" t="n">
-        <v>0.237</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="40">
@@ -2038,7 +2038,7 @@
         <v>0.132</v>
       </c>
       <c r="J40" t="n">
-        <v>0.246</v>
+        <v>0.06887500000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2078,7 +2078,7 @@
         <v>0.132</v>
       </c>
       <c r="J41" t="n">
-        <v>0.144</v>
+        <v>0.03199999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -2118,7 +2118,7 @@
         <v>0.246</v>
       </c>
       <c r="J42" t="n">
-        <v>0.945</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="43">
@@ -2158,7 +2158,7 @@
         <v>0.246</v>
       </c>
       <c r="J43" t="n">
-        <v>0.494</v>
+        <v>0.29875</v>
       </c>
     </row>
     <row r="44">
@@ -2198,7 +2198,7 @@
         <v>0.147</v>
       </c>
       <c r="J44" t="n">
-        <v>0.246</v>
+        <v>0.06887500000000001</v>
       </c>
     </row>
     <row r="45">
@@ -2238,7 +2238,7 @@
         <v>0.147</v>
       </c>
       <c r="J45" t="n">
-        <v>0.144</v>
+        <v>0.03199999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2278,7 +2278,7 @@
         <v>0.236</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="47">
@@ -2318,7 +2318,7 @@
         <v>0.236</v>
       </c>
       <c r="J47" t="n">
-        <v>0.627</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="48">
@@ -2358,7 +2358,7 @@
         <v>0.115</v>
       </c>
       <c r="J48" t="n">
-        <v>0.246</v>
+        <v>0.06887500000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2398,7 +2398,7 @@
         <v>0.115</v>
       </c>
       <c r="J49" t="n">
-        <v>0.165</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="50">
@@ -2438,7 +2438,7 @@
         <v>0.127</v>
       </c>
       <c r="J50" t="n">
-        <v>0.246</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="51">
@@ -2478,7 +2478,7 @@
         <v>0.127</v>
       </c>
       <c r="J51" t="n">
-        <v>0.144</v>
+        <v>0.02925</v>
       </c>
     </row>
     <row r="52">
@@ -2518,7 +2518,7 @@
         <v>0.171</v>
       </c>
       <c r="J52" t="n">
-        <v>0.61</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="53">
@@ -2558,7 +2558,7 @@
         <v>0.171</v>
       </c>
       <c r="J53" t="n">
-        <v>0.731</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="54">
@@ -2598,7 +2598,7 @@
         <v>0.163</v>
       </c>
       <c r="J54" t="n">
-        <v>0.61</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="55">
@@ -2638,7 +2638,7 @@
         <v>0.163</v>
       </c>
       <c r="J55" t="n">
-        <v>0.572</v>
+        <v>0.3813333333333333</v>
       </c>
     </row>
     <row r="56">
@@ -2678,7 +2678,7 @@
         <v>0.144</v>
       </c>
       <c r="J56" t="n">
-        <v>0.619</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="57">
@@ -2718,7 +2718,7 @@
         <v>0.144</v>
       </c>
       <c r="J57" t="n">
-        <v>0.456</v>
+        <v>0.3813333333333333</v>
       </c>
     </row>
     <row r="58">
@@ -2758,7 +2758,7 @@
         <v>0.16</v>
       </c>
       <c r="J58" t="n">
-        <v>0.417</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="59">
@@ -2798,7 +2798,7 @@
         <v>0.16</v>
       </c>
       <c r="J59" t="n">
-        <v>0.388</v>
+        <v>0.3813333333333333</v>
       </c>
     </row>
     <row r="60">
@@ -2838,7 +2838,7 @@
         <v>0.178</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="61">
@@ -2878,7 +2878,7 @@
         <v>0.178</v>
       </c>
       <c r="J61" t="n">
-        <v>0.237</v>
+        <v>0.0712</v>
       </c>
     </row>
     <row r="62">
@@ -2918,7 +2918,7 @@
         <v>0.223</v>
       </c>
       <c r="J62" t="n">
-        <v>0.417</v>
+        <v>0.3475</v>
       </c>
     </row>
     <row r="63">
@@ -2958,7 +2958,7 @@
         <v>0.223</v>
       </c>
       <c r="J63" t="n">
-        <v>0.331</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="64">
@@ -2998,7 +2998,7 @@
         <v>0.291</v>
       </c>
       <c r="J64" t="n">
-        <v>0.61</v>
+        <v>0.44375</v>
       </c>
     </row>
     <row r="65">
@@ -3038,7 +3038,7 @@
         <v>0.291</v>
       </c>
       <c r="J65" t="n">
-        <v>0.627</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="66">
@@ -3078,7 +3078,7 @@
         <v>0.214</v>
       </c>
       <c r="J66" t="n">
-        <v>0.61</v>
+        <v>0.5183333333333333</v>
       </c>
     </row>
     <row r="67">
@@ -3118,7 +3118,7 @@
         <v>0.214</v>
       </c>
       <c r="J67" t="n">
-        <v>0.629</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="68">
@@ -3158,7 +3158,7 @@
         <v>0.304</v>
       </c>
       <c r="J68" t="n">
-        <v>0.246</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="69">
@@ -3198,7 +3198,7 @@
         <v>0.304</v>
       </c>
       <c r="J69" t="n">
-        <v>0.165</v>
+        <v>0.1645</v>
       </c>
     </row>
     <row r="70">
@@ -3238,7 +3238,7 @@
         <v>0.184</v>
       </c>
       <c r="J70" t="n">
-        <v>0.343</v>
+        <v>0.3475</v>
       </c>
     </row>
     <row r="71">
@@ -3278,7 +3278,7 @@
         <v>0.184</v>
       </c>
       <c r="J71" t="n">
-        <v>0.237</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="72">
@@ -3318,7 +3318,7 @@
         <v>0.292</v>
       </c>
       <c r="J72" t="n">
-        <v>0.469</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="73">
@@ -3358,7 +3358,7 @@
         <v>0.292</v>
       </c>
       <c r="J73" t="n">
-        <v>0.388</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="74">
@@ -3398,7 +3398,7 @@
         <v>0.184</v>
       </c>
       <c r="J74" t="n">
-        <v>0.836</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="75">
@@ -3438,7 +3438,7 @@
         <v>0.184</v>
       </c>
       <c r="J75" t="n">
-        <v>0.627</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="76">
@@ -3478,7 +3478,7 @@
         <v>0.281</v>
       </c>
       <c r="J76" t="n">
-        <v>0.645</v>
+        <v>0.44375</v>
       </c>
     </row>
     <row r="77">
@@ -3518,7 +3518,7 @@
         <v>0.281</v>
       </c>
       <c r="J77" t="n">
-        <v>0.847</v>
+        <v>0.8139999999999998</v>
       </c>
     </row>
     <row r="78">
@@ -3558,7 +3558,7 @@
         <v>0.191</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="79">
@@ -3598,7 +3598,7 @@
         <v>0.191</v>
       </c>
       <c r="J79" t="n">
-        <v>0.846</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="80">
@@ -3638,7 +3638,7 @@
         <v>0.204</v>
       </c>
       <c r="J80" t="n">
-        <v>0.972</v>
+        <v>0.9399999999999998</v>
       </c>
     </row>
     <row r="81">
@@ -3678,7 +3678,7 @@
         <v>0.204</v>
       </c>
       <c r="J81" t="n">
-        <v>0.846</v>
+        <v>0.8139999999999998</v>
       </c>
     </row>
     <row r="82">
@@ -3718,7 +3718,7 @@
         <v>0.214</v>
       </c>
       <c r="J82" t="n">
-        <v>0.945</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="83">
@@ -3758,7 +3758,7 @@
         <v>0.214</v>
       </c>
       <c r="J83" t="n">
-        <v>0.847</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3798,7 +3798,7 @@
         <v>0.214</v>
       </c>
       <c r="J84" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.7533333333333333</v>
       </c>
     </row>
     <row r="85">
@@ -3838,7 +3838,7 @@
         <v>0.214</v>
       </c>
       <c r="J85" t="n">
-        <v>0.846</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -3878,7 +3878,7 @@
         <v>0.203</v>
       </c>
       <c r="J86" t="n">
-        <v>0.246</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="87">
@@ -3918,7 +3918,7 @@
         <v>0.203</v>
       </c>
       <c r="J87" t="n">
-        <v>0.202</v>
+        <v>0.2024</v>
       </c>
     </row>
     <row r="88">
@@ -3958,7 +3958,7 @@
         <v>0.216</v>
       </c>
       <c r="J88" t="n">
-        <v>0.573</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="89">
@@ -3998,7 +3998,7 @@
         <v>0.216</v>
       </c>
       <c r="J89" t="n">
-        <v>0.415</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="90">
@@ -4038,7 +4038,7 @@
         <v>0.227</v>
       </c>
       <c r="J90" t="n">
-        <v>0.246</v>
+        <v>0.00693</v>
       </c>
     </row>
     <row r="91">
@@ -4078,7 +4078,7 @@
         <v>0.227</v>
       </c>
       <c r="J91" t="n">
-        <v>0.133</v>
+        <v>0.00222</v>
       </c>
     </row>
     <row r="92">
@@ -4118,7 +4118,7 @@
         <v>0.13</v>
       </c>
       <c r="J92" t="n">
-        <v>0.959</v>
+        <v>0.9109999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -4158,7 +4158,7 @@
         <v>0.13</v>
       </c>
       <c r="J93" t="n">
-        <v>0.833</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="94">
@@ -4198,7 +4198,7 @@
         <v>0.264</v>
       </c>
       <c r="J94" t="n">
-        <v>0.864</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="95">
@@ -4278,7 +4278,7 @@
         <v>0.144</v>
       </c>
       <c r="J96" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="97">
@@ -4318,7 +4318,7 @@
         <v>0.144</v>
       </c>
       <c r="J97" t="n">
-        <v>0.847</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="98">
@@ -4358,7 +4358,7 @@
         <v>0.276</v>
       </c>
       <c r="J98" t="n">
-        <v>0.61</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="99">
@@ -4398,7 +4398,7 @@
         <v>0.276</v>
       </c>
       <c r="J99" t="n">
-        <v>0.847</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="100">
@@ -4438,7 +4438,7 @@
         <v>0.149</v>
       </c>
       <c r="J100" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="101">
@@ -4478,7 +4478,7 @@
         <v>0.149</v>
       </c>
       <c r="J101" t="n">
-        <v>0.762</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="102">
@@ -4518,7 +4518,7 @@
         <v>0.258</v>
       </c>
       <c r="J102" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="103">
@@ -4558,7 +4558,7 @@
         <v>0.258</v>
       </c>
       <c r="J103" t="n">
-        <v>0.846</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="104">
@@ -4598,7 +4598,7 @@
         <v>0.121</v>
       </c>
       <c r="J104" t="n">
-        <v>0.836</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="105">
@@ -4638,7 +4638,7 @@
         <v>0.121</v>
       </c>
       <c r="J105" t="n">
-        <v>0.846</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="106">
@@ -4678,7 +4678,7 @@
         <v>0.241</v>
       </c>
       <c r="J106" t="n">
-        <v>0.864</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="107">
@@ -4718,7 +4718,7 @@
         <v>0.241</v>
       </c>
       <c r="J107" t="n">
-        <v>0.846</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="108">
@@ -4758,7 +4758,7 @@
         <v>0.128</v>
       </c>
       <c r="J108" t="n">
-        <v>0.588</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="109">
@@ -4798,7 +4798,7 @@
         <v>0.128</v>
       </c>
       <c r="J109" t="n">
-        <v>0.627</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="110">
@@ -4838,7 +4838,7 @@
         <v>0.137</v>
       </c>
       <c r="J110" t="n">
-        <v>0.588</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="111">
@@ -4878,7 +4878,7 @@
         <v>0.137</v>
       </c>
       <c r="J111" t="n">
-        <v>0.338</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="112">
@@ -4918,7 +4918,7 @@
         <v>0.179</v>
       </c>
       <c r="J112" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="113">
@@ -4958,7 +4958,7 @@
         <v>0.179</v>
       </c>
       <c r="J113" t="n">
-        <v>0.833</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="114">
@@ -4998,7 +4998,7 @@
         <v>0.181</v>
       </c>
       <c r="J114" t="n">
-        <v>0.708</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="115">
@@ -5038,7 +5038,7 @@
         <v>0.181</v>
       </c>
       <c r="J115" t="n">
-        <v>0.846</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="116">
@@ -5078,7 +5078,7 @@
         <v>0.169</v>
       </c>
       <c r="J116" t="n">
-        <v>0.246</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="117">
@@ -5118,7 +5118,7 @@
         <v>0.169</v>
       </c>
       <c r="J117" t="n">
-        <v>0.191</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="118">
@@ -5158,7 +5158,7 @@
         <v>0.168</v>
       </c>
       <c r="J118" t="n">
-        <v>0.246</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="119">
@@ -5198,7 +5198,7 @@
         <v>0.168</v>
       </c>
       <c r="J119" t="n">
-        <v>0.144</v>
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -5238,7 +5238,7 @@
         <v>0.191</v>
       </c>
       <c r="J120" t="n">
-        <v>0.246</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="121">
@@ -5278,7 +5278,7 @@
         <v>0.191</v>
       </c>
       <c r="J121" t="n">
-        <v>0.165</v>
+        <v>0.0268</v>
       </c>
     </row>
   </sheetData>
